--- a/data/df_main.xlsx
+++ b/data/df_main.xlsx
@@ -32631,7 +32631,7 @@
         <v>351</v>
       </c>
       <c r="B329" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C329" t="n">
         <v>0</v>
@@ -32640,7 +32640,7 @@
         <v>0</v>
       </c>
       <c r="E329" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F329" t="n">
         <v>0</v>

--- a/data/df_main.xlsx
+++ b/data/df_main.xlsx
@@ -436,7 +436,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>net_impact</t>
+          <t>no_fragmentation</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
@@ -576,7 +576,7 @@
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>We_Re</t>
+          <t>K</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
@@ -601,7 +601,7 @@
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>drop_density</t>
+          <t>droplet_density</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">

--- a/data/df_main.xlsx
+++ b/data/df_main.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN373"/>
+  <dimension ref="A1:AP373"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -611,20 +611,30 @@
       </c>
       <c r="AK1" s="1" t="inlineStr">
         <is>
+          <t>sign_sedimentation_Stk</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>sign_particle_droplet_diameter_ratio</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
           <t>droplet_density</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>free_fall_velocity</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>drag_velocity</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>relative_roughness</t>
         </is>
@@ -746,15 +756,21 @@
         <v>9.157839388730198e-05</v>
       </c>
       <c r="AK2" t="n">
+        <v>8.252778095517668e-08</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>0.01330128205128205</v>
+      </c>
+      <c r="AM2" t="n">
         <v>836.8285868675472</v>
       </c>
-      <c r="AL2" t="n">
+      <c r="AN2" t="n">
         <v>3.961141249690548</v>
       </c>
-      <c r="AM2" t="n">
+      <c r="AO2" t="n">
         <v>3.682513497785235</v>
       </c>
-      <c r="AN2" t="n">
+      <c r="AP2" t="n">
         <v>3.205128205128205e-05</v>
       </c>
     </row>
@@ -874,15 +890,21 @@
         <v>9.157839388730198e-05</v>
       </c>
       <c r="AK3" t="n">
+        <v>8.252778095517668e-08</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>0.01330128205128205</v>
+      </c>
+      <c r="AM3" t="n">
         <v>835.2982444578599</v>
       </c>
-      <c r="AL3" t="n">
+      <c r="AN3" t="n">
         <v>3.961141249690548</v>
       </c>
-      <c r="AM3" t="n">
+      <c r="AO3" t="n">
         <v>3.682027496496301</v>
       </c>
-      <c r="AN3" t="n">
+      <c r="AP3" t="n">
         <v>3.205128205128205e-05</v>
       </c>
     </row>
@@ -1002,15 +1024,21 @@
         <v>9.157839388730198e-05</v>
       </c>
       <c r="AK4" t="n">
+        <v>8.252778095517668e-08</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>0.01330128205128205</v>
+      </c>
+      <c r="AM4" t="n">
         <v>835.2982444578599</v>
       </c>
-      <c r="AL4" t="n">
+      <c r="AN4" t="n">
         <v>3.961141249690548</v>
       </c>
-      <c r="AM4" t="n">
+      <c r="AO4" t="n">
         <v>3.682027496496301</v>
       </c>
-      <c r="AN4" t="n">
+      <c r="AP4" t="n">
         <v>3.205128205128205e-05</v>
       </c>
     </row>
@@ -1130,15 +1158,21 @@
         <v>9.157839388730198e-05</v>
       </c>
       <c r="AK5" t="n">
+        <v>8.582889219338375e-08</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>0.01383333333333333</v>
+      </c>
+      <c r="AM5" t="n">
         <v>836.869873642735</v>
       </c>
-      <c r="AL5" t="n">
+      <c r="AN5" t="n">
         <v>3.961141249690548</v>
       </c>
-      <c r="AM5" t="n">
+      <c r="AO5" t="n">
         <v>3.668434996402615</v>
       </c>
-      <c r="AN5" t="n">
+      <c r="AP5" t="n">
         <v>1.333333333333333e-05</v>
       </c>
     </row>
@@ -1258,15 +1292,21 @@
         <v>9.157839388730198e-05</v>
       </c>
       <c r="AK6" t="n">
+        <v>8.582889219338375e-08</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>0.01383333333333333</v>
+      </c>
+      <c r="AM6" t="n">
         <v>836.7950289868945</v>
       </c>
-      <c r="AL6" t="n">
+      <c r="AN6" t="n">
         <v>3.961141249690548</v>
       </c>
-      <c r="AM6" t="n">
+      <c r="AO6" t="n">
         <v>3.66841013411497</v>
       </c>
-      <c r="AN6" t="n">
+      <c r="AP6" t="n">
         <v>1.333333333333333e-05</v>
       </c>
     </row>
@@ -1386,15 +1426,21 @@
         <v>9.157839388730198e-05</v>
       </c>
       <c r="AK7" t="n">
+        <v>8.226411392337101e-08</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>0.01325878594249201</v>
+      </c>
+      <c r="AM7" t="n">
         <v>835.8498204726242</v>
       </c>
-      <c r="AL7" t="n">
+      <c r="AN7" t="n">
         <v>3.961141249690548</v>
       </c>
-      <c r="AM7" t="n">
+      <c r="AO7" t="n">
         <v>3.683323173999915</v>
       </c>
-      <c r="AN7" t="n">
+      <c r="AP7" t="n">
         <v>1.277955271565495e-05</v>
       </c>
     </row>
@@ -1514,15 +1560,21 @@
         <v>9.157839388730198e-05</v>
       </c>
       <c r="AK8" t="n">
+        <v>7.971723733131618e-08</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>0.01284829721362229</v>
+      </c>
+      <c r="AM8" t="n">
         <v>836.3189646353669</v>
       </c>
-      <c r="AL8" t="n">
+      <c r="AN8" t="n">
         <v>3.961141249690548</v>
       </c>
-      <c r="AM8" t="n">
+      <c r="AO8" t="n">
         <v>3.694237237277959</v>
       </c>
-      <c r="AN8" t="n">
+      <c r="AP8" t="n">
         <v>0.0007708978328173377</v>
       </c>
     </row>
@@ -1642,15 +1694,21 @@
         <v>9.157839388730198e-05</v>
       </c>
       <c r="AK9" t="n">
+        <v>7.996480639135131e-08</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>0.01288819875776397</v>
+      </c>
+      <c r="AM9" t="n">
         <v>836.4579549418531</v>
       </c>
-      <c r="AL9" t="n">
+      <c r="AN9" t="n">
         <v>3.961141249690548</v>
       </c>
-      <c r="AM9" t="n">
+      <c r="AO9" t="n">
         <v>3.693237303454563</v>
       </c>
-      <c r="AN9" t="n">
+      <c r="AP9" t="n">
         <v>0.003381987577639751</v>
       </c>
     </row>
@@ -1770,15 +1828,21 @@
         <v>0</v>
       </c>
       <c r="AK10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>0.04645270270270271</v>
+      </c>
+      <c r="AM10" t="n">
         <v>1000</v>
       </c>
-      <c r="AL10" t="n">
+      <c r="AN10" t="n">
         <v>3.961141249690548</v>
       </c>
-      <c r="AM10" t="n">
+      <c r="AO10" t="n">
         <v>3.709931613862793</v>
       </c>
-      <c r="AN10" t="n">
+      <c r="AP10" t="n">
         <v>3.378378378378378e-05</v>
       </c>
     </row>
@@ -1898,15 +1962,21 @@
         <v>0</v>
       </c>
       <c r="AK11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>0.04530477759472817</v>
+      </c>
+      <c r="AM11" t="n">
         <v>1000</v>
       </c>
-      <c r="AL11" t="n">
+      <c r="AN11" t="n">
         <v>3.961141249690548</v>
       </c>
-      <c r="AM11" t="n">
+      <c r="AO11" t="n">
         <v>3.717783124367191</v>
       </c>
-      <c r="AN11" t="n">
+      <c r="AP11" t="n">
         <v>3.29489291598023e-05</v>
       </c>
     </row>
@@ -2026,15 +2096,21 @@
         <v>0</v>
       </c>
       <c r="AK12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>0.04530477759472817</v>
+      </c>
+      <c r="AM12" t="n">
         <v>1000</v>
       </c>
-      <c r="AL12" t="n">
+      <c r="AN12" t="n">
         <v>3.961141249690548</v>
       </c>
-      <c r="AM12" t="n">
+      <c r="AO12" t="n">
         <v>3.717783124367191</v>
       </c>
-      <c r="AN12" t="n">
+      <c r="AP12" t="n">
         <v>1.317957166392092e-05</v>
       </c>
     </row>
@@ -2154,15 +2230,21 @@
         <v>0</v>
       </c>
       <c r="AK13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>0.04530477759472817</v>
+      </c>
+      <c r="AM13" t="n">
         <v>1000</v>
       </c>
-      <c r="AL13" t="n">
+      <c r="AN13" t="n">
         <v>3.961141249690548</v>
       </c>
-      <c r="AM13" t="n">
+      <c r="AO13" t="n">
         <v>3.717783124367191</v>
       </c>
-      <c r="AN13" t="n">
+      <c r="AP13" t="n">
         <v>1.317957166392092e-05</v>
       </c>
     </row>
@@ -2282,15 +2364,21 @@
         <v>0</v>
       </c>
       <c r="AK14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>0.04414125200642054</v>
+      </c>
+      <c r="AM14" t="n">
         <v>1000</v>
       </c>
-      <c r="AL14" t="n">
+      <c r="AN14" t="n">
         <v>3.961141249690548</v>
       </c>
-      <c r="AM14" t="n">
+      <c r="AO14" t="n">
         <v>3.725683295241426</v>
       </c>
-      <c r="AN14" t="n">
+      <c r="AP14" t="n">
         <v>0.0007993579454253613</v>
       </c>
     </row>
@@ -2410,15 +2498,21 @@
         <v>0</v>
       </c>
       <c r="AK15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>0.04243827160493827</v>
+      </c>
+      <c r="AM15" t="n">
         <v>1000</v>
       </c>
-      <c r="AL15" t="n">
+      <c r="AN15" t="n">
         <v>3.961141249690548</v>
       </c>
-      <c r="AM15" t="n">
+      <c r="AO15" t="n">
         <v>3.737137643920139</v>
       </c>
-      <c r="AN15" t="n">
+      <c r="AP15" t="n">
         <v>0.0007685185185185186</v>
       </c>
     </row>
@@ -2538,15 +2632,21 @@
         <v>0</v>
       </c>
       <c r="AK16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>0.04414125200642054</v>
+      </c>
+      <c r="AM16" t="n">
         <v>1000</v>
       </c>
-      <c r="AL16" t="n">
+      <c r="AN16" t="n">
         <v>3.961141249690548</v>
       </c>
-      <c r="AM16" t="n">
+      <c r="AO16" t="n">
         <v>3.725683295241426</v>
       </c>
-      <c r="AN16" t="n">
+      <c r="AP16" t="n">
         <v>0.0007993579454253613</v>
       </c>
     </row>
@@ -2666,15 +2766,21 @@
         <v>0</v>
       </c>
       <c r="AK17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>0.04185692541856925</v>
+      </c>
+      <c r="AM17" t="n">
         <v>1000</v>
       </c>
-      <c r="AL17" t="n">
+      <c r="AN17" t="n">
         <v>3.961141249690548</v>
       </c>
-      <c r="AM17" t="n">
+      <c r="AO17" t="n">
         <v>3.741017463414428</v>
       </c>
-      <c r="AN17" t="n">
+      <c r="AP17" t="n">
         <v>0.003315068493150685</v>
       </c>
     </row>
@@ -2794,15 +2900,21 @@
         <v>0</v>
       </c>
       <c r="AK18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>0.04185692541856925</v>
+      </c>
+      <c r="AM18" t="n">
         <v>1000</v>
       </c>
-      <c r="AL18" t="n">
+      <c r="AN18" t="n">
         <v>3.961141249690548</v>
       </c>
-      <c r="AM18" t="n">
+      <c r="AO18" t="n">
         <v>3.741017463414428</v>
       </c>
-      <c r="AN18" t="n">
+      <c r="AP18" t="n">
         <v>0.003315068493150685</v>
       </c>
     </row>
@@ -2922,15 +3034,21 @@
         <v>0</v>
       </c>
       <c r="AK19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>0.04583333333333334</v>
+      </c>
+      <c r="AM19" t="n">
         <v>1000</v>
       </c>
-      <c r="AL19" t="n">
+      <c r="AN19" t="n">
         <v>3.961141249690548</v>
       </c>
-      <c r="AM19" t="n">
+      <c r="AO19" t="n">
         <v>3.714174914583952</v>
       </c>
-      <c r="AN19" t="n">
+      <c r="AP19" t="n">
         <v>1.333333333333333e-05</v>
       </c>
     </row>
@@ -3050,15 +3168,21 @@
         <v>0</v>
       </c>
       <c r="AK20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>0.04407051282051282</v>
+      </c>
+      <c r="AM20" t="n">
         <v>1000</v>
       </c>
-      <c r="AL20" t="n">
+      <c r="AN20" t="n">
         <v>3.961141249690548</v>
       </c>
-      <c r="AM20" t="n">
+      <c r="AO20" t="n">
         <v>3.726161685296046</v>
       </c>
-      <c r="AN20" t="n">
+      <c r="AP20" t="n">
         <v>3.205128205128205e-05</v>
       </c>
     </row>
@@ -3178,15 +3302,21 @@
         <v>-0.0003989206273344665</v>
       </c>
       <c r="AK21" t="n">
+        <v>-2.873090305437607e-07</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>-0.01374172185430463</v>
+      </c>
+      <c r="AM21" t="n">
         <v>1054.995240434749</v>
       </c>
-      <c r="AL21" t="n">
+      <c r="AN21" t="n">
         <v>3.961141249690548</v>
       </c>
-      <c r="AM21" t="n">
+      <c r="AO21" t="n">
         <v>3.728516073995413</v>
       </c>
-      <c r="AN21" t="n">
+      <c r="AP21" t="n">
         <v>3.311258278145695e-05</v>
       </c>
     </row>
@@ -3306,15 +3436,21 @@
         <v>-0.0003989206273344665</v>
       </c>
       <c r="AK22" t="n">
+        <v>-2.745801494437206e-07</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>-0.01313291139240506</v>
+      </c>
+      <c r="AM22" t="n">
         <v>1055.601731168147</v>
       </c>
-      <c r="AL22" t="n">
+      <c r="AN22" t="n">
         <v>3.961141249690548</v>
       </c>
-      <c r="AM22" t="n">
+      <c r="AO22" t="n">
         <v>3.741658915404045</v>
       </c>
-      <c r="AN22" t="n">
+      <c r="AP22" t="n">
         <v>3.164556962025316e-05</v>
       </c>
     </row>
@@ -3434,15 +3570,21 @@
         <v>-0.0003989206273344665</v>
       </c>
       <c r="AK23" t="n">
+        <v>-2.79894603949083e-07</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>-0.01338709677419355</v>
+      </c>
+      <c r="AM23" t="n">
         <v>1055.020803462263</v>
       </c>
-      <c r="AL23" t="n">
+      <c r="AN23" t="n">
         <v>3.961141249690548</v>
       </c>
-      <c r="AM23" t="n">
+      <c r="AO23" t="n">
         <v>3.73612716293629</v>
       </c>
-      <c r="AN23" t="n">
+      <c r="AP23" t="n">
         <v>1.290322580645161e-05</v>
       </c>
     </row>
@@ -3562,15 +3704,21 @@
         <v>-0.0003989206273344665</v>
       </c>
       <c r="AK24" t="n">
+        <v>-2.719978909850022e-07</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>-0.01300940438871473</v>
+      </c>
+      <c r="AM24" t="n">
         <v>1054.857650163281</v>
       </c>
-      <c r="AL24" t="n">
+      <c r="AN24" t="n">
         <v>3.961141249690548</v>
       </c>
-      <c r="AM24" t="n">
+      <c r="AO24" t="n">
         <v>3.74413026985831</v>
       </c>
-      <c r="AN24" t="n">
+      <c r="AP24" t="n">
         <v>1.253918495297806e-05</v>
       </c>
     </row>
@@ -3690,15 +3838,21 @@
         <v>-0.0003989206273344665</v>
       </c>
       <c r="AK25" t="n">
+        <v>-2.686294960502035e-07</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>-0.01284829721362229</v>
+      </c>
+      <c r="AM25" t="n">
         <v>1054.673654429518</v>
       </c>
-      <c r="AL25" t="n">
+      <c r="AN25" t="n">
         <v>3.961141249690548</v>
       </c>
-      <c r="AM25" t="n">
+      <c r="AO25" t="n">
         <v>3.747501555657688</v>
       </c>
-      <c r="AN25" t="n">
+      <c r="AP25" t="n">
         <v>0.0007708978328173377</v>
       </c>
     </row>
@@ -3818,15 +3972,21 @@
         <v>-0.0003989206273344665</v>
       </c>
       <c r="AK26" t="n">
+        <v>-2.781004077699222e-07</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>-0.01330128205128205</v>
+      </c>
+      <c r="AM26" t="n">
         <v>1055.297456817683</v>
       </c>
-      <c r="AL26" t="n">
+      <c r="AN26" t="n">
         <v>3.961141249690548</v>
       </c>
-      <c r="AM26" t="n">
+      <c r="AO26" t="n">
         <v>3.738015162587003</v>
       </c>
-      <c r="AN26" t="n">
+      <c r="AP26" t="n">
         <v>0.0007980769230769232</v>
       </c>
     </row>
@@ -3946,15 +4106,21 @@
         <v>-0.0003989206273344665</v>
       </c>
       <c r="AK27" t="n">
+        <v>-2.785467968674662e-07</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>-0.01332263242375602</v>
+      </c>
+      <c r="AM27" t="n">
         <v>1055.190348147041</v>
       </c>
-      <c r="AL27" t="n">
+      <c r="AN27" t="n">
         <v>3.961141249690548</v>
       </c>
-      <c r="AM27" t="n">
+      <c r="AO27" t="n">
         <v>3.737538035876294</v>
       </c>
-      <c r="AN27" t="n">
+      <c r="AP27" t="n">
         <v>0.003495987158908507</v>
       </c>
     </row>
@@ -4074,15 +4240,21 @@
         <v>-0.0003989206273344665</v>
       </c>
       <c r="AK28" t="n">
+        <v>-3.033822630217333e-07</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>-0.01451048951048951</v>
+      </c>
+      <c r="AM28" t="n">
         <v>1055.391503682689</v>
       </c>
-      <c r="AL28" t="n">
+      <c r="AN28" t="n">
         <v>3.961141249690548</v>
       </c>
-      <c r="AM28" t="n">
+      <c r="AO28" t="n">
         <v>3.711922080297822</v>
       </c>
-      <c r="AN28" t="n">
+      <c r="AP28" t="n">
         <v>0.003807692307692308</v>
       </c>
     </row>
@@ -4202,15 +4374,21 @@
         <v>-0.0003989206273344665</v>
       </c>
       <c r="AK29" t="n">
+        <v>-3.098833115150561e-07</v>
+      </c>
+      <c r="AL29" t="n">
+        <v>-0.01482142857142857</v>
+      </c>
+      <c r="AM29" t="n">
         <v>1055.209724461915</v>
       </c>
-      <c r="AL29" t="n">
+      <c r="AN29" t="n">
         <v>3.961141249690548</v>
       </c>
-      <c r="AM29" t="n">
+      <c r="AO29" t="n">
         <v>3.705060851425578</v>
       </c>
-      <c r="AN29" t="n">
+      <c r="AP29" t="n">
         <v>0.003889285714285714</v>
       </c>
     </row>
@@ -4330,15 +4508,21 @@
         <v>-8.865952311505664e-05</v>
       </c>
       <c r="AK30" t="n">
+        <v>-5.728643463674261e-08</v>
+      </c>
+      <c r="AL30" t="n">
+        <v>-0.01325878594249201</v>
+      </c>
+      <c r="AM30" t="n">
         <v>1127.267669201892</v>
       </c>
-      <c r="AL30" t="n">
+      <c r="AN30" t="n">
         <v>3.961141249690548</v>
       </c>
-      <c r="AM30" t="n">
+      <c r="AO30" t="n">
         <v>3.752618699624822</v>
       </c>
-      <c r="AN30" t="n">
+      <c r="AP30" t="n">
         <v>3.194888178913738e-05</v>
       </c>
     </row>
@@ -4458,15 +4642,21 @@
         <v>-8.865952311505664e-05</v>
       </c>
       <c r="AK31" t="n">
+        <v>-5.728643463674261e-08</v>
+      </c>
+      <c r="AL31" t="n">
+        <v>-0.01325878594249201</v>
+      </c>
+      <c r="AM31" t="n">
         <v>1128.263695003378</v>
       </c>
-      <c r="AL31" t="n">
+      <c r="AN31" t="n">
         <v>3.961141249690548</v>
       </c>
-      <c r="AM31" t="n">
+      <c r="AO31" t="n">
         <v>3.752796473191149</v>
       </c>
-      <c r="AN31" t="n">
+      <c r="AP31" t="n">
         <v>3.194888178913738e-05</v>
       </c>
     </row>
@@ -4586,15 +4776,21 @@
         <v>-8.865952311505664e-05</v>
       </c>
       <c r="AK32" t="n">
+        <v>-5.433531527666799e-08</v>
+      </c>
+      <c r="AL32" t="n">
+        <v>-0.01257575757575757</v>
+      </c>
+      <c r="AM32" t="n">
         <v>1127.158938407229</v>
       </c>
-      <c r="AL32" t="n">
+      <c r="AN32" t="n">
         <v>3.961141249690548</v>
       </c>
-      <c r="AM32" t="n">
+      <c r="AO32" t="n">
         <v>3.766179213378137</v>
       </c>
-      <c r="AN32" t="n">
+      <c r="AP32" t="n">
         <v>1.212121212121212e-05</v>
       </c>
     </row>
@@ -4714,15 +4910,21 @@
         <v>-8.865952311505664e-05</v>
       </c>
       <c r="AK33" t="n">
+        <v>-5.568526099782744e-08</v>
+      </c>
+      <c r="AL33" t="n">
+        <v>-0.01288819875776397</v>
+      </c>
+      <c r="AM33" t="n">
         <v>1127.08115174453</v>
       </c>
-      <c r="AL33" t="n">
+      <c r="AN33" t="n">
         <v>3.961141249690548</v>
       </c>
-      <c r="AM33" t="n">
+      <c r="AO33" t="n">
         <v>3.759980847095854</v>
       </c>
-      <c r="AN33" t="n">
+      <c r="AP33" t="n">
         <v>1.242236024844721e-05</v>
       </c>
     </row>
@@ -4842,15 +5044,21 @@
         <v>-8.865952311505664e-05</v>
       </c>
       <c r="AK34" t="n">
+        <v>-5.408945412156996e-08</v>
+      </c>
+      <c r="AL34" t="n">
+        <v>-0.01251885369532428</v>
+      </c>
+      <c r="AM34" t="n">
         <v>1126.971785697088</v>
       </c>
-      <c r="AL34" t="n">
+      <c r="AN34" t="n">
         <v>3.961141249690548</v>
       </c>
-      <c r="AM34" t="n">
+      <c r="AO34" t="n">
         <v>3.767269494397141</v>
       </c>
-      <c r="AN34" t="n">
+      <c r="AP34" t="n">
         <v>0.0007511312217194572</v>
       </c>
     </row>
@@ -4970,15 +5178,21 @@
         <v>-8.865952311505664e-05</v>
       </c>
       <c r="AK35" t="n">
+        <v>-5.48338044076466e-08</v>
+      </c>
+      <c r="AL35" t="n">
+        <v>-0.01269113149847095</v>
+      </c>
+      <c r="AM35" t="n">
         <v>1127.429355191294</v>
       </c>
-      <c r="AL35" t="n">
+      <c r="AN35" t="n">
         <v>3.961141249690548</v>
       </c>
-      <c r="AM35" t="n">
+      <c r="AO35" t="n">
         <v>3.763946483325837</v>
       </c>
-      <c r="AN35" t="n">
+      <c r="AP35" t="n">
         <v>0.000761467889908257</v>
       </c>
     </row>
@@ -5098,15 +5312,21 @@
         <v>-8.865952311505664e-05</v>
       </c>
       <c r="AK36" t="n">
+        <v>-5.433531527666799e-08</v>
+      </c>
+      <c r="AL36" t="n">
+        <v>-0.01257575757575758</v>
+      </c>
+      <c r="AM36" t="n">
         <v>1126.907835085663</v>
       </c>
-      <c r="AL36" t="n">
+      <c r="AN36" t="n">
         <v>3.961141249690548</v>
       </c>
-      <c r="AM36" t="n">
+      <c r="AO36" t="n">
         <v>3.766137152705515</v>
       </c>
-      <c r="AN36" t="n">
+      <c r="AP36" t="n">
         <v>0.0033</v>
       </c>
     </row>
@@ -5226,15 +5446,21 @@
         <v>-8.865952311505664e-05</v>
       </c>
       <c r="AK37" t="n">
+        <v>-5.810322113188735e-08</v>
+      </c>
+      <c r="AL37" t="n">
+        <v>-0.01344782890473104</v>
+      </c>
+      <c r="AM37" t="n">
         <v>1127.511621755338</v>
       </c>
-      <c r="AL37" t="n">
+      <c r="AN37" t="n">
         <v>3.961141249690548</v>
       </c>
-      <c r="AM37" t="n">
+      <c r="AO37" t="n">
         <v>3.748866890822422</v>
       </c>
-      <c r="AN37" t="n">
+      <c r="AP37" t="n">
         <v>0.003528839922229423</v>
       </c>
     </row>
@@ -5354,15 +5580,21 @@
         <v>-8.865952311505664e-05</v>
       </c>
       <c r="AK38" t="n">
+        <v>-5.810322113188735e-08</v>
+      </c>
+      <c r="AL38" t="n">
+        <v>-0.01344782890473104</v>
+      </c>
+      <c r="AM38" t="n">
         <v>1127.157335406431</v>
       </c>
-      <c r="AL38" t="n">
+      <c r="AN38" t="n">
         <v>3.961141249690548</v>
       </c>
-      <c r="AM38" t="n">
+      <c r="AO38" t="n">
         <v>3.748802504650531</v>
       </c>
-      <c r="AN38" t="n">
+      <c r="AP38" t="n">
         <v>0.003528839922229423</v>
       </c>
     </row>
@@ -5482,15 +5714,21 @@
         <v>-4.25749611131928e-05</v>
       </c>
       <c r="AK39" t="n">
+        <v>-1.247783111721399e-08</v>
+      </c>
+      <c r="AL39" t="n">
+        <v>-0.01383333333333333</v>
+      </c>
+      <c r="AM39" t="n">
         <v>1117.842509211853</v>
       </c>
-      <c r="AL39" t="n">
+      <c r="AN39" t="n">
         <v>3.961141249690548</v>
       </c>
-      <c r="AM39" t="n">
+      <c r="AO39" t="n">
         <v>3.739244175717368</v>
       </c>
-      <c r="AN39" t="n">
+      <c r="AP39" t="n">
         <v>3.333333333333333e-05</v>
       </c>
     </row>
@@ -5610,15 +5848,21 @@
         <v>-4.25749611131928e-05</v>
       </c>
       <c r="AK40" t="n">
+        <v>-1.117417711989312e-08</v>
+      </c>
+      <c r="AL40" t="n">
+        <v>-0.01238805970149254</v>
+      </c>
+      <c r="AM40" t="n">
         <v>1114.038071218274</v>
       </c>
-      <c r="AL40" t="n">
+      <c r="AN40" t="n">
         <v>3.961141249690548</v>
       </c>
-      <c r="AM40" t="n">
+      <c r="AO40" t="n">
         <v>3.76769069866167</v>
       </c>
-      <c r="AN40" t="n">
+      <c r="AP40" t="n">
         <v>2.985074626865671e-05</v>
       </c>
     </row>
@@ -5738,15 +5982,21 @@
         <v>-4.25749611131928e-05</v>
       </c>
       <c r="AK41" t="n">
+        <v>-1.247783111721399e-08</v>
+      </c>
+      <c r="AL41" t="n">
+        <v>-0.01383333333333333</v>
+      </c>
+      <c r="AM41" t="n">
         <v>1117.00847004171</v>
       </c>
-      <c r="AL41" t="n">
+      <c r="AN41" t="n">
         <v>3.961141249690548</v>
       </c>
-      <c r="AM41" t="n">
+      <c r="AO41" t="n">
         <v>3.739084588583578</v>
       </c>
-      <c r="AN41" t="n">
+      <c r="AP41" t="n">
         <v>1.333333333333333e-05</v>
       </c>
     </row>
@@ -5866,15 +6116,21 @@
         <v>-4.25749611131928e-05</v>
       </c>
       <c r="AK42" t="n">
+        <v>-1.117417711989312e-08</v>
+      </c>
+      <c r="AL42" t="n">
+        <v>-0.01238805970149254</v>
+      </c>
+      <c r="AM42" t="n">
         <v>1113.588832629873</v>
       </c>
-      <c r="AL42" t="n">
+      <c r="AN42" t="n">
         <v>3.961141249690548</v>
       </c>
-      <c r="AM42" t="n">
+      <c r="AO42" t="n">
         <v>3.767615120757383</v>
       </c>
-      <c r="AN42" t="n">
+      <c r="AP42" t="n">
         <v>1.194029850746269e-05</v>
       </c>
     </row>
@@ -5994,15 +6250,21 @@
         <v>-4.25749611131928e-05</v>
       </c>
       <c r="AK43" t="n">
+        <v>-1.117417711989312e-08</v>
+      </c>
+      <c r="AL43" t="n">
+        <v>-0.01238805970149254</v>
+      </c>
+      <c r="AM43" t="n">
         <v>1115.236040787342</v>
       </c>
-      <c r="AL43" t="n">
+      <c r="AN43" t="n">
         <v>3.961141249690548</v>
       </c>
-      <c r="AM43" t="n">
+      <c r="AO43" t="n">
         <v>3.767891952495937</v>
       </c>
-      <c r="AN43" t="n">
+      <c r="AP43" t="n">
         <v>1.194029850746269e-05</v>
       </c>
     </row>
@@ -6122,15 +6384,21 @@
         <v>-4.25749611131928e-05</v>
       </c>
       <c r="AK44" t="n">
+        <v>-1.199791453578268e-08</v>
+      </c>
+      <c r="AL44" t="n">
+        <v>-0.01330128205128205</v>
+      </c>
+      <c r="AM44" t="n">
         <v>1114.414577852456</v>
       </c>
-      <c r="AL44" t="n">
+      <c r="AN44" t="n">
         <v>3.961141249690548</v>
       </c>
-      <c r="AM44" t="n">
+      <c r="AO44" t="n">
         <v>3.749436166849891</v>
       </c>
-      <c r="AN44" t="n">
+      <c r="AP44" t="n">
         <v>0.0007980769230769232</v>
       </c>
     </row>
@@ -6250,15 +6518,21 @@
         <v>-4.25749611131928e-05</v>
       </c>
       <c r="AK45" t="n">
+        <v>-1.117417711989312e-08</v>
+      </c>
+      <c r="AL45" t="n">
+        <v>-0.01238805970149254</v>
+      </c>
+      <c r="AM45" t="n">
         <v>1113.588832629873</v>
       </c>
-      <c r="AL45" t="n">
+      <c r="AN45" t="n">
         <v>3.961141249690548</v>
       </c>
-      <c r="AM45" t="n">
+      <c r="AO45" t="n">
         <v>3.767615120757383</v>
       </c>
-      <c r="AN45" t="n">
+      <c r="AP45" t="n">
         <v>0.0007432835820895523</v>
       </c>
     </row>
@@ -6378,15 +6652,21 @@
         <v>-4.25749611131928e-05</v>
       </c>
       <c r="AK46" t="n">
+        <v>-1.256157495021543e-08</v>
+      </c>
+      <c r="AL46" t="n">
+        <v>-0.01392617449664429</v>
+      </c>
+      <c r="AM46" t="n">
         <v>1116.573129676832</v>
       </c>
-      <c r="AL46" t="n">
+      <c r="AN46" t="n">
         <v>3.961141249690548</v>
       </c>
-      <c r="AM46" t="n">
+      <c r="AO46" t="n">
         <v>3.737098530427906</v>
       </c>
-      <c r="AN46" t="n">
+      <c r="AP46" t="n">
         <v>0.003654362416107383</v>
       </c>
     </row>
@@ -6506,15 +6786,21 @@
         <v>-4.25749611131928e-05</v>
       </c>
       <c r="AK47" t="n">
+        <v>-1.092948710996846e-08</v>
+      </c>
+      <c r="AL47" t="n">
+        <v>-0.01211678832116788</v>
+      </c>
+      <c r="AM47" t="n">
         <v>1121.712883356608</v>
       </c>
-      <c r="AL47" t="n">
+      <c r="AN47" t="n">
         <v>3.961141249690548</v>
       </c>
-      <c r="AM47" t="n">
+      <c r="AO47" t="n">
         <v>3.774304364628232</v>
       </c>
-      <c r="AN47" t="n">
+      <c r="AP47" t="n">
         <v>0.003179562043795621</v>
       </c>
     </row>
@@ -6634,15 +6920,21 @@
         <v>-4.25749611131928e-05</v>
       </c>
       <c r="AK48" t="n">
+        <v>-1.092948710996846e-08</v>
+      </c>
+      <c r="AL48" t="n">
+        <v>-0.01211678832116788</v>
+      </c>
+      <c r="AM48" t="n">
         <v>1116.388220808502</v>
       </c>
-      <c r="AL48" t="n">
+      <c r="AN48" t="n">
         <v>3.961141249690548</v>
       </c>
-      <c r="AM48" t="n">
+      <c r="AO48" t="n">
         <v>3.773440371780204</v>
       </c>
-      <c r="AN48" t="n">
+      <c r="AP48" t="n">
         <v>0.000727007299270073</v>
       </c>
     </row>
@@ -6762,15 +7054,21 @@
         <v>-4.25749611131928e-05</v>
       </c>
       <c r="AK49" t="n">
+        <v>-1.092948710996846e-08</v>
+      </c>
+      <c r="AL49" t="n">
+        <v>-0.01211678832116788</v>
+      </c>
+      <c r="AM49" t="n">
         <v>1119.330797479824</v>
       </c>
-      <c r="AL49" t="n">
+      <c r="AN49" t="n">
         <v>3.961141249690548</v>
       </c>
-      <c r="AM49" t="n">
+      <c r="AO49" t="n">
         <v>3.773918823078744</v>
       </c>
-      <c r="AN49" t="n">
+      <c r="AP49" t="n">
         <v>1.167883211678832e-05</v>
       </c>
     </row>
@@ -6890,15 +7188,21 @@
         <v>-4.25749611131928e-05</v>
       </c>
       <c r="AK50" t="n">
+        <v>-1.173463741430783e-08</v>
+      </c>
+      <c r="AL50" t="n">
+        <v>-0.01300940438871473</v>
+      </c>
+      <c r="AM50" t="n">
         <v>1152.958309455517</v>
       </c>
-      <c r="AL50" t="n">
+      <c r="AN50" t="n">
         <v>3.961141249690548</v>
       </c>
-      <c r="AM50" t="n">
+      <c r="AO50" t="n">
         <v>3.761989104764215</v>
       </c>
-      <c r="AN50" t="n">
+      <c r="AP50" t="n">
         <v>3.134796238244514e-05</v>
       </c>
     </row>
@@ -7018,15 +7322,21 @@
         <v>6.452497583807169e-05</v>
       </c>
       <c r="AK51" t="n">
+        <v>8.587002580002603e-08</v>
+      </c>
+      <c r="AL51" t="n">
+        <v>0.01284829721362229</v>
+      </c>
+      <c r="AM51" t="n">
         <v>1278.015402507899</v>
       </c>
-      <c r="AL51" t="n">
+      <c r="AN51" t="n">
         <v>3.961141249690548</v>
       </c>
-      <c r="AM51" t="n">
+      <c r="AO51" t="n">
         <v>3.783758918364402</v>
       </c>
-      <c r="AN51" t="n">
+      <c r="AP51" t="n">
         <v>3.095975232198142e-05</v>
       </c>
     </row>
@@ -7146,15 +7456,21 @@
         <v>6.452497583807169e-05</v>
       </c>
       <c r="AK52" t="n">
+        <v>9.434019841295377e-08</v>
+      </c>
+      <c r="AL52" t="n">
+        <v>0.0141156462585034</v>
+      </c>
+      <c r="AM52" t="n">
         <v>1281.866692501734</v>
       </c>
-      <c r="AL52" t="n">
+      <c r="AN52" t="n">
         <v>3.961141249690548</v>
       </c>
-      <c r="AM52" t="n">
+      <c r="AO52" t="n">
         <v>3.761632807959211</v>
       </c>
-      <c r="AN52" t="n">
+      <c r="AP52" t="n">
         <v>3.401360544217687e-05</v>
       </c>
     </row>
@@ -7274,15 +7590,21 @@
         <v>6.452497583807169e-05</v>
       </c>
       <c r="AK53" t="n">
+        <v>8.964453242859859e-08</v>
+      </c>
+      <c r="AL53" t="n">
+        <v>0.01341305753070459</v>
+      </c>
+      <c r="AM53" t="n">
         <v>1282.530689645075</v>
       </c>
-      <c r="AL53" t="n">
+      <c r="AN53" t="n">
         <v>3.961141249690548</v>
       </c>
-      <c r="AM53" t="n">
+      <c r="AO53" t="n">
         <v>3.774361824533606</v>
       </c>
-      <c r="AN53" t="n">
+      <c r="AP53" t="n">
         <v>1.292824822236587e-05</v>
       </c>
     </row>
@@ -7402,15 +7724,21 @@
         <v>6.452497583807169e-05</v>
       </c>
       <c r="AK54" t="n">
+        <v>8.964453242859859e-08</v>
+      </c>
+      <c r="AL54" t="n">
+        <v>0.01341305753070459</v>
+      </c>
+      <c r="AM54" t="n">
         <v>1273.836403177121</v>
       </c>
-      <c r="AL54" t="n">
+      <c r="AN54" t="n">
         <v>3.961141249690548</v>
       </c>
-      <c r="AM54" t="n">
+      <c r="AO54" t="n">
         <v>3.773125494282089</v>
       </c>
-      <c r="AN54" t="n">
+      <c r="AP54" t="n">
         <v>1.292824822236587e-05</v>
       </c>
     </row>
@@ -7530,15 +7858,21 @@
         <v>6.452497583807169e-05</v>
       </c>
       <c r="AK55" t="n">
+        <v>8.225390964830489e-08</v>
+      </c>
+      <c r="AL55" t="n">
+        <v>0.01230723606168446</v>
+      </c>
+      <c r="AM55" t="n">
         <v>1274.535158520326</v>
       </c>
-      <c r="AL55" t="n">
+      <c r="AN55" t="n">
         <v>3.961141249690548</v>
       </c>
-      <c r="AM55" t="n">
+      <c r="AO55" t="n">
         <v>3.792799865310049</v>
       </c>
-      <c r="AN55" t="n">
+      <c r="AP55" t="n">
         <v>0.0007384341637010677</v>
       </c>
     </row>
@@ -7658,15 +7992,21 @@
         <v>6.452497583807169e-05</v>
       </c>
       <c r="AK56" t="n">
+        <v>8.225390964830489e-08</v>
+      </c>
+      <c r="AL56" t="n">
+        <v>0.01230723606168446</v>
+      </c>
+      <c r="AM56" t="n">
         <v>1294.435402397751</v>
       </c>
-      <c r="AL56" t="n">
+      <c r="AN56" t="n">
         <v>3.961141249690548</v>
       </c>
-      <c r="AM56" t="n">
+      <c r="AO56" t="n">
         <v>3.795320490474449</v>
       </c>
-      <c r="AN56" t="n">
+      <c r="AP56" t="n">
         <v>0.0007384341637010677</v>
       </c>
     </row>
@@ -7786,15 +8126,21 @@
         <v>6.452497583807169e-05</v>
       </c>
       <c r="AK57" t="n">
+        <v>9.905720833360145e-08</v>
+      </c>
+      <c r="AL57" t="n">
+        <v>0.01482142857142857</v>
+      </c>
+      <c r="AM57" t="n">
         <v>1290.709303773896</v>
       </c>
-      <c r="AL57" t="n">
+      <c r="AN57" t="n">
         <v>3.961141249690548</v>
       </c>
-      <c r="AM57" t="n">
+      <c r="AO57" t="n">
         <v>3.750148818572502</v>
       </c>
-      <c r="AN57" t="n">
+      <c r="AP57" t="n">
         <v>0.003889285714285714</v>
       </c>
     </row>
@@ -7914,15 +8260,21 @@
         <v>6.452497583807169e-05</v>
       </c>
       <c r="AK58" t="n">
+        <v>8.904018726615861e-08</v>
+      </c>
+      <c r="AL58" t="n">
+        <v>0.01332263242375602</v>
+      </c>
+      <c r="AM58" t="n">
         <v>1273.590590000643</v>
       </c>
-      <c r="AL58" t="n">
+      <c r="AN58" t="n">
         <v>3.961141249690548</v>
       </c>
-      <c r="AM58" t="n">
+      <c r="AO58" t="n">
         <v>3.774711640759508</v>
       </c>
-      <c r="AN58" t="n">
+      <c r="AP58" t="n">
         <v>0.003495987158908507</v>
       </c>
     </row>
@@ -8042,15 +8394,21 @@
         <v>6.452497583807169e-05</v>
       </c>
       <c r="AK59" t="n">
+        <v>8.777220991584939e-08</v>
+      </c>
+      <c r="AL59" t="n">
+        <v>0.01313291139240506</v>
+      </c>
+      <c r="AM59" t="n">
         <v>1277.92163349798</v>
       </c>
-      <c r="AL59" t="n">
+      <c r="AN59" t="n">
         <v>3.961141249690548</v>
       </c>
-      <c r="AM59" t="n">
+      <c r="AO59" t="n">
         <v>3.778704484453188</v>
       </c>
-      <c r="AN59" t="n">
+      <c r="AP59" t="n">
         <v>0.00344620253164557</v>
       </c>
     </row>
@@ -8170,15 +8528,21 @@
         <v>6.452497583807169e-05</v>
       </c>
       <c r="AK60" t="n">
+        <v>1.002023783721402e-07</v>
+      </c>
+      <c r="AL60" t="n">
+        <v>0.01499277456647399</v>
+      </c>
+      <c r="AM60" t="n">
         <v>1301.174508006347</v>
       </c>
-      <c r="AL60" t="n">
+      <c r="AN60" t="n">
         <v>3.961141249690548</v>
       </c>
-      <c r="AM60" t="n">
+      <c r="AO60" t="n">
         <v>3.74867350708905</v>
       </c>
-      <c r="AN60" t="n">
+      <c r="AP60" t="n">
         <v>0.003934248554913295</v>
       </c>
     </row>
@@ -8298,15 +8662,21 @@
         <v>4.601922739624822e-05</v>
       </c>
       <c r="AK61" t="n">
+        <v>1.291524559735175e-07</v>
+      </c>
+      <c r="AL61" t="n">
+        <v>0.04967485549132949</v>
+      </c>
+      <c r="AM61" t="n">
         <v>1181.68731269209</v>
       </c>
-      <c r="AL61" t="n">
+      <c r="AN61" t="n">
         <v>3.961141249690548</v>
       </c>
-      <c r="AM61" t="n">
+      <c r="AO61" t="n">
         <v>3.72801386067346</v>
       </c>
-      <c r="AN61" t="n">
+      <c r="AP61" t="n">
         <v>3.61271676300578e-05</v>
       </c>
     </row>
@@ -8426,15 +8796,21 @@
         <v>4.601922739624822e-05</v>
       </c>
       <c r="AK62" t="n">
+        <v>1.051452935690284e-07</v>
+      </c>
+      <c r="AL62" t="n">
+        <v>0.04044117647058824</v>
+      </c>
+      <c r="AM62" t="n">
         <v>1181.64608860543</v>
       </c>
-      <c r="AL62" t="n">
+      <c r="AN62" t="n">
         <v>3.961141249690548</v>
       </c>
-      <c r="AM62" t="n">
+      <c r="AO62" t="n">
         <v>3.781845549882189</v>
       </c>
-      <c r="AN62" t="n">
+      <c r="AP62" t="n">
         <v>2.941176470588235e-05</v>
       </c>
     </row>
@@ -8554,15 +8930,21 @@
         <v>4.601922739624822e-05</v>
       </c>
       <c r="AK63" t="n">
+        <v>1.051452935690284e-07</v>
+      </c>
+      <c r="AL63" t="n">
+        <v>0.04044117647058824</v>
+      </c>
+      <c r="AM63" t="n">
         <v>1181.648136987893</v>
       </c>
-      <c r="AL63" t="n">
+      <c r="AN63" t="n">
         <v>3.961141249690548</v>
       </c>
-      <c r="AM63" t="n">
+      <c r="AO63" t="n">
         <v>3.781845851755203</v>
       </c>
-      <c r="AN63" t="n">
+      <c r="AP63" t="n">
         <v>1.176470588235294e-05</v>
       </c>
     </row>
@@ -8682,15 +9064,21 @@
         <v>4.601922739624822e-05</v>
       </c>
       <c r="AK64" t="n">
+        <v>1.093253816925678e-07</v>
+      </c>
+      <c r="AL64" t="n">
+        <v>0.04204892966360857</v>
+      </c>
+      <c r="AM64" t="n">
         <v>1181.655260623917</v>
       </c>
-      <c r="AL64" t="n">
+      <c r="AN64" t="n">
         <v>3.961141249690548</v>
       </c>
-      <c r="AM64" t="n">
+      <c r="AO64" t="n">
         <v>3.772718564387044</v>
       </c>
-      <c r="AN64" t="n">
+      <c r="AP64" t="n">
         <v>0.000761467889908257</v>
       </c>
     </row>
@@ -8810,15 +9198,21 @@
         <v>4.601922739624822e-05</v>
       </c>
       <c r="AK65" t="n">
+        <v>1.10679256388451e-07</v>
+      </c>
+      <c r="AL65" t="n">
+        <v>0.04256965944272446</v>
+      </c>
+      <c r="AM65" t="n">
         <v>1181.65853374586</v>
       </c>
-      <c r="AL65" t="n">
+      <c r="AN65" t="n">
         <v>3.961141249690548</v>
       </c>
-      <c r="AM65" t="n">
+      <c r="AO65" t="n">
         <v>3.769739177702135</v>
       </c>
-      <c r="AN65" t="n">
+      <c r="AP65" t="n">
         <v>0.003371517027863777</v>
       </c>
     </row>
@@ -8938,15 +9332,21 @@
         <v>4.601922739624822e-05</v>
       </c>
       <c r="AK66" t="n">
+        <v>1.078413267374651e-07</v>
+      </c>
+      <c r="AL66" t="n">
+        <v>0.04147812971342384</v>
+      </c>
+      <c r="AM66" t="n">
         <v>1181.661880702214</v>
       </c>
-      <c r="AL66" t="n">
+      <c r="AN66" t="n">
         <v>3.961141249690548</v>
       </c>
-      <c r="AM66" t="n">
+      <c r="AO66" t="n">
         <v>3.775972968930921</v>
       </c>
-      <c r="AN66" t="n">
+      <c r="AP66" t="n">
         <v>0.003285067873303168</v>
       </c>
     </row>
@@ -9066,15 +9466,21 @@
         <v>4.601922739624822e-05</v>
       </c>
       <c r="AK67" t="n">
+        <v>1.110229807871728e-07</v>
+      </c>
+      <c r="AL67" t="n">
+        <v>0.04270186335403726</v>
+      </c>
+      <c r="AM67" t="n">
         <v>1181.666315168735</v>
       </c>
-      <c r="AL67" t="n">
+      <c r="AN67" t="n">
         <v>3.961141249690548</v>
       </c>
-      <c r="AM67" t="n">
+      <c r="AO67" t="n">
         <v>3.768982072731264</v>
       </c>
-      <c r="AN67" t="n">
+      <c r="AP67" t="n">
         <v>0.0007732919254658386</v>
       </c>
     </row>
@@ -9194,15 +9600,21 @@
         <v>4.601922739624822e-05</v>
       </c>
       <c r="AK68" t="n">
+        <v>1.115425891215902e-07</v>
+      </c>
+      <c r="AL68" t="n">
+        <v>0.04290171606864275</v>
+      </c>
+      <c r="AM68" t="n">
         <v>1181.677032546094</v>
       </c>
-      <c r="AL68" t="n">
+      <c r="AN68" t="n">
         <v>3.961141249690548</v>
       </c>
-      <c r="AM68" t="n">
+      <c r="AO68" t="n">
         <v>3.767836040979826</v>
       </c>
-      <c r="AN68" t="n">
+      <c r="AP68" t="n">
         <v>1.24804992199688e-05</v>
       </c>
     </row>
@@ -9322,15 +9734,21 @@
         <v>4.601922739624822e-05</v>
       </c>
       <c r="AK69" t="n">
+        <v>1.142153348673152e-07</v>
+      </c>
+      <c r="AL69" t="n">
+        <v>0.0439297124600639</v>
+      </c>
+      <c r="AM69" t="n">
         <v>1181.678765501469</v>
       </c>
-      <c r="AL69" t="n">
+      <c r="AN69" t="n">
         <v>3.961141249690548</v>
       </c>
-      <c r="AM69" t="n">
+      <c r="AO69" t="n">
         <v>3.761906946164126</v>
       </c>
-      <c r="AN69" t="n">
+      <c r="AP69" t="n">
         <v>3.194888178913738e-05</v>
       </c>
     </row>
@@ -9450,15 +9868,21 @@
         <v>4.601922739624822e-05</v>
       </c>
       <c r="AK70" t="n">
+        <v>1.089920726020416e-07</v>
+      </c>
+      <c r="AL70" t="n">
+        <v>0.04192073170731708</v>
+      </c>
+      <c r="AM70" t="n">
         <v>1181.667305148236</v>
       </c>
-      <c r="AL70" t="n">
+      <c r="AN70" t="n">
         <v>3.961141249690548</v>
       </c>
-      <c r="AM70" t="n">
+      <c r="AO70" t="n">
         <v>3.773452303727211</v>
       </c>
-      <c r="AN70" t="n">
+      <c r="AP70" t="n">
         <v>1.219512195121951e-05</v>
       </c>
     </row>
@@ -9578,15 +10002,21 @@
         <v>0</v>
       </c>
       <c r="AK71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL71" t="n">
+        <v>0.01227810650887574</v>
+      </c>
+      <c r="AM71" t="n">
         <v>1000</v>
       </c>
-      <c r="AL71" t="n">
+      <c r="AN71" t="n">
         <v>3.961141249690548</v>
       </c>
-      <c r="AM71" t="n">
+      <c r="AO71" t="n">
         <v>3.748820384115742</v>
       </c>
-      <c r="AN71" t="n">
+      <c r="AP71" t="n">
         <v>0.0007366863905325444</v>
       </c>
     </row>
@@ -9706,15 +10136,21 @@
         <v>0</v>
       </c>
       <c r="AK72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL72" t="n">
+        <v>0.01248264692272096</v>
+      </c>
+      <c r="AM72" t="n">
         <v>1000</v>
       </c>
-      <c r="AL72" t="n">
+      <c r="AN72" t="n">
         <v>3.961141249690548</v>
       </c>
-      <c r="AM72" t="n">
+      <c r="AO72" t="n">
         <v>3.744333520855724</v>
       </c>
-      <c r="AN72" t="n">
+      <c r="AP72" t="n">
         <v>1.203146691346599e-05</v>
       </c>
     </row>
@@ -9834,15 +10270,21 @@
         <v>0</v>
       </c>
       <c r="AK73" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL73" t="n">
+        <v>0.01499277456647399</v>
+      </c>
+      <c r="AM73" t="n">
         <v>1000</v>
       </c>
-      <c r="AL73" t="n">
+      <c r="AN73" t="n">
         <v>3.961141249690548</v>
       </c>
-      <c r="AM73" t="n">
+      <c r="AO73" t="n">
         <v>3.687601437910904</v>
       </c>
-      <c r="AN73" t="n">
+      <c r="AP73" t="n">
         <v>0.0008995664739884394</v>
       </c>
     </row>
@@ -9962,15 +10404,21 @@
         <v>0</v>
       </c>
       <c r="AK74" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL74" t="n">
+        <v>0.0125</v>
+      </c>
+      <c r="AM74" t="n">
         <v>1000</v>
       </c>
-      <c r="AL74" t="n">
+      <c r="AN74" t="n">
         <v>3.961141249690548</v>
       </c>
-      <c r="AM74" t="n">
+      <c r="AO74" t="n">
         <v>3.743951854080553</v>
       </c>
-      <c r="AN74" t="n">
+      <c r="AP74" t="n">
         <v>1.204819277108434e-05</v>
       </c>
     </row>
@@ -10090,15 +10538,21 @@
         <v>0</v>
       </c>
       <c r="AK75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>0.01175637393767705</v>
+      </c>
+      <c r="AM75" t="n">
         <v>1000</v>
       </c>
-      <c r="AL75" t="n">
+      <c r="AN75" t="n">
         <v>3.961141249690548</v>
       </c>
-      <c r="AM75" t="n">
+      <c r="AO75" t="n">
         <v>3.760164515579596</v>
       </c>
-      <c r="AN75" t="n">
+      <c r="AP75" t="n">
         <v>2.832861189801699e-05</v>
       </c>
     </row>
@@ -10218,15 +10672,21 @@
         <v>0</v>
       </c>
       <c r="AK76" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL76" t="n">
+        <v>0.01146408839779006</v>
+      </c>
+      <c r="AM76" t="n">
         <v>1000</v>
       </c>
-      <c r="AL76" t="n">
+      <c r="AN76" t="n">
         <v>3.961141249690548</v>
       </c>
-      <c r="AM76" t="n">
+      <c r="AO76" t="n">
         <v>3.766454753338581</v>
       </c>
-      <c r="AN76" t="n">
+      <c r="AP76" t="n">
         <v>2.762430939226519e-05</v>
       </c>
     </row>
@@ -10346,15 +10806,21 @@
         <v>0</v>
       </c>
       <c r="AK77" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL77" t="n">
+        <v>0.01192528735632184</v>
+      </c>
+      <c r="AM77" t="n">
         <v>1000</v>
       </c>
-      <c r="AL77" t="n">
+      <c r="AN77" t="n">
         <v>3.961141249690548</v>
       </c>
-      <c r="AM77" t="n">
+      <c r="AO77" t="n">
         <v>3.756507878202096</v>
       </c>
-      <c r="AN77" t="n">
+      <c r="AP77" t="n">
         <v>0.0007155172413793105</v>
       </c>
     </row>
@@ -10474,15 +10940,21 @@
         <v>-1.28239052559562e-05</v>
       </c>
       <c r="AK78" t="n">
+        <v>-8.161603822334206e-09</v>
+      </c>
+      <c r="AL78" t="n">
+        <v>-0.01351791530944626</v>
+      </c>
+      <c r="AM78" t="n">
         <v>1171.346818312983</v>
       </c>
-      <c r="AL78" t="n">
+      <c r="AN78" t="n">
         <v>3.961141249690548</v>
       </c>
-      <c r="AM78" t="n">
+      <c r="AO78" t="n">
         <v>3.755181664286654</v>
       </c>
-      <c r="AN78" t="n">
+      <c r="AP78" t="n">
         <v>1.302931596091205e-05</v>
       </c>
     </row>
@@ -10602,15 +11074,21 @@
         <v>-1.28239052559562e-05</v>
       </c>
       <c r="AK79" t="n">
+        <v>-7.854584242810663e-09</v>
+      </c>
+      <c r="AL79" t="n">
+        <v>-0.01300940438871473</v>
+      </c>
+      <c r="AM79" t="n">
         <v>1171.23828987274</v>
       </c>
-      <c r="AL79" t="n">
+      <c r="AN79" t="n">
         <v>3.961141249690548</v>
       </c>
-      <c r="AM79" t="n">
+      <c r="AO79" t="n">
         <v>3.7649979570125</v>
       </c>
-      <c r="AN79" t="n">
+      <c r="AP79" t="n">
         <v>0.0007805642633228841</v>
       </c>
     </row>
@@ -10730,15 +11208,21 @@
         <v>-1.28239052559562e-05</v>
       </c>
       <c r="AK80" t="n">
+        <v>-8.082620559537425e-09</v>
+      </c>
+      <c r="AL80" t="n">
+        <v>-0.01338709677419355</v>
+      </c>
+      <c r="AM80" t="n">
         <v>1171.287723070056</v>
       </c>
-      <c r="AL80" t="n">
+      <c r="AN80" t="n">
         <v>3.961141249690548</v>
       </c>
-      <c r="AM80" t="n">
+      <c r="AO80" t="n">
         <v>3.757712516689845</v>
       </c>
-      <c r="AN80" t="n">
+      <c r="AP80" t="n">
         <v>1.290322580645161e-05</v>
       </c>
     </row>
@@ -10858,15 +11342,21 @@
         <v>-1.28239052559562e-05</v>
       </c>
       <c r="AK81" t="n">
+        <v>-8.197205147622467e-09</v>
+      </c>
+      <c r="AL81" t="n">
+        <v>-0.01357688113413304</v>
+      </c>
+      <c r="AM81" t="n">
         <v>1171.563666718426</v>
       </c>
-      <c r="AL81" t="n">
+      <c r="AN81" t="n">
         <v>3.961141249690548</v>
       </c>
-      <c r="AM81" t="n">
+      <c r="AO81" t="n">
         <v>3.754071012897144</v>
       </c>
-      <c r="AN81" t="n">
+      <c r="AP81" t="n">
         <v>0.0008146128680479825</v>
       </c>
     </row>
@@ -10986,15 +11476,21 @@
         <v>-1.28239052559562e-05</v>
       </c>
       <c r="AK82" t="n">
+        <v>-8.551578066404783e-09</v>
+      </c>
+      <c r="AL82" t="n">
+        <v>-0.01416382252559727</v>
+      </c>
+      <c r="AM82" t="n">
         <v>1171.531928210345</v>
       </c>
-      <c r="AL82" t="n">
+      <c r="AN82" t="n">
         <v>3.961141249690548</v>
       </c>
-      <c r="AM82" t="n">
+      <c r="AO82" t="n">
         <v>3.742562018117074</v>
       </c>
-      <c r="AN82" t="n">
+      <c r="AP82" t="n">
         <v>0.0008498293515358363</v>
       </c>
     </row>
@@ -11114,15 +11610,21 @@
         <v>-1.28239052559562e-05</v>
       </c>
       <c r="AK83" t="n">
+        <v>-8.269347767183503e-09</v>
+      </c>
+      <c r="AL83" t="n">
+        <v>-0.0136963696369637</v>
+      </c>
+      <c r="AM83" t="n">
         <v>1171.383281803179</v>
       </c>
-      <c r="AL83" t="n">
+      <c r="AN83" t="n">
         <v>3.961141249690548</v>
       </c>
-      <c r="AM83" t="n">
+      <c r="AO83" t="n">
         <v>3.751709983154772</v>
       </c>
-      <c r="AN83" t="n">
+      <c r="AP83" t="n">
         <v>3.3003300330033e-05</v>
       </c>
     </row>
@@ -11242,15 +11744,21 @@
         <v>-1.28239052559562e-05</v>
       </c>
       <c r="AK84" t="n">
+        <v>-7.391186942349857e-09</v>
+      </c>
+      <c r="AL84" t="n">
+        <v>-0.01224188790560472</v>
+      </c>
+      <c r="AM84" t="n">
         <v>1171.262949830897</v>
       </c>
-      <c r="AL84" t="n">
+      <c r="AN84" t="n">
         <v>3.961141249690548</v>
       </c>
-      <c r="AM84" t="n">
+      <c r="AO84" t="n">
         <v>3.779623123043296</v>
       </c>
-      <c r="AN84" t="n">
+      <c r="AP84" t="n">
         <v>0.0007345132743362833</v>
       </c>
     </row>
@@ -11370,15 +11878,21 @@
         <v>-1.28239052559562e-05</v>
       </c>
       <c r="AK85" t="n">
+        <v>-8.436405297833676e-09</v>
+      </c>
+      <c r="AL85" t="n">
+        <v>-0.01397306397306397</v>
+      </c>
+      <c r="AM85" t="n">
         <v>1171.3990033728</v>
       </c>
-      <c r="AL85" t="n">
+      <c r="AN85" t="n">
         <v>3.961141249690548</v>
       </c>
-      <c r="AM85" t="n">
+      <c r="AO85" t="n">
         <v>3.746293252451529</v>
       </c>
-      <c r="AN85" t="n">
+      <c r="AP85" t="n">
         <v>3.367003367003367e-05</v>
       </c>
     </row>
@@ -11498,15 +12012,21 @@
         <v>-1.28239052559562e-05</v>
       </c>
       <c r="AK86" t="n">
+        <v>-7.904139979358364e-09</v>
+      </c>
+      <c r="AL86" t="n">
+        <v>-0.01309148264984227</v>
+      </c>
+      <c r="AM86" t="n">
         <v>1171.46596840732</v>
       </c>
-      <c r="AL86" t="n">
+      <c r="AN86" t="n">
         <v>3.961141249690548</v>
       </c>
-      <c r="AM86" t="n">
+      <c r="AO86" t="n">
         <v>3.763455527180499</v>
       </c>
-      <c r="AN86" t="n">
+      <c r="AP86" t="n">
         <v>0.0007854889589905364</v>
       </c>
     </row>
@@ -11626,15 +12146,21 @@
         <v>-1.28239052559562e-05</v>
       </c>
       <c r="AK87" t="n">
+        <v>-7.536548092303519e-09</v>
+      </c>
+      <c r="AL87" t="n">
+        <v>-0.01248264692272096</v>
+      </c>
+      <c r="AM87" t="n">
         <v>1171.284460313315</v>
       </c>
-      <c r="AL87" t="n">
+      <c r="AN87" t="n">
         <v>3.961141249690548</v>
       </c>
-      <c r="AM87" t="n">
+      <c r="AO87" t="n">
         <v>3.775069503896765</v>
       </c>
-      <c r="AN87" t="n">
+      <c r="AP87" t="n">
         <v>0.0007489588153632578</v>
       </c>
     </row>
@@ -11754,15 +12280,21 @@
         <v>1.48124178509601e-06</v>
       </c>
       <c r="AK88" t="n">
+        <v>1.027505333491867e-09</v>
+      </c>
+      <c r="AL88" t="n">
+        <v>0.01227810650887574</v>
+      </c>
+      <c r="AM88" t="n">
         <v>1180.803779965656</v>
       </c>
-      <c r="AL88" t="n">
+      <c r="AN88" t="n">
         <v>3.961141249690548</v>
       </c>
-      <c r="AM88" t="n">
+      <c r="AO88" t="n">
         <v>3.780368756101577</v>
       </c>
-      <c r="AN88" t="n">
+      <c r="AP88" t="n">
         <v>1.183431952662722e-05</v>
       </c>
     </row>
@@ -11882,15 +12414,21 @@
         <v>1.48124178509601e-06</v>
       </c>
       <c r="AK89" t="n">
+        <v>1.046074706988708e-09</v>
+      </c>
+      <c r="AL89" t="n">
+        <v>0.0125</v>
+      </c>
+      <c r="AM89" t="n">
         <v>1180.80281550322</v>
       </c>
-      <c r="AL89" t="n">
+      <c r="AN89" t="n">
         <v>3.961141249690548</v>
       </c>
-      <c r="AM89" t="n">
+      <c r="AO89" t="n">
         <v>3.776197729573671</v>
       </c>
-      <c r="AN89" t="n">
+      <c r="AP89" t="n">
         <v>0.0007500000000000001</v>
       </c>
     </row>
@@ -12010,15 +12548,21 @@
         <v>1.48124178509601e-06</v>
       </c>
       <c r="AK90" t="n">
+        <v>1.133105392235729e-09</v>
+      </c>
+      <c r="AL90" t="n">
+        <v>0.01353996737357259</v>
+      </c>
+      <c r="AM90" t="n">
         <v>1180.805143831056</v>
       </c>
-      <c r="AL90" t="n">
+      <c r="AN90" t="n">
         <v>3.961141249690548</v>
       </c>
-      <c r="AM90" t="n">
+      <c r="AO90" t="n">
         <v>3.756350386721849</v>
       </c>
-      <c r="AN90" t="n">
+      <c r="AP90" t="n">
         <v>0.0008123980424143558</v>
       </c>
     </row>
@@ -12138,15 +12682,21 @@
         <v>1.48124178509601e-06</v>
       </c>
       <c r="AK91" t="n">
+        <v>1.133105392235729e-09</v>
+      </c>
+      <c r="AL91" t="n">
+        <v>0.01353996737357259</v>
+      </c>
+      <c r="AM91" t="n">
         <v>1180.803205575875</v>
       </c>
-      <c r="AL91" t="n">
+      <c r="AN91" t="n">
         <v>3.961141249690548</v>
       </c>
-      <c r="AM91" t="n">
+      <c r="AO91" t="n">
         <v>3.75635006182565</v>
       </c>
-      <c r="AN91" t="n">
+      <c r="AP91" t="n">
         <v>1.305057096247961e-05</v>
       </c>
     </row>
@@ -12266,15 +12816,21 @@
         <v>1.48124178509601e-06</v>
       </c>
       <c r="AK92" t="n">
+        <v>1.133105392235729e-09</v>
+      </c>
+      <c r="AL92" t="n">
+        <v>0.01353996737357259</v>
+      </c>
+      <c r="AM92" t="n">
         <v>1180.803280124152</v>
       </c>
-      <c r="AL92" t="n">
+      <c r="AN92" t="n">
         <v>3.961141249690548</v>
       </c>
-      <c r="AM92" t="n">
+      <c r="AO92" t="n">
         <v>3.756350074321679</v>
       </c>
-      <c r="AN92" t="n">
+      <c r="AP92" t="n">
         <v>3.262642740619902e-05</v>
       </c>
     </row>
@@ -12394,15 +12950,21 @@
         <v>1.48124178509601e-06</v>
       </c>
       <c r="AK93" t="n">
+        <v>1.133105392235729e-09</v>
+      </c>
+      <c r="AL93" t="n">
+        <v>0.01353996737357259</v>
+      </c>
+      <c r="AM93" t="n">
         <v>1180.803727413809</v>
       </c>
-      <c r="AL93" t="n">
+      <c r="AN93" t="n">
         <v>3.961141249690548</v>
       </c>
-      <c r="AM93" t="n">
+      <c r="AO93" t="n">
         <v>3.756350149297806</v>
       </c>
-      <c r="AN93" t="n">
+      <c r="AP93" t="n">
         <v>3.262642740619902e-05</v>
       </c>
     </row>
@@ -12522,15 +13084,21 @@
         <v>1.48124178509601e-06</v>
       </c>
       <c r="AK94" t="n">
+        <v>1.133105392235729e-09</v>
+      </c>
+      <c r="AL94" t="n">
+        <v>0.01353996737357259</v>
+      </c>
+      <c r="AM94" t="n">
         <v>1180.80350376898</v>
       </c>
-      <c r="AL94" t="n">
+      <c r="AN94" t="n">
         <v>3.961141249690548</v>
       </c>
-      <c r="AM94" t="n">
+      <c r="AO94" t="n">
         <v>3.756350111809749</v>
       </c>
-      <c r="AN94" t="n">
+      <c r="AP94" t="n">
         <v>0.0008123980424143558</v>
       </c>
     </row>
@@ -12650,15 +13218,21 @@
         <v>1.48124178509601e-06</v>
       </c>
       <c r="AK95" t="n">
+        <v>1.033621436667414e-09</v>
+      </c>
+      <c r="AL95" t="n">
+        <v>0.01235119047619048</v>
+      </c>
+      <c r="AM95" t="n">
         <v>1180.807525976377</v>
       </c>
-      <c r="AL95" t="n">
+      <c r="AN95" t="n">
         <v>3.961141249690548</v>
       </c>
-      <c r="AM95" t="n">
+      <c r="AO95" t="n">
         <v>3.77899812833378</v>
       </c>
-      <c r="AN95" t="n">
+      <c r="AP95" t="n">
         <v>1.190476190476191e-05</v>
       </c>
     </row>
@@ -12778,15 +13352,21 @@
         <v>1.48124178509601e-06</v>
       </c>
       <c r="AK96" t="n">
+        <v>1.033621436667414e-09</v>
+      </c>
+      <c r="AL96" t="n">
+        <v>0.01235119047619048</v>
+      </c>
+      <c r="AM96" t="n">
         <v>1180.804866420815</v>
       </c>
-      <c r="AL96" t="n">
+      <c r="AN96" t="n">
         <v>3.961141249690548</v>
       </c>
-      <c r="AM96" t="n">
+      <c r="AO96" t="n">
         <v>3.778997730103757</v>
       </c>
-      <c r="AN96" t="n">
+      <c r="AP96" t="n">
         <v>2.976190476190476e-05</v>
       </c>
     </row>
@@ -12906,15 +13486,21 @@
         <v>0</v>
       </c>
       <c r="AK97" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL97" t="n">
+        <v>0.04044117647058824</v>
+      </c>
+      <c r="AM97" t="n">
         <v>1000</v>
       </c>
-      <c r="AL97" t="n">
+      <c r="AN97" t="n">
         <v>3.961141249690548</v>
       </c>
-      <c r="AM97" t="n">
+      <c r="AO97" t="n">
         <v>3.750399463094666</v>
       </c>
-      <c r="AN97" t="n">
+      <c r="AP97" t="n">
         <v>2.941176470588235e-05</v>
       </c>
     </row>
@@ -13034,15 +13620,21 @@
         <v>0</v>
       </c>
       <c r="AK98" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL98" t="n">
+        <v>0.04154078549848943</v>
+      </c>
+      <c r="AM98" t="n">
         <v>1000</v>
       </c>
-      <c r="AL98" t="n">
+      <c r="AN98" t="n">
         <v>3.961141249690548</v>
       </c>
-      <c r="AM98" t="n">
+      <c r="AO98" t="n">
         <v>3.743120718827931</v>
       </c>
-      <c r="AN98" t="n">
+      <c r="AP98" t="n">
         <v>3.021148036253776e-05</v>
       </c>
     </row>
@@ -13162,15 +13754,21 @@
         <v>0</v>
       </c>
       <c r="AK99" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL99" t="n">
+        <v>0.0402046783625731</v>
+      </c>
+      <c r="AM99" t="n">
         <v>1000</v>
       </c>
-      <c r="AL99" t="n">
+      <c r="AN99" t="n">
         <v>3.961141249690548</v>
       </c>
-      <c r="AM99" t="n">
+      <c r="AO99" t="n">
         <v>3.751957355084721</v>
       </c>
-      <c r="AN99" t="n">
+      <c r="AP99" t="n">
         <v>1.169590643274854e-05</v>
       </c>
     </row>
@@ -13290,15 +13888,21 @@
         <v>0</v>
       </c>
       <c r="AK100" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL100" t="n">
+        <v>0.04008746355685131</v>
+      </c>
+      <c r="AM100" t="n">
         <v>1000</v>
       </c>
-      <c r="AL100" t="n">
+      <c r="AN100" t="n">
         <v>3.961141249690548</v>
       </c>
-      <c r="AM100" t="n">
+      <c r="AO100" t="n">
         <v>3.752728481900707</v>
       </c>
-      <c r="AN100" t="n">
+      <c r="AP100" t="n">
         <v>1.166180758017493e-05</v>
       </c>
     </row>
@@ -13418,15 +14022,21 @@
         <v>0</v>
       </c>
       <c r="AK101" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL101" t="n">
+        <v>0.04008746355685132</v>
+      </c>
+      <c r="AM101" t="n">
         <v>1000</v>
       </c>
-      <c r="AL101" t="n">
+      <c r="AN101" t="n">
         <v>3.961141249690548</v>
       </c>
-      <c r="AM101" t="n">
+      <c r="AO101" t="n">
         <v>3.752728481900707</v>
       </c>
-      <c r="AN101" t="n">
+      <c r="AP101" t="n">
         <v>0.0007259475218658894</v>
       </c>
     </row>
@@ -13546,15 +14156,21 @@
         <v>0</v>
       </c>
       <c r="AK102" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL102" t="n">
+        <v>0.04008746355685132</v>
+      </c>
+      <c r="AM102" t="n">
         <v>1000</v>
       </c>
-      <c r="AL102" t="n">
+      <c r="AN102" t="n">
         <v>3.961141249690548</v>
       </c>
-      <c r="AM102" t="n">
+      <c r="AO102" t="n">
         <v>3.752728481900707</v>
       </c>
-      <c r="AN102" t="n">
+      <c r="AP102" t="n">
         <v>0.0007259475218658894</v>
       </c>
     </row>
@@ -13674,15 +14290,21 @@
         <v>0</v>
       </c>
       <c r="AK103" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL103" t="n">
+        <v>0.04008746355685132</v>
+      </c>
+      <c r="AM103" t="n">
         <v>1000</v>
       </c>
-      <c r="AL103" t="n">
+      <c r="AN103" t="n">
         <v>3.961141249690548</v>
       </c>
-      <c r="AM103" t="n">
+      <c r="AO103" t="n">
         <v>3.752728481900707</v>
       </c>
-      <c r="AN103" t="n">
+      <c r="AP103" t="n">
         <v>0.0007259475218658894</v>
       </c>
     </row>
@@ -13802,15 +14424,21 @@
         <v>0</v>
       </c>
       <c r="AK104" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL104" t="n">
+        <v>0.04008746355685132</v>
+      </c>
+      <c r="AM104" t="n">
         <v>1000</v>
       </c>
-      <c r="AL104" t="n">
+      <c r="AN104" t="n">
         <v>3.961141249690548</v>
       </c>
-      <c r="AM104" t="n">
+      <c r="AO104" t="n">
         <v>3.752728481900707</v>
       </c>
-      <c r="AN104" t="n">
+      <c r="AP104" t="n">
         <v>1.166180758017493e-05</v>
       </c>
     </row>
@@ -13930,15 +14558,21 @@
         <v>0</v>
       </c>
       <c r="AK105" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL105" t="n">
+        <v>0.0476878612716763</v>
+      </c>
+      <c r="AM105" t="n">
         <v>1000</v>
       </c>
-      <c r="AL105" t="n">
+      <c r="AN105" t="n">
         <v>3.961141249690548</v>
       </c>
-      <c r="AM105" t="n">
+      <c r="AO105" t="n">
         <v>3.701421609289706</v>
       </c>
-      <c r="AN105" t="n">
+      <c r="AP105" t="n">
         <v>3.46820809248555e-05</v>
       </c>
     </row>
@@ -14058,15 +14692,21 @@
         <v>-0.0004872167922797028</v>
       </c>
       <c r="AK106" t="n">
+        <v>-3.580142090133943e-07</v>
+      </c>
+      <c r="AL106" t="n">
+        <v>-0.01402027027027027</v>
+      </c>
+      <c r="AM106" t="n">
         <v>1057.453849652152</v>
       </c>
-      <c r="AL106" t="n">
+      <c r="AN106" t="n">
         <v>3.961141249690548</v>
       </c>
-      <c r="AM106" t="n">
+      <c r="AO106" t="n">
         <v>3.723034218419877</v>
       </c>
-      <c r="AN106" t="n">
+      <c r="AP106" t="n">
         <v>3.378378378378378e-05</v>
       </c>
     </row>
@@ -14186,15 +14826,21 @@
         <v>-0.0004872167922797028</v>
       </c>
       <c r="AK107" t="n">
+        <v>-3.924896513628323e-07</v>
+      </c>
+      <c r="AL107" t="n">
+        <v>-0.01537037037037037</v>
+      </c>
+      <c r="AM107" t="n">
         <v>1057.91692206664</v>
       </c>
-      <c r="AL107" t="n">
+      <c r="AN107" t="n">
         <v>3.961141249690548</v>
       </c>
-      <c r="AM107" t="n">
+      <c r="AO107" t="n">
         <v>3.693576591045216</v>
       </c>
-      <c r="AN107" t="n">
+      <c r="AP107" t="n">
         <v>3.703703703703704e-05</v>
       </c>
     </row>
@@ -14314,15 +14960,21 @@
         <v>-0.0004872167922797028</v>
       </c>
       <c r="AK108" t="n">
+        <v>-3.53240686226549e-07</v>
+      </c>
+      <c r="AL108" t="n">
+        <v>-0.01383333333333333</v>
+      </c>
+      <c r="AM108" t="n">
         <v>1057.678123667545</v>
       </c>
-      <c r="AL108" t="n">
+      <c r="AN108" t="n">
         <v>3.961141249690548</v>
       </c>
-      <c r="AM108" t="n">
+      <c r="AO108" t="n">
         <v>3.727113619945359</v>
       </c>
-      <c r="AN108" t="n">
+      <c r="AP108" t="n">
         <v>1.333333333333333e-05</v>
       </c>
     </row>
@@ -14442,15 +15094,21 @@
         <v>-0.0004872167922797028</v>
       </c>
       <c r="AK109" t="n">
+        <v>-3.654213995447059e-07</v>
+      </c>
+      <c r="AL109" t="n">
+        <v>-0.01431034482758621</v>
+      </c>
+      <c r="AM109" t="n">
         <v>1058.072458838219</v>
       </c>
-      <c r="AL109" t="n">
+      <c r="AN109" t="n">
         <v>3.961141249690548</v>
       </c>
-      <c r="AM109" t="n">
+      <c r="AO109" t="n">
         <v>3.716884270911825</v>
       </c>
-      <c r="AN109" t="n">
+      <c r="AP109" t="n">
         <v>1.379310344827586e-05</v>
       </c>
     </row>
@@ -14570,15 +15228,21 @@
         <v>-0.0004872167922797028</v>
       </c>
       <c r="AK110" t="n">
+        <v>-3.509013439336579e-07</v>
+      </c>
+      <c r="AL110" t="n">
+        <v>-0.01374172185430463</v>
+      </c>
+      <c r="AM110" t="n">
         <v>1057.560280889023</v>
       </c>
-      <c r="AL110" t="n">
+      <c r="AN110" t="n">
         <v>3.961141249690548</v>
       </c>
-      <c r="AM110" t="n">
+      <c r="AO110" t="n">
         <v>3.729058411286788</v>
       </c>
-      <c r="AN110" t="n">
+      <c r="AP110" t="n">
         <v>0.0008245033112582782</v>
       </c>
     </row>
@@ -14698,15 +15362,21 @@
         <v>-0.0004872167922797028</v>
       </c>
       <c r="AK111" t="n">
+        <v>-3.451863383321326e-07</v>
+      </c>
+      <c r="AL111" t="n">
+        <v>-0.01351791530944626</v>
+      </c>
+      <c r="AM111" t="n">
         <v>1057.596627731161</v>
       </c>
-      <c r="AL111" t="n">
+      <c r="AN111" t="n">
         <v>3.961141249690548</v>
       </c>
-      <c r="AM111" t="n">
+      <c r="AO111" t="n">
         <v>3.733862091982028</v>
       </c>
-      <c r="AN111" t="n">
+      <c r="AP111" t="n">
         <v>3.257328990228013e-05</v>
       </c>
     </row>
@@ -14826,15 +15496,21 @@
         <v>-0.0004872167922797028</v>
       </c>
       <c r="AK112" t="n">
+        <v>-3.087318452089285e-07</v>
+      </c>
+      <c r="AL112" t="n">
+        <v>-0.01209031318281136</v>
+      </c>
+      <c r="AM112" t="n">
         <v>1057.297509487812</v>
       </c>
-      <c r="AL112" t="n">
+      <c r="AN112" t="n">
         <v>3.961141249690548</v>
       </c>
-      <c r="AM112" t="n">
+      <c r="AO112" t="n">
         <v>3.763836806296226</v>
       </c>
-      <c r="AN112" t="n">
+      <c r="AP112" t="n">
         <v>0.0007254187909686819</v>
       </c>
     </row>
@@ -14954,15 +15630,21 @@
         <v>-0.0004872167922797028</v>
       </c>
       <c r="AK113" t="n">
+        <v>-3.423980803488359e-07</v>
+      </c>
+      <c r="AL113" t="n">
+        <v>-0.01340872374798062</v>
+      </c>
+      <c r="AM113" t="n">
         <v>1057.551407518674</v>
       </c>
-      <c r="AL113" t="n">
+      <c r="AN113" t="n">
         <v>3.961141249690548</v>
       </c>
-      <c r="AM113" t="n">
+      <c r="AO113" t="n">
         <v>3.736184316536219</v>
       </c>
-      <c r="AN113" t="n">
+      <c r="AP113" t="n">
         <v>1.292407108239095e-05</v>
       </c>
     </row>
@@ -15082,15 +15764,21 @@
         <v>-0.0004872167922797028</v>
       </c>
       <c r="AK114" t="n">
+        <v>-3.423980803488359e-07</v>
+      </c>
+      <c r="AL114" t="n">
+        <v>-0.01340872374798062</v>
+      </c>
+      <c r="AM114" t="n">
         <v>1057.485238616433</v>
       </c>
-      <c r="AL114" t="n">
+      <c r="AN114" t="n">
         <v>3.961141249690548</v>
       </c>
-      <c r="AM114" t="n">
+      <c r="AO114" t="n">
         <v>3.736170768128944</v>
       </c>
-      <c r="AN114" t="n">
+      <c r="AP114" t="n">
         <v>1.292407108239095e-05</v>
       </c>
     </row>
@@ -15210,15 +15898,21 @@
         <v>-0.0001082903277166726</v>
       </c>
       <c r="AK115" t="n">
+        <v>-7.300273879535273e-08</v>
+      </c>
+      <c r="AL115" t="n">
+        <v>-0.01383333333333333</v>
+      </c>
+      <c r="AM115" t="n">
         <v>1133.973448839236</v>
       </c>
-      <c r="AL115" t="n">
+      <c r="AN115" t="n">
         <v>3.961141249690548</v>
       </c>
-      <c r="AM115" t="n">
+      <c r="AO115" t="n">
         <v>3.742286352424583</v>
       </c>
-      <c r="AN115" t="n">
+      <c r="AP115" t="n">
         <v>3.333333333333333e-05</v>
       </c>
     </row>
@@ -15338,15 +16032,21 @@
         <v>-0.0001082903277166726</v>
       </c>
       <c r="AK116" t="n">
+        <v>-7.064781173743812e-08</v>
+      </c>
+      <c r="AL116" t="n">
+        <v>-0.01338709677419355</v>
+      </c>
+      <c r="AM116" t="n">
         <v>1133.668802646064</v>
       </c>
-      <c r="AL116" t="n">
+      <c r="AN116" t="n">
         <v>3.961141249690548</v>
       </c>
-      <c r="AM116" t="n">
+      <c r="AO116" t="n">
         <v>3.751194602232578</v>
       </c>
-      <c r="AN116" t="n">
+      <c r="AP116" t="n">
         <v>3.225806451612903e-05</v>
       </c>
     </row>
@@ -15466,15 +16166,21 @@
         <v>-0.0001082903277166726</v>
       </c>
       <c r="AK117" t="n">
+        <v>-6.930639759052474e-08</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>-0.01313291139240506</v>
+      </c>
+      <c r="AM117" t="n">
         <v>1133.980724034225</v>
       </c>
-      <c r="AL117" t="n">
+      <c r="AN117" t="n">
         <v>3.961141249690548</v>
       </c>
-      <c r="AM117" t="n">
+      <c r="AO117" t="n">
         <v>3.756315875696112</v>
       </c>
-      <c r="AN117" t="n">
+      <c r="AP117" t="n">
         <v>1.265822784810127e-05</v>
       </c>
     </row>
@@ -15594,15 +16300,21 @@
         <v>-0.0001082903277166726</v>
       </c>
       <c r="AK118" t="n">
+        <v>-6.997067616167993e-08</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>-0.01325878594249201</v>
+      </c>
+      <c r="AM118" t="n">
         <v>1134.023019503228</v>
       </c>
-      <c r="AL118" t="n">
+      <c r="AN118" t="n">
         <v>3.961141249690548</v>
       </c>
-      <c r="AM118" t="n">
+      <c r="AO118" t="n">
         <v>3.753818519779897</v>
       </c>
-      <c r="AN118" t="n">
+      <c r="AP118" t="n">
         <v>0.0007955271565495208</v>
       </c>
     </row>
@@ -15722,15 +16434,21 @@
         <v>-0.0001082903277166726</v>
       </c>
       <c r="AK119" t="n">
+        <v>-7.110656376170719e-08</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>-0.01347402597402597</v>
+      </c>
+      <c r="AM119" t="n">
         <v>1133.85602228006</v>
       </c>
-      <c r="AL119" t="n">
+      <c r="AN119" t="n">
         <v>3.961141249690548</v>
       </c>
-      <c r="AM119" t="n">
+      <c r="AO119" t="n">
         <v>3.74948884683551</v>
       </c>
-      <c r="AN119" t="n">
+      <c r="AP119" t="n">
         <v>1.298701298701299e-05</v>
       </c>
     </row>
@@ -15850,15 +16568,21 @@
         <v>-0.0001082903277166726</v>
       </c>
       <c r="AK120" t="n">
+        <v>-6.518101678156492e-08</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>-0.01235119047619048</v>
+      </c>
+      <c r="AM120" t="n">
         <v>1133.648179613701</v>
       </c>
-      <c r="AL120" t="n">
+      <c r="AN120" t="n">
         <v>3.961141249690548</v>
       </c>
-      <c r="AM120" t="n">
+      <c r="AO120" t="n">
         <v>3.771653045497734</v>
       </c>
-      <c r="AN120" t="n">
+      <c r="AP120" t="n">
         <v>0.003241071428571429</v>
       </c>
     </row>
@@ -15978,15 +16702,21 @@
         <v>-0.0001082903277166726</v>
       </c>
       <c r="AK121" t="n">
+        <v>-6.380428736665934e-08</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>-0.01209031318281136</v>
+      </c>
+      <c r="AM121" t="n">
         <v>1134.320760626649</v>
       </c>
-      <c r="AL121" t="n">
+      <c r="AN121" t="n">
         <v>3.961141249690548</v>
       </c>
-      <c r="AM121" t="n">
+      <c r="AO121" t="n">
         <v>3.776831899646142</v>
       </c>
-      <c r="AN121" t="n">
+      <c r="AP121" t="n">
         <v>0.0007254187909686819</v>
       </c>
     </row>
@@ -16106,15 +16836,21 @@
         <v>-0.0001082903277166726</v>
       </c>
       <c r="AK122" t="n">
+        <v>-6.699775484277782e-08</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>-0.01269544527532291</v>
+      </c>
+      <c r="AM122" t="n">
         <v>1133.594676544809</v>
       </c>
-      <c r="AL122" t="n">
+      <c r="AN122" t="n">
         <v>3.961141249690548</v>
       </c>
-      <c r="AM122" t="n">
+      <c r="AO122" t="n">
         <v>3.764899762402797</v>
       </c>
-      <c r="AN122" t="n">
+      <c r="AP122" t="n">
         <v>0.003331407205982325</v>
       </c>
     </row>
@@ -16234,15 +16970,21 @@
         <v>-0.0001082903277166726</v>
       </c>
       <c r="AK123" t="n">
+        <v>-9.025063862062839e-08</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>-0.01710164835164835</v>
+      </c>
+      <c r="AM123" t="n">
         <v>1134.245960065437</v>
       </c>
-      <c r="AL123" t="n">
+      <c r="AN123" t="n">
         <v>3.961141249690548</v>
       </c>
-      <c r="AM123" t="n">
+      <c r="AO123" t="n">
         <v>3.674227416181522</v>
       </c>
-      <c r="AN123" t="n">
+      <c r="AP123" t="n">
         <v>4.120879120879122e-05</v>
       </c>
     </row>
@@ -16362,15 +17104,21 @@
         <v>0.0004306941242754933</v>
       </c>
       <c r="AK124" t="n">
+        <v>2.215753436146231e-06</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0.09105960264900663</v>
+      </c>
+      <c r="AM124" t="n">
         <v>1181.104338303142</v>
       </c>
-      <c r="AL124" t="n">
+      <c r="AN124" t="n">
         <v>3.961141249690548</v>
       </c>
-      <c r="AM124" t="n">
+      <c r="AO124" t="n">
         <v>3.75249567632417</v>
       </c>
-      <c r="AN124" t="n">
+      <c r="AP124" t="n">
         <v>3.311258278145695e-05</v>
       </c>
     </row>
@@ -16490,15 +17238,21 @@
         <v>0.0004306941242754933</v>
       </c>
       <c r="AK125" t="n">
+        <v>1.973916040460655e-06</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>0.08112094395280237</v>
+      </c>
+      <c r="AM125" t="n">
         <v>1180.932969192683</v>
       </c>
-      <c r="AL125" t="n">
+      <c r="AN125" t="n">
         <v>3.961141249690548</v>
       </c>
-      <c r="AM125" t="n">
+      <c r="AO125" t="n">
         <v>3.781066480230215</v>
       </c>
-      <c r="AN125" t="n">
+      <c r="AP125" t="n">
         <v>2.949852507374631e-05</v>
       </c>
     </row>
@@ -16618,15 +17372,21 @@
         <v>0.0004306941242754933</v>
       </c>
       <c r="AK126" t="n">
+        <v>1.962338820282e-06</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>0.08064516129032258</v>
+      </c>
+      <c r="AM126" t="n">
         <v>1180.906889935221</v>
       </c>
-      <c r="AL126" t="n">
+      <c r="AN126" t="n">
         <v>3.961141249690548</v>
       </c>
-      <c r="AM126" t="n">
+      <c r="AO126" t="n">
         <v>3.782405912166555</v>
       </c>
-      <c r="AN126" t="n">
+      <c r="AP126" t="n">
         <v>2.932551319648094e-05</v>
       </c>
     </row>
@@ -16746,15 +17506,21 @@
         <v>0.0004306941242754933</v>
       </c>
       <c r="AK127" t="n">
+        <v>1.956600987474158e-06</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>0.08040935672514621</v>
+      </c>
+      <c r="AM127" t="n">
         <v>1180.908309599664</v>
       </c>
-      <c r="AL127" t="n">
+      <c r="AN127" t="n">
         <v>3.961141249690548</v>
       </c>
-      <c r="AM127" t="n">
+      <c r="AO127" t="n">
         <v>3.783070965725743</v>
       </c>
-      <c r="AN127" t="n">
+      <c r="AP127" t="n">
         <v>1.169590643274854e-05</v>
       </c>
     </row>
@@ -16874,15 +17640,21 @@
         <v>0.0004306941242754933</v>
       </c>
       <c r="AK128" t="n">
+        <v>2.052630483791908e-06</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0.08435582822085891</v>
+      </c>
+      <c r="AM128" t="n">
         <v>1180.963111990383</v>
       </c>
-      <c r="AL128" t="n">
+      <c r="AN128" t="n">
         <v>3.961141249690548</v>
       </c>
-      <c r="AM128" t="n">
+      <c r="AO128" t="n">
         <v>3.771874027135714</v>
       </c>
-      <c r="AN128" t="n">
+      <c r="AP128" t="n">
         <v>0.0007638036809815952</v>
       </c>
     </row>
@@ -17002,15 +17774,21 @@
         <v>0.0004306941242754933</v>
       </c>
       <c r="AK129" t="n">
+        <v>1.979756028746041e-06</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>0.08136094674556214</v>
+      </c>
+      <c r="AM129" t="n">
         <v>1180.926835457534</v>
       </c>
-      <c r="AL129" t="n">
+      <c r="AN129" t="n">
         <v>3.961141249690548</v>
       </c>
-      <c r="AM129" t="n">
+      <c r="AO129" t="n">
         <v>3.780387046274697</v>
       </c>
-      <c r="AN129" t="n">
+      <c r="AP129" t="n">
         <v>1.183431952662722e-05</v>
       </c>
     </row>
@@ -17130,15 +17908,21 @@
         <v>0.0004306941242754933</v>
       </c>
       <c r="AK130" t="n">
+        <v>2.013513152606304e-06</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0.08274824473420261</v>
+      </c>
+      <c r="AM130" t="n">
         <v>1180.929585707569</v>
       </c>
-      <c r="AL130" t="n">
+      <c r="AN130" t="n">
         <v>3.961141249690548</v>
       </c>
-      <c r="AM130" t="n">
+      <c r="AO130" t="n">
         <v>3.776453248333941</v>
       </c>
-      <c r="AN130" t="n">
+      <c r="AP130" t="n">
         <v>0.000749247743229689</v>
       </c>
     </row>
@@ -17258,15 +18042,21 @@
         <v>0.0004306941242754933</v>
       </c>
       <c r="AK131" t="n">
+        <v>1.962338820282e-06</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>0.08064516129032258</v>
+      </c>
+      <c r="AM131" t="n">
         <v>1180.916391262796</v>
       </c>
-      <c r="AL131" t="n">
+      <c r="AN131" t="n">
         <v>3.961141249690548</v>
       </c>
-      <c r="AM131" t="n">
+      <c r="AO131" t="n">
         <v>3.78240730903006</v>
       </c>
-      <c r="AN131" t="n">
+      <c r="AP131" t="n">
         <v>0.003193548387096774</v>
       </c>
     </row>
@@ -17386,15 +18176,21 @@
         <v>0.0004306941242754933</v>
       </c>
       <c r="AK132" t="n">
+        <v>1.973916040460655e-06</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0.08112094395280237</v>
+      </c>
+      <c r="AM132" t="n">
         <v>1180.903957732461</v>
       </c>
-      <c r="AL132" t="n">
+      <c r="AN132" t="n">
         <v>3.961141249690548</v>
       </c>
-      <c r="AM132" t="n">
+      <c r="AO132" t="n">
         <v>3.781062184148229</v>
       </c>
-      <c r="AN132" t="n">
+      <c r="AP132" t="n">
         <v>0.003212389380530974</v>
       </c>
     </row>
@@ -17514,15 +18310,21 @@
         <v>-5.200256684232078e-05</v>
       </c>
       <c r="AK133" t="n">
+        <v>-1.465467815593975e-08</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>-0.01330128205128205</v>
+      </c>
+      <c r="AM133" t="n">
         <v>1147.80180341665</v>
       </c>
-      <c r="AL133" t="n">
+      <c r="AN133" t="n">
         <v>3.961141249690548</v>
       </c>
-      <c r="AM133" t="n">
+      <c r="AO133" t="n">
         <v>3.755385814738139</v>
       </c>
-      <c r="AN133" t="n">
+      <c r="AP133" t="n">
         <v>3.205128205128205e-05</v>
       </c>
     </row>
@@ -17642,15 +18444,21 @@
         <v>-5.200256684232078e-05</v>
       </c>
       <c r="AK134" t="n">
+        <v>-1.465467815593975e-08</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>-0.01330128205128205</v>
+      </c>
+      <c r="AM134" t="n">
         <v>1149.613089065766</v>
       </c>
-      <c r="AL134" t="n">
+      <c r="AN134" t="n">
         <v>3.961141249690548</v>
       </c>
-      <c r="AM134" t="n">
+      <c r="AO134" t="n">
         <v>3.755699071946919</v>
       </c>
-      <c r="AN134" t="n">
+      <c r="AP134" t="n">
         <v>3.205128205128205e-05</v>
       </c>
     </row>
@@ -17770,15 +18578,21 @@
         <v>-5.200256684232078e-05</v>
       </c>
       <c r="AK135" t="n">
+        <v>-1.470179930756657e-08</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>-0.01334405144694534</v>
+      </c>
+      <c r="AM135" t="n">
         <v>1149.672247583789</v>
       </c>
-      <c r="AL135" t="n">
+      <c r="AN135" t="n">
         <v>3.961141249690548</v>
       </c>
-      <c r="AM135" t="n">
+      <c r="AO135" t="n">
         <v>3.754866559590258</v>
       </c>
-      <c r="AN135" t="n">
+      <c r="AP135" t="n">
         <v>1.286173633440515e-05</v>
       </c>
     </row>
@@ -17898,15 +18712,21 @@
         <v>-5.200256684232078e-05</v>
       </c>
       <c r="AK136" t="n">
+        <v>-1.465467815593975e-08</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>-0.01330128205128205</v>
+      </c>
+      <c r="AM136" t="n">
         <v>1159.009133370553</v>
       </c>
-      <c r="AL136" t="n">
+      <c r="AN136" t="n">
         <v>3.961141249690548</v>
       </c>
-      <c r="AM136" t="n">
+      <c r="AO136" t="n">
         <v>3.757308957807639</v>
       </c>
-      <c r="AN136" t="n">
+      <c r="AP136" t="n">
         <v>1.282051282051282e-05</v>
       </c>
     </row>
@@ -18026,15 +18846,21 @@
         <v>-5.200256684232078e-05</v>
       </c>
       <c r="AK137" t="n">
+        <v>-1.375274747813319e-08</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>-0.01248264692272096</v>
+      </c>
+      <c r="AM137" t="n">
         <v>1147.803921549611</v>
       </c>
-      <c r="AL137" t="n">
+      <c r="AN137" t="n">
         <v>3.961141249690548</v>
       </c>
-      <c r="AM137" t="n">
+      <c r="AO137" t="n">
         <v>3.771379958824801</v>
       </c>
-      <c r="AN137" t="n">
+      <c r="AP137" t="n">
         <v>0.0007489588153632578</v>
       </c>
     </row>
@@ -18154,15 +18980,21 @@
         <v>-5.200256684232078e-05</v>
       </c>
       <c r="AK138" t="n">
+        <v>-1.470179930756657e-08</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>-0.01334405144694534</v>
+      </c>
+      <c r="AM138" t="n">
         <v>1148.414937890795</v>
       </c>
-      <c r="AL138" t="n">
+      <c r="AN138" t="n">
         <v>3.961141249690548</v>
       </c>
-      <c r="AM138" t="n">
+      <c r="AO138" t="n">
         <v>3.754648377193014</v>
       </c>
-      <c r="AN138" t="n">
+      <c r="AP138" t="n">
         <v>0.0008006430868167203</v>
       </c>
     </row>
@@ -18282,15 +19114,21 @@
         <v>-5.200256684232078e-05</v>
       </c>
       <c r="AK139" t="n">
+        <v>-1.583923643644297e-08</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>-0.01437644341801386</v>
+      </c>
+      <c r="AM139" t="n">
         <v>1151.361465687147</v>
       </c>
-      <c r="AL139" t="n">
+      <c r="AN139" t="n">
         <v>3.961141249690548</v>
       </c>
-      <c r="AM139" t="n">
+      <c r="AO139" t="n">
         <v>3.734602491740909</v>
       </c>
-      <c r="AN139" t="n">
+      <c r="AP139" t="n">
         <v>0.0008625866050808314</v>
       </c>
     </row>
@@ -18410,15 +19248,21 @@
         <v>-5.200256684232078e-05</v>
       </c>
       <c r="AK140" t="n">
+        <v>-1.446917590080128e-08</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>-0.01313291139240506</v>
+      </c>
+      <c r="AM140" t="n">
         <v>1152.652690646451</v>
       </c>
-      <c r="AL140" t="n">
+      <c r="AN140" t="n">
         <v>3.961141249690548</v>
       </c>
-      <c r="AM140" t="n">
+      <c r="AO140" t="n">
         <v>3.759524271496536</v>
       </c>
-      <c r="AN140" t="n">
+      <c r="AP140" t="n">
         <v>3.164556962025316e-05</v>
       </c>
     </row>
@@ -18538,15 +19382,21 @@
         <v>-5.200256684232078e-05</v>
       </c>
       <c r="AK141" t="n">
+        <v>-1.385533207470668e-08</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>-0.01257575757575758</v>
+      </c>
+      <c r="AM141" t="n">
         <v>1148.570663555671</v>
       </c>
-      <c r="AL141" t="n">
+      <c r="AN141" t="n">
         <v>3.961141249690548</v>
       </c>
-      <c r="AM141" t="n">
+      <c r="AO141" t="n">
         <v>3.76970045191429</v>
       </c>
-      <c r="AN141" t="n">
+      <c r="AP141" t="n">
         <v>0.0007545454545454547</v>
       </c>
     </row>
@@ -18666,15 +19516,21 @@
         <v>-5.200256684232078e-05</v>
       </c>
       <c r="AK142" t="n">
+        <v>-1.379263826441389e-08</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>-0.01251885369532428</v>
+      </c>
+      <c r="AM142" t="n">
         <v>1148.690902084174</v>
       </c>
-      <c r="AL142" t="n">
+      <c r="AN142" t="n">
         <v>3.961141249690548</v>
       </c>
-      <c r="AM142" t="n">
+      <c r="AO142" t="n">
         <v>3.77082170228662</v>
       </c>
-      <c r="AN142" t="n">
+      <c r="AP142" t="n">
         <v>0.0007511312217194572</v>
       </c>
     </row>
@@ -18794,15 +19650,21 @@
         <v>-5.200256684232078e-05</v>
       </c>
       <c r="AK143" t="n">
+        <v>-1.364853607359165e-08</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>-0.01238805970149254</v>
+      </c>
+      <c r="AM143" t="n">
         <v>1148.529896098098</v>
       </c>
-      <c r="AL143" t="n">
+      <c r="AN143" t="n">
         <v>3.961141249690548</v>
       </c>
-      <c r="AM143" t="n">
+      <c r="AO143" t="n">
         <v>3.773322928590142</v>
       </c>
-      <c r="AN143" t="n">
+      <c r="AP143" t="n">
         <v>0.0007432835820895523</v>
       </c>
     </row>
@@ -18922,15 +19784,21 @@
         <v>5.386666955660741e-05</v>
       </c>
       <c r="AK144" t="n">
+        <v>1.264216816705672e-07</v>
+      </c>
+      <c r="AL144" t="n">
+        <v>0.04154078549848943</v>
+      </c>
+      <c r="AM144" t="n">
         <v>1180.828584941382</v>
       </c>
-      <c r="AL144" t="n">
+      <c r="AN144" t="n">
         <v>3.961141249690548</v>
       </c>
-      <c r="AM144" t="n">
+      <c r="AO144" t="n">
         <v>3.775489519416669</v>
       </c>
-      <c r="AN144" t="n">
+      <c r="AP144" t="n">
         <v>3.021148036253776e-05</v>
       </c>
     </row>
@@ -19050,15 +19918,21 @@
         <v>5.386666955660741e-05</v>
       </c>
       <c r="AK145" t="n">
+        <v>1.238034811625969e-07</v>
+      </c>
+      <c r="AL145" t="n">
+        <v>0.04068047337278107</v>
+      </c>
+      <c r="AM145" t="n">
         <v>1180.830506228175</v>
       </c>
-      <c r="AL145" t="n">
+      <c r="AN145" t="n">
         <v>3.961141249690548</v>
       </c>
-      <c r="AM145" t="n">
+      <c r="AO145" t="n">
         <v>3.780372728833979</v>
       </c>
-      <c r="AN145" t="n">
+      <c r="AP145" t="n">
         <v>2.958579881656804e-05</v>
       </c>
     </row>
@@ -19178,15 +20052,21 @@
         <v>5.386666955660741e-05</v>
       </c>
       <c r="AK146" t="n">
+        <v>1.249121690536052e-07</v>
+      </c>
+      <c r="AL146" t="n">
+        <v>0.04104477611940299</v>
+      </c>
+      <c r="AM146" t="n">
         <v>1180.825066527863</v>
       </c>
-      <c r="AL146" t="n">
+      <c r="AN146" t="n">
         <v>3.961141249690548</v>
       </c>
-      <c r="AM146" t="n">
+      <c r="AO146" t="n">
         <v>3.778308078079982</v>
       </c>
-      <c r="AN146" t="n">
+      <c r="AP146" t="n">
         <v>1.194029850746269e-05</v>
       </c>
     </row>
@@ -19306,15 +20186,21 @@
         <v>5.386666955660741e-05</v>
       </c>
       <c r="AK147" t="n">
+        <v>1.223554872308706e-07</v>
+      </c>
+      <c r="AL147" t="n">
+        <v>0.0402046783625731</v>
+      </c>
+      <c r="AM147" t="n">
         <v>1180.828859338532</v>
       </c>
-      <c r="AL147" t="n">
+      <c r="AN147" t="n">
         <v>3.961141249690548</v>
       </c>
-      <c r="AM147" t="n">
+      <c r="AO147" t="n">
         <v>3.783059326248336</v>
       </c>
-      <c r="AN147" t="n">
+      <c r="AP147" t="n">
         <v>1.169590643274854e-05</v>
       </c>
     </row>
@@ -19434,15 +20320,21 @@
         <v>5.386666955660741e-05</v>
       </c>
       <c r="AK148" t="n">
+        <v>1.234382791532677e-07</v>
+      </c>
+      <c r="AL148" t="n">
+        <v>0.04056047197640118</v>
+      </c>
+      <c r="AM148" t="n">
         <v>1180.826608610277</v>
       </c>
-      <c r="AL148" t="n">
+      <c r="AN148" t="n">
         <v>3.961141249690548</v>
       </c>
-      <c r="AM148" t="n">
+      <c r="AO148" t="n">
         <v>3.781050729119022</v>
       </c>
-      <c r="AN148" t="n">
+      <c r="AP148" t="n">
         <v>0.0007345132743362833</v>
       </c>
     </row>
@@ -19562,15 +20454,21 @@
         <v>5.386666955660741e-05</v>
       </c>
       <c r="AK149" t="n">
+        <v>1.435525785007126e-07</v>
+      </c>
+      <c r="AL149" t="n">
+        <v>0.04716981132075472</v>
+      </c>
+      <c r="AM149" t="n">
         <v>1180.840899819285</v>
       </c>
-      <c r="AL149" t="n">
+      <c r="AN149" t="n">
         <v>3.961141249690548</v>
       </c>
-      <c r="AM149" t="n">
+      <c r="AO149" t="n">
         <v>3.742795426748617</v>
       </c>
-      <c r="AN149" t="n">
+      <c r="AP149" t="n">
         <v>0.0008542024013722128</v>
       </c>
     </row>
@@ -19690,15 +20588,21 @@
         <v>5.386666955660741e-05</v>
       </c>
       <c r="AK150" t="n">
+        <v>1.404213980971736e-07</v>
+      </c>
+      <c r="AL150" t="n">
+        <v>0.04614093959731544</v>
+      </c>
+      <c r="AM150" t="n">
         <v>1180.848074367425</v>
       </c>
-      <c r="AL150" t="n">
+      <c r="AN150" t="n">
         <v>3.961141249690548</v>
       </c>
-      <c r="AM150" t="n">
+      <c r="AO150" t="n">
         <v>3.748866029889523</v>
       </c>
-      <c r="AN150" t="n">
+      <c r="AP150" t="n">
         <v>0.003654362416107383</v>
       </c>
     </row>
@@ -19818,15 +20722,21 @@
         <v>5.386666955660741e-05</v>
       </c>
       <c r="AK151" t="n">
+        <v>1.268047776756295e-07</v>
+      </c>
+      <c r="AL151" t="n">
+        <v>0.04166666666666667</v>
+      </c>
+      <c r="AM151" t="n">
         <v>1180.828845592745</v>
       </c>
-      <c r="AL151" t="n">
+      <c r="AN151" t="n">
         <v>3.961141249690548</v>
       </c>
-      <c r="AM151" t="n">
+      <c r="AO151" t="n">
         <v>3.77477244941778</v>
       </c>
-      <c r="AN151" t="n">
+      <c r="AP151" t="n">
         <v>3.03030303030303e-05</v>
       </c>
     </row>
@@ -19946,15 +20856,21 @@
         <v>5.386666955660741e-05</v>
       </c>
       <c r="AK152" t="n">
+        <v>1.262310004010792e-07</v>
+      </c>
+      <c r="AL152" t="n">
+        <v>0.04147812971342384</v>
+      </c>
+      <c r="AM152" t="n">
         <v>1180.829749237871</v>
       </c>
-      <c r="AL152" t="n">
+      <c r="AN152" t="n">
         <v>3.961141249690548</v>
       </c>
-      <c r="AM152" t="n">
+      <c r="AO152" t="n">
         <v>3.775846379516666</v>
       </c>
-      <c r="AN152" t="n">
+      <c r="AP152" t="n">
         <v>0.003285067873303168</v>
       </c>
     </row>
@@ -20074,15 +20990,21 @@
         <v>7.552776175644405e-05</v>
       </c>
       <c r="AK153" t="n">
+        <v>1.002023413830669e-07</v>
+      </c>
+      <c r="AL153" t="n">
+        <v>0.01280864197530864</v>
+      </c>
+      <c r="AM153" t="n">
         <v>1228.51334408644</v>
       </c>
-      <c r="AL153" t="n">
+      <c r="AN153" t="n">
         <v>3.961141249690548</v>
       </c>
-      <c r="AM153" t="n">
+      <c r="AO153" t="n">
         <v>3.777548082803794</v>
       </c>
-      <c r="AN153" t="n">
+      <c r="AP153" t="n">
         <v>3.08641975308642e-05</v>
       </c>
     </row>
@@ -20202,15 +21124,21 @@
         <v>7.552776175644405e-05</v>
       </c>
       <c r="AK154" t="n">
+        <v>9.749416999433533e-08</v>
+      </c>
+      <c r="AL154" t="n">
+        <v>0.01246246246246246</v>
+      </c>
+      <c r="AM154" t="n">
         <v>1226.846543322034</v>
       </c>
-      <c r="AL154" t="n">
+      <c r="AN154" t="n">
         <v>3.961141249690548</v>
       </c>
-      <c r="AM154" t="n">
+      <c r="AO154" t="n">
         <v>3.783622520465595</v>
       </c>
-      <c r="AN154" t="n">
+      <c r="AP154" t="n">
         <v>3.003003003003003e-05</v>
       </c>
     </row>
@@ -20330,15 +21258,21 @@
         <v>7.552776175644405e-05</v>
       </c>
       <c r="AK155" t="n">
+        <v>9.928305384744239e-08</v>
+      </c>
+      <c r="AL155" t="n">
+        <v>0.01269113149847095</v>
+      </c>
+      <c r="AM155" t="n">
         <v>1231.33611629438</v>
       </c>
-      <c r="AL155" t="n">
+      <c r="AN155" t="n">
         <v>3.961141249690548</v>
       </c>
-      <c r="AM155" t="n">
+      <c r="AO155" t="n">
         <v>3.780099407973557</v>
       </c>
-      <c r="AN155" t="n">
+      <c r="AP155" t="n">
         <v>1.223241590214067e-05</v>
       </c>
     </row>
@@ -20458,15 +21392,21 @@
         <v>7.552776175644405e-05</v>
       </c>
       <c r="AK156" t="n">
+        <v>1.124672930997009e-07</v>
+      </c>
+      <c r="AL156" t="n">
+        <v>0.01437644341801386</v>
+      </c>
+      <c r="AM156" t="n">
         <v>1231.938615268019</v>
       </c>
-      <c r="AL156" t="n">
+      <c r="AN156" t="n">
         <v>3.961141249690548</v>
       </c>
-      <c r="AM156" t="n">
+      <c r="AO156" t="n">
         <v>3.748901496189908</v>
       </c>
-      <c r="AN156" t="n">
+      <c r="AP156" t="n">
         <v>0.0008625866050808314</v>
       </c>
     </row>
@@ -20586,15 +21526,21 @@
         <v>7.552776175644405e-05</v>
       </c>
       <c r="AK157" t="n">
+        <v>9.492853394185282e-08</v>
+      </c>
+      <c r="AL157" t="n">
+        <v>0.01213450292397661</v>
+      </c>
+      <c r="AM157" t="n">
         <v>1227.218881993087</v>
       </c>
-      <c r="AL157" t="n">
+      <c r="AN157" t="n">
         <v>3.961141249690548</v>
       </c>
-      <c r="AM157" t="n">
+      <c r="AO157" t="n">
         <v>3.789606988459723</v>
       </c>
-      <c r="AN157" t="n">
+      <c r="AP157" t="n">
         <v>0.0007280701754385966</v>
       </c>
     </row>
@@ -20714,15 +21660,21 @@
         <v>7.552776175644405e-05</v>
       </c>
       <c r="AK158" t="n">
+        <v>1.033934987519543e-07</v>
+      </c>
+      <c r="AL158" t="n">
+        <v>0.01321656050955414</v>
+      </c>
+      <c r="AM158" t="n">
         <v>1229.995198520354</v>
       </c>
-      <c r="AL158" t="n">
+      <c r="AN158" t="n">
         <v>3.961141249690548</v>
       </c>
-      <c r="AM158" t="n">
+      <c r="AO158" t="n">
         <v>3.770269542710188</v>
       </c>
-      <c r="AN158" t="n">
+      <c r="AP158" t="n">
         <v>0.0007929936305732485</v>
       </c>
     </row>
@@ -20842,15 +21794,21 @@
         <v>7.552776175644405e-05</v>
       </c>
       <c r="AK159" t="n">
+        <v>9.928305384744239e-08</v>
+      </c>
+      <c r="AL159" t="n">
+        <v>0.01269113149847095</v>
+      </c>
+      <c r="AM159" t="n">
         <v>1230.059011289001</v>
       </c>
-      <c r="AL159" t="n">
+      <c r="AN159" t="n">
         <v>3.961141249690548</v>
       </c>
-      <c r="AM159" t="n">
+      <c r="AO159" t="n">
         <v>3.779916896369529</v>
       </c>
-      <c r="AN159" t="n">
+      <c r="AP159" t="n">
         <v>1.223241590214067e-05</v>
       </c>
     </row>
@@ -20970,15 +21928,21 @@
         <v>7.552776175644405e-05</v>
       </c>
       <c r="AK160" t="n">
+        <v>9.928305384744239e-08</v>
+      </c>
+      <c r="AL160" t="n">
+        <v>0.01269113149847095</v>
+      </c>
+      <c r="AM160" t="n">
         <v>1228.302991906604</v>
       </c>
-      <c r="AL160" t="n">
+      <c r="AN160" t="n">
         <v>3.961141249690548</v>
       </c>
-      <c r="AM160" t="n">
+      <c r="AO160" t="n">
         <v>3.779665343529674</v>
       </c>
-      <c r="AN160" t="n">
+      <c r="AP160" t="n">
         <v>0.000761467889908257</v>
       </c>
     </row>
@@ -21098,15 +22062,21 @@
         <v>7.552776175644405e-05</v>
       </c>
       <c r="AK161" t="n">
+        <v>1.011388118632825e-07</v>
+      </c>
+      <c r="AL161" t="n">
+        <v>0.01292834890965732</v>
+      </c>
+      <c r="AM161" t="n">
         <v>1229.575424305167</v>
       </c>
-      <c r="AL161" t="n">
+      <c r="AN161" t="n">
         <v>3.961141249690548</v>
       </c>
-      <c r="AM161" t="n">
+      <c r="AO161" t="n">
         <v>3.775509905263395</v>
       </c>
-      <c r="AN161" t="n">
+      <c r="AP161" t="n">
         <v>0.003392523364485983</v>
       </c>
     </row>
@@ -21226,15 +22196,21 @@
         <v>0.0001071936632371646</v>
       </c>
       <c r="AK162" t="n">
+        <v>1.057513674783038e-07</v>
+      </c>
+      <c r="AL162" t="n">
+        <v>0.01456140350877193</v>
+      </c>
+      <c r="AM162" t="n">
         <v>828.6305205655575</v>
       </c>
-      <c r="AL162" t="n">
+      <c r="AN162" t="n">
         <v>3.961141249690548</v>
       </c>
-      <c r="AM162" t="n">
+      <c r="AO162" t="n">
         <v>3.645982328171687</v>
       </c>
-      <c r="AN162" t="n">
+      <c r="AP162" t="n">
         <v>3.508771929824561e-05</v>
       </c>
     </row>
@@ -21354,15 +22330,21 @@
         <v>0.0001071936632371646</v>
       </c>
       <c r="AK163" t="n">
+        <v>1.004637991043886e-07</v>
+      </c>
+      <c r="AL163" t="n">
+        <v>0.01383333333333333</v>
+      </c>
+      <c r="AM163" t="n">
         <v>828.2512793456242</v>
       </c>
-      <c r="AL163" t="n">
+      <c r="AN163" t="n">
         <v>3.961141249690548</v>
       </c>
-      <c r="AM163" t="n">
+      <c r="AO163" t="n">
         <v>3.665544070147539</v>
       </c>
-      <c r="AN163" t="n">
+      <c r="AP163" t="n">
         <v>3.333333333333333e-05</v>
       </c>
     </row>
@@ -21482,15 +22464,21 @@
         <v>0.0001071936632371646</v>
       </c>
       <c r="AK164" t="n">
+        <v>1.00799798432497e-07</v>
+      </c>
+      <c r="AL164" t="n">
+        <v>0.01387959866220736</v>
+      </c>
+      <c r="AM164" t="n">
         <v>832.0889924597337</v>
       </c>
-      <c r="AL164" t="n">
+      <c r="AN164" t="n">
         <v>3.961141249690548</v>
       </c>
-      <c r="AM164" t="n">
+      <c r="AO164" t="n">
         <v>3.665599705739155</v>
       </c>
-      <c r="AN164" t="n">
+      <c r="AP164" t="n">
         <v>1.337792642140468e-05</v>
       </c>
     </row>
@@ -21610,15 +22598,21 @@
         <v>0.0001071936632371646</v>
       </c>
       <c r="AK165" t="n">
+        <v>1.00799798432497e-07</v>
+      </c>
+      <c r="AL165" t="n">
+        <v>0.01387959866220736</v>
+      </c>
+      <c r="AM165" t="n">
         <v>829.4343359205119</v>
       </c>
-      <c r="AL165" t="n">
+      <c r="AN165" t="n">
         <v>3.961141249690548</v>
       </c>
-      <c r="AM165" t="n">
+      <c r="AO165" t="n">
         <v>3.664702065375538</v>
       </c>
-      <c r="AN165" t="n">
+      <c r="AP165" t="n">
         <v>0.0008327759197324416</v>
       </c>
     </row>
@@ -21738,15 +22732,21 @@
         <v>0.0001071936632371646</v>
       </c>
       <c r="AK166" t="n">
+        <v>9.881685157808719e-08</v>
+      </c>
+      <c r="AL166" t="n">
+        <v>0.01360655737704918</v>
+      </c>
+      <c r="AM166" t="n">
         <v>828.5547354562499</v>
       </c>
-      <c r="AL166" t="n">
+      <c r="AN166" t="n">
         <v>3.961141249690548</v>
       </c>
-      <c r="AM166" t="n">
+      <c r="AO166" t="n">
         <v>3.671725469617342</v>
       </c>
-      <c r="AN166" t="n">
+      <c r="AP166" t="n">
         <v>1.311475409836066e-05</v>
       </c>
     </row>
@@ -21866,15 +22866,21 @@
         <v>0.0001071936632371646</v>
       </c>
       <c r="AK167" t="n">
+        <v>9.389140103213896e-08</v>
+      </c>
+      <c r="AL167" t="n">
+        <v>0.01292834890965732</v>
+      </c>
+      <c r="AM167" t="n">
         <v>827.897252642005</v>
       </c>
-      <c r="AL167" t="n">
+      <c r="AN167" t="n">
         <v>3.961141249690548</v>
       </c>
-      <c r="AM167" t="n">
+      <c r="AO167" t="n">
         <v>3.689536230738573</v>
       </c>
-      <c r="AN167" t="n">
+      <c r="AP167" t="n">
         <v>1.246105919003116e-05</v>
       </c>
     </row>
@@ -21994,15 +23000,21 @@
         <v>0.0001071936632371646</v>
       </c>
       <c r="AK168" t="n">
+        <v>9.160832745081033e-08</v>
+      </c>
+      <c r="AL168" t="n">
+        <v>0.01261398176291793</v>
+      </c>
+      <c r="AM168" t="n">
         <v>828.163121235263</v>
       </c>
-      <c r="AL168" t="n">
+      <c r="AN168" t="n">
         <v>3.961141249690548</v>
       </c>
-      <c r="AM168" t="n">
+      <c r="AO168" t="n">
         <v>3.697888139162671</v>
       </c>
-      <c r="AN168" t="n">
+      <c r="AP168" t="n">
         <v>3.03951367781155e-05</v>
       </c>
     </row>
@@ -22122,15 +23134,21 @@
         <v>0.0001071936632371646</v>
       </c>
       <c r="AK169" t="n">
+        <v>9.188762113206278e-08</v>
+      </c>
+      <c r="AL169" t="n">
+        <v>0.01265243902439024</v>
+      </c>
+      <c r="AM169" t="n">
         <v>828.1551992730772</v>
       </c>
-      <c r="AL169" t="n">
+      <c r="AN169" t="n">
         <v>3.961141249690548</v>
       </c>
-      <c r="AM169" t="n">
+      <c r="AO169" t="n">
         <v>3.696877184869867</v>
       </c>
-      <c r="AN169" t="n">
+      <c r="AP169" t="n">
         <v>1.219512195121951e-05</v>
       </c>
     </row>
@@ -22250,15 +23268,21 @@
         <v>0.0001071936632371646</v>
       </c>
       <c r="AK170" t="n">
+        <v>9.833324545290895e-08</v>
+      </c>
+      <c r="AL170" t="n">
+        <v>0.01353996737357259</v>
+      </c>
+      <c r="AM170" t="n">
         <v>828.6170928699888</v>
       </c>
-      <c r="AL170" t="n">
+      <c r="AN170" t="n">
         <v>3.961141249690548</v>
       </c>
-      <c r="AM170" t="n">
+      <c r="AO170" t="n">
         <v>3.67352587104391</v>
       </c>
-      <c r="AN170" t="n">
+      <c r="AP170" t="n">
         <v>1.305057096247961e-05</v>
       </c>
     </row>
@@ -22378,15 +23402,21 @@
         <v>0.0001071936632371646</v>
       </c>
       <c r="AK171" t="n">
+        <v>9.860132954629199e-08</v>
+      </c>
+      <c r="AL171" t="n">
+        <v>0.01357688113413304</v>
+      </c>
+      <c r="AM171" t="n">
         <v>827.9040043342827</v>
       </c>
-      <c r="AL171" t="n">
+      <c r="AN171" t="n">
         <v>3.961141249690548</v>
       </c>
-      <c r="AM171" t="n">
+      <c r="AO171" t="n">
         <v>3.672303364145292</v>
       </c>
-      <c r="AN171" t="n">
+      <c r="AP171" t="n">
         <v>1.308615049073064e-05</v>
       </c>
     </row>
@@ -22506,15 +23536,21 @@
         <v>0</v>
       </c>
       <c r="AK172" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL172" t="n">
+        <v>0.01231454005934718</v>
+      </c>
+      <c r="AM172" t="n">
         <v>1000</v>
       </c>
-      <c r="AL172" t="n">
+      <c r="AN172" t="n">
         <v>3.961141249690548</v>
       </c>
-      <c r="AM172" t="n">
+      <c r="AO172" t="n">
         <v>3.748022771196685</v>
       </c>
-      <c r="AN172" t="n">
+      <c r="AP172" t="n">
         <v>2.967359050445104e-05</v>
       </c>
     </row>
@@ -22634,15 +23670,21 @@
         <v>0</v>
       </c>
       <c r="AK173" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL173" t="n">
+        <v>0.01227810650887574</v>
+      </c>
+      <c r="AM173" t="n">
         <v>1000</v>
       </c>
-      <c r="AL173" t="n">
+      <c r="AN173" t="n">
         <v>3.961141249690548</v>
       </c>
-      <c r="AM173" t="n">
+      <c r="AO173" t="n">
         <v>3.748820384115742</v>
       </c>
-      <c r="AN173" t="n">
+      <c r="AP173" t="n">
         <v>1.183431952662722e-05</v>
       </c>
     </row>
@@ -22762,15 +23804,21 @@
         <v>0</v>
       </c>
       <c r="AK174" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL174" t="n">
+        <v>0.01261398176291793</v>
+      </c>
+      <c r="AM174" t="n">
         <v>1000</v>
       </c>
-      <c r="AL174" t="n">
+      <c r="AN174" t="n">
         <v>3.961141249690548</v>
       </c>
-      <c r="AM174" t="n">
+      <c r="AO174" t="n">
         <v>3.741441048117355</v>
       </c>
-      <c r="AN174" t="n">
+      <c r="AP174" t="n">
         <v>0.0007568389057750761</v>
       </c>
     </row>
@@ -22890,15 +23938,21 @@
         <v>0</v>
       </c>
       <c r="AK175" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL175" t="n">
+        <v>0.01261398176291793</v>
+      </c>
+      <c r="AM175" t="n">
         <v>1000</v>
       </c>
-      <c r="AL175" t="n">
+      <c r="AN175" t="n">
         <v>3.961141249690548</v>
       </c>
-      <c r="AM175" t="n">
+      <c r="AO175" t="n">
         <v>3.741441048117355</v>
       </c>
-      <c r="AN175" t="n">
+      <c r="AP175" t="n">
         <v>0.003310030395136779</v>
       </c>
     </row>
@@ -23018,15 +24072,21 @@
         <v>0</v>
       </c>
       <c r="AK176" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL176" t="n">
+        <v>0.01213450292397661</v>
+      </c>
+      <c r="AM176" t="n">
         <v>1000</v>
       </c>
-      <c r="AL176" t="n">
+      <c r="AN176" t="n">
         <v>3.961141249690548</v>
       </c>
-      <c r="AM176" t="n">
+      <c r="AO176" t="n">
         <v>3.751957355084721</v>
       </c>
-      <c r="AN176" t="n">
+      <c r="AP176" t="n">
         <v>0.0007280701754385966</v>
       </c>
     </row>
@@ -23146,15 +24206,21 @@
         <v>0</v>
       </c>
       <c r="AK177" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL177" t="n">
+        <v>0.01189111747851003</v>
+      </c>
+      <c r="AM177" t="n">
         <v>1000</v>
       </c>
-      <c r="AL177" t="n">
+      <c r="AN177" t="n">
         <v>3.961141249690548</v>
       </c>
-      <c r="AM177" t="n">
+      <c r="AO177" t="n">
         <v>3.757248842555899</v>
       </c>
-      <c r="AN177" t="n">
+      <c r="AP177" t="n">
         <v>1.146131805157593e-05</v>
       </c>
     </row>
@@ -23274,15 +24340,21 @@
         <v>0</v>
       </c>
       <c r="AK178" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL178" t="n">
+        <v>0.01189111747851003</v>
+      </c>
+      <c r="AM178" t="n">
         <v>1000</v>
       </c>
-      <c r="AL178" t="n">
+      <c r="AN178" t="n">
         <v>3.961141249690548</v>
       </c>
-      <c r="AM178" t="n">
+      <c r="AO178" t="n">
         <v>3.757248842555899</v>
       </c>
-      <c r="AN178" t="n">
+      <c r="AP178" t="n">
         <v>0.0007134670487106018</v>
       </c>
     </row>
@@ -23402,15 +24474,21 @@
         <v>0</v>
       </c>
       <c r="AK179" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL179" t="n">
+        <v>0.01292834890965732</v>
+      </c>
+      <c r="AM179" t="n">
         <v>1000</v>
       </c>
-      <c r="AL179" t="n">
+      <c r="AN179" t="n">
         <v>3.961141249690548</v>
       </c>
-      <c r="AM179" t="n">
+      <c r="AO179" t="n">
         <v>3.734481709985246</v>
       </c>
-      <c r="AN179" t="n">
+      <c r="AP179" t="n">
         <v>0.0007757009345794396</v>
       </c>
     </row>
@@ -23530,15 +24608,21 @@
         <v>-1.049890220956849e-05</v>
       </c>
       <c r="AK180" t="n">
+        <v>-7.770224164260761e-09</v>
+      </c>
+      <c r="AL180" t="n">
+        <v>-0.01571969696969697</v>
+      </c>
+      <c r="AM180" t="n">
         <v>1162.930224384304</v>
       </c>
-      <c r="AL180" t="n">
+      <c r="AN180" t="n">
         <v>3.961141249690548</v>
       </c>
-      <c r="AM180" t="n">
+      <c r="AO180" t="n">
         <v>3.709617956922959</v>
       </c>
-      <c r="AN180" t="n">
+      <c r="AP180" t="n">
         <v>3.787878787878788e-05</v>
       </c>
     </row>
@@ -23658,15 +24742,21 @@
         <v>-1.049890220956849e-05</v>
       </c>
       <c r="AK181" t="n">
+        <v>-7.486639340747597e-09</v>
+      </c>
+      <c r="AL181" t="n">
+        <v>-0.01514598540145985</v>
+      </c>
+      <c r="AM181" t="n">
         <v>1162.565791898417</v>
       </c>
-      <c r="AL181" t="n">
+      <c r="AN181" t="n">
         <v>3.961141249690548</v>
       </c>
-      <c r="AM181" t="n">
+      <c r="AO181" t="n">
         <v>3.721230506094791</v>
       </c>
-      <c r="AN181" t="n">
+      <c r="AP181" t="n">
         <v>1.45985401459854e-05</v>
       </c>
     </row>
@@ -23786,15 +24876,21 @@
         <v>-1.049890220956849e-05</v>
       </c>
       <c r="AK182" t="n">
+        <v>-7.073583377120142e-09</v>
+      </c>
+      <c r="AL182" t="n">
+        <v>-0.01431034482758621</v>
+      </c>
+      <c r="AM182" t="n">
         <v>1164.217647877595</v>
       </c>
-      <c r="AL182" t="n">
+      <c r="AN182" t="n">
         <v>3.961141249690548</v>
       </c>
-      <c r="AM182" t="n">
+      <c r="AO182" t="n">
         <v>3.738327466697453</v>
       </c>
-      <c r="AN182" t="n">
+      <c r="AP182" t="n">
         <v>0.0008586206896551725</v>
       </c>
     </row>
@@ -23914,15 +25010,21 @@
         <v>-1.049890220956849e-05</v>
       </c>
       <c r="AK183" t="n">
+        <v>-7.147523273048226e-09</v>
+      </c>
+      <c r="AL183" t="n">
+        <v>-0.01445993031358885</v>
+      </c>
+      <c r="AM183" t="n">
         <v>1162.666103379995</v>
       </c>
-      <c r="AL183" t="n">
+      <c r="AN183" t="n">
         <v>3.961141249690548</v>
       </c>
-      <c r="AM183" t="n">
+      <c r="AO183" t="n">
         <v>3.73505625268597</v>
       </c>
-      <c r="AN183" t="n">
+      <c r="AP183" t="n">
         <v>0.003794425087108014</v>
       </c>
     </row>
@@ -24042,15 +25144,21 @@
         <v>-1.049890220956849e-05</v>
       </c>
       <c r="AK184" t="n">
+        <v>-7.625796205817253e-09</v>
+      </c>
+      <c r="AL184" t="n">
+        <v>-0.0154275092936803</v>
+      </c>
+      <c r="AM184" t="n">
         <v>1162.967242443242</v>
       </c>
-      <c r="AL184" t="n">
+      <c r="AN184" t="n">
         <v>3.961141249690548</v>
       </c>
-      <c r="AM184" t="n">
+      <c r="AO184" t="n">
         <v>3.715592230324373</v>
       </c>
-      <c r="AN184" t="n">
+      <c r="AP184" t="n">
         <v>1.486988847583643e-05</v>
       </c>
     </row>
@@ -24170,15 +25278,21 @@
         <v>-1.049890220956849e-05</v>
       </c>
       <c r="AK185" t="n">
+        <v>-6.390464733223807e-09</v>
+      </c>
+      <c r="AL185" t="n">
+        <v>-0.01292834890965732</v>
+      </c>
+      <c r="AM185" t="n">
         <v>1162.496770314802</v>
       </c>
-      <c r="AL185" t="n">
+      <c r="AN185" t="n">
         <v>3.961141249690548</v>
       </c>
-      <c r="AM185" t="n">
+      <c r="AO185" t="n">
         <v>3.765138359324784</v>
       </c>
-      <c r="AN185" t="n">
+      <c r="AP185" t="n">
         <v>3.115264797507789e-05</v>
       </c>
     </row>
@@ -24298,15 +25412,21 @@
         <v>-1.049890220956849e-05</v>
       </c>
       <c r="AK186" t="n">
+        <v>-6.235073493510156e-09</v>
+      </c>
+      <c r="AL186" t="n">
+        <v>-0.01261398176291793</v>
+      </c>
+      <c r="AM186" t="n">
         <v>1162.538306754294</v>
       </c>
-      <c r="AL186" t="n">
+      <c r="AN186" t="n">
         <v>3.961141249690548</v>
       </c>
-      <c r="AM186" t="n">
+      <c r="AO186" t="n">
         <v>3.771197218966782</v>
       </c>
-      <c r="AN186" t="n">
+      <c r="AP186" t="n">
         <v>3.03951367781155e-05</v>
       </c>
     </row>
@@ -24426,15 +25546,21 @@
         <v>1.26542967403936e-06</v>
       </c>
       <c r="AK187" t="n">
+        <v>9.045633779907923e-10</v>
+      </c>
+      <c r="AL187" t="n">
+        <v>0.01265243902439024</v>
+      </c>
+      <c r="AM187" t="n">
         <v>1181.618292043855</v>
       </c>
-      <c r="AL187" t="n">
+      <c r="AN187" t="n">
         <v>3.961141249690548</v>
       </c>
-      <c r="AM187" t="n">
+      <c r="AO187" t="n">
         <v>3.773444754580211</v>
       </c>
-      <c r="AN187" t="n">
+      <c r="AP187" t="n">
         <v>3.048780487804878e-05</v>
       </c>
     </row>
@@ -24554,15 +25680,21 @@
         <v>1.26542967403936e-06</v>
       </c>
       <c r="AK188" t="n">
+        <v>9.018139452309419e-10</v>
+      </c>
+      <c r="AL188" t="n">
+        <v>0.01261398176291793</v>
+      </c>
+      <c r="AM188" t="n">
         <v>1181.605458323518</v>
       </c>
-      <c r="AL188" t="n">
+      <c r="AN188" t="n">
         <v>3.961141249690548</v>
       </c>
-      <c r="AM188" t="n">
+      <c r="AO188" t="n">
         <v>3.774169558720175</v>
       </c>
-      <c r="AN188" t="n">
+      <c r="AP188" t="n">
         <v>1.21580547112462e-05</v>
       </c>
     </row>
@@ -24682,15 +25814,21 @@
         <v>1.26542967403936e-06</v>
       </c>
       <c r="AK189" t="n">
+        <v>9.479130606421081e-10</v>
+      </c>
+      <c r="AL189" t="n">
+        <v>0.01325878594249201</v>
+      </c>
+      <c r="AM189" t="n">
         <v>1181.613156209172</v>
       </c>
-      <c r="AL189" t="n">
+      <c r="AN189" t="n">
         <v>3.961141249690548</v>
       </c>
-      <c r="AM189" t="n">
+      <c r="AO189" t="n">
         <v>3.761896242929261</v>
       </c>
-      <c r="AN189" t="n">
+      <c r="AP189" t="n">
         <v>0.0007955271565495208</v>
       </c>
     </row>
@@ -24810,15 +25948,21 @@
         <v>1.26542967403936e-06</v>
       </c>
       <c r="AK190" t="n">
+        <v>8.936650240390961e-10</v>
+      </c>
+      <c r="AL190" t="n">
+        <v>0.0125</v>
+      </c>
+      <c r="AM190" t="n">
         <v>1181.61032271818</v>
       </c>
-      <c r="AL190" t="n">
+      <c r="AN190" t="n">
         <v>3.961141249690548</v>
       </c>
-      <c r="AM190" t="n">
+      <c r="AO190" t="n">
         <v>3.776320353641986</v>
       </c>
-      <c r="AN190" t="n">
+      <c r="AP190" t="n">
         <v>0.003280120481927711</v>
       </c>
     </row>
@@ -24938,15 +26082,21 @@
         <v>1.26542967403936e-06</v>
       </c>
       <c r="AK191" t="n">
+        <v>9.330087672357859e-10</v>
+      </c>
+      <c r="AL191" t="n">
+        <v>0.0130503144654088</v>
+      </c>
+      <c r="AM191" t="n">
         <v>1181.605816475638</v>
       </c>
-      <c r="AL191" t="n">
+      <c r="AN191" t="n">
         <v>3.961141249690548</v>
       </c>
-      <c r="AM191" t="n">
+      <c r="AO191" t="n">
         <v>3.765884002234684</v>
       </c>
-      <c r="AN191" t="n">
+      <c r="AP191" t="n">
         <v>3.144654088050314e-05</v>
       </c>
     </row>
@@ -25066,15 +26216,21 @@
         <v>1.26542967403936e-06</v>
       </c>
       <c r="AK192" t="n">
+        <v>9.27177462440562e-10</v>
+      </c>
+      <c r="AL192" t="n">
+        <v>0.01296875</v>
+      </c>
+      <c r="AM192" t="n">
         <v>1181.605036556104</v>
       </c>
-      <c r="AL192" t="n">
+      <c r="AN192" t="n">
         <v>3.961141249690548</v>
       </c>
-      <c r="AM192" t="n">
+      <c r="AO192" t="n">
         <v>3.76743927824613</v>
       </c>
-      <c r="AN192" t="n">
+      <c r="AP192" t="n">
         <v>1.25e-05</v>
       </c>
     </row>
@@ -25194,15 +26350,21 @@
         <v>1.26542967403936e-06</v>
       </c>
       <c r="AK193" t="n">
+        <v>9.045633779907923e-10</v>
+      </c>
+      <c r="AL193" t="n">
+        <v>0.01265243902439024</v>
+      </c>
+      <c r="AM193" t="n">
         <v>1181.604884807166</v>
       </c>
-      <c r="AL193" t="n">
+      <c r="AN193" t="n">
         <v>3.961141249690548</v>
       </c>
-      <c r="AM193" t="n">
+      <c r="AO193" t="n">
         <v>3.773442689451564</v>
       </c>
-      <c r="AN193" t="n">
+      <c r="AP193" t="n">
         <v>0.0007591463414634148</v>
       </c>
     </row>
@@ -25322,15 +26484,21 @@
         <v>1.26542967403936e-06</v>
       </c>
       <c r="AK194" t="n">
+        <v>9.418945650189837e-10</v>
+      </c>
+      <c r="AL194" t="n">
+        <v>0.01317460317460317</v>
+      </c>
+      <c r="AM194" t="n">
         <v>1181.606218924802</v>
       </c>
-      <c r="AL194" t="n">
+      <c r="AN194" t="n">
         <v>3.961141249690548</v>
       </c>
-      <c r="AM194" t="n">
+      <c r="AO194" t="n">
         <v>3.763508213277201</v>
       </c>
-      <c r="AN194" t="n">
+      <c r="AP194" t="n">
         <v>0.003457142857142857</v>
       </c>
     </row>
@@ -25450,15 +26618,21 @@
         <v>0.0003679703698917816</v>
       </c>
       <c r="AK195" t="n">
+        <v>1.737706312919478e-06</v>
+      </c>
+      <c r="AL195" t="n">
+        <v>0.08358662613981764</v>
+      </c>
+      <c r="AM195" t="n">
         <v>1182.309534134848</v>
       </c>
-      <c r="AL195" t="n">
+      <c r="AN195" t="n">
         <v>3.961141249690548</v>
       </c>
-      <c r="AM195" t="n">
+      <c r="AO195" t="n">
         <v>3.774277542302639</v>
       </c>
-      <c r="AN195" t="n">
+      <c r="AP195" t="n">
         <v>1.21580547112462e-05</v>
       </c>
     </row>
@@ -25578,15 +26752,21 @@
         <v>0.0003679703698917816</v>
       </c>
       <c r="AK196" t="n">
+        <v>1.743004198019842e-06</v>
+      </c>
+      <c r="AL196" t="n">
+        <v>0.08384146341463415</v>
+      </c>
+      <c r="AM196" t="n">
         <v>1182.042396353164</v>
       </c>
-      <c r="AL196" t="n">
+      <c r="AN196" t="n">
         <v>3.961141249690548</v>
       </c>
-      <c r="AM196" t="n">
+      <c r="AO196" t="n">
         <v>3.773510056387354</v>
       </c>
-      <c r="AN196" t="n">
+      <c r="AP196" t="n">
         <v>0.0007591463414634148</v>
       </c>
     </row>
@@ -25706,15 +26886,21 @@
         <v>0.0003679703698917816</v>
       </c>
       <c r="AK197" t="n">
+        <v>1.775482537113379e-06</v>
+      </c>
+      <c r="AL197" t="n">
+        <v>0.08540372670807453</v>
+      </c>
+      <c r="AM197" t="n">
         <v>1181.812102797456</v>
       </c>
-      <c r="AL197" t="n">
+      <c r="AN197" t="n">
         <v>3.961141249690548</v>
       </c>
-      <c r="AM197" t="n">
+      <c r="AO197" t="n">
         <v>3.769005038764909</v>
       </c>
-      <c r="AN197" t="n">
+      <c r="AP197" t="n">
         <v>0.003381987577639751</v>
       </c>
     </row>
@@ -25834,15 +27020,21 @@
         <v>0.0003679703698917816</v>
       </c>
       <c r="AK198" t="n">
+        <v>1.797815650787762e-06</v>
+      </c>
+      <c r="AL198" t="n">
+        <v>0.08647798742138366</v>
+      </c>
+      <c r="AM198" t="n">
         <v>1181.825212498651</v>
       </c>
-      <c r="AL198" t="n">
+      <c r="AN198" t="n">
         <v>3.961141249690548</v>
       </c>
-      <c r="AM198" t="n">
+      <c r="AO198" t="n">
         <v>3.765919099871435</v>
       </c>
-      <c r="AN198" t="n">
+      <c r="AP198" t="n">
         <v>3.144654088050314e-05</v>
       </c>
     </row>
@@ -25962,15 +27154,21 @@
         <v>0.0003679703698917816</v>
       </c>
       <c r="AK199" t="n">
+        <v>1.797815650787762e-06</v>
+      </c>
+      <c r="AL199" t="n">
+        <v>0.08647798742138366</v>
+      </c>
+      <c r="AM199" t="n">
         <v>1181.995373053187</v>
       </c>
-      <c r="AL199" t="n">
+      <c r="AN199" t="n">
         <v>3.961141249690548</v>
       </c>
-      <c r="AM199" t="n">
+      <c r="AO199" t="n">
         <v>3.765946312462994</v>
       </c>
-      <c r="AN199" t="n">
+      <c r="AP199" t="n">
         <v>3.144654088050314e-05</v>
       </c>
     </row>
@@ -26090,15 +27288,21 @@
         <v>0.0003679703698917816</v>
       </c>
       <c r="AK200" t="n">
+        <v>1.753697475308307e-06</v>
+      </c>
+      <c r="AL200" t="n">
+        <v>0.08435582822085891</v>
+      </c>
+      <c r="AM200" t="n">
         <v>1182.106331600524</v>
       </c>
-      <c r="AL200" t="n">
+      <c r="AN200" t="n">
         <v>3.961141249690548</v>
       </c>
-      <c r="AM200" t="n">
+      <c r="AO200" t="n">
         <v>3.772051468485949</v>
       </c>
-      <c r="AN200" t="n">
+      <c r="AP200" t="n">
         <v>0.0007638036809815952</v>
       </c>
     </row>
@@ -26218,15 +27422,21 @@
         <v>0</v>
       </c>
       <c r="AK201" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL201" t="n">
+        <v>0.01220588235294118</v>
+      </c>
+      <c r="AM201" t="n">
         <v>1000</v>
       </c>
-      <c r="AL201" t="n">
+      <c r="AN201" t="n">
         <v>1.980570624845274</v>
       </c>
-      <c r="AM201" t="n">
+      <c r="AO201" t="n">
         <v>1.946392312109065</v>
       </c>
-      <c r="AN201" t="n">
+      <c r="AP201" t="n">
         <v>1.176470588235294e-05</v>
       </c>
     </row>
@@ -26346,15 +27556,21 @@
         <v>0</v>
       </c>
       <c r="AK202" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL202" t="n">
+        <v>0.01231454005934718</v>
+      </c>
+      <c r="AM202" t="n">
         <v>1000</v>
       </c>
-      <c r="AL202" t="n">
+      <c r="AN202" t="n">
         <v>1.980570624845274</v>
       </c>
-      <c r="AM202" t="n">
+      <c r="AO202" t="n">
         <v>1.945976204262558</v>
       </c>
-      <c r="AN202" t="n">
+      <c r="AP202" t="n">
         <v>2.967359050445104e-05</v>
       </c>
     </row>
@@ -26474,15 +27690,21 @@
         <v>0</v>
       </c>
       <c r="AK203" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL203" t="n">
+        <v>0.01265243902439024</v>
+      </c>
+      <c r="AM203" t="n">
         <v>1000</v>
       </c>
-      <c r="AL203" t="n">
+      <c r="AN203" t="n">
         <v>1.980570624845274</v>
       </c>
-      <c r="AM203" t="n">
+      <c r="AO203" t="n">
         <v>1.944673090056523</v>
       </c>
-      <c r="AN203" t="n">
+      <c r="AP203" t="n">
         <v>0.0007591463414634148</v>
       </c>
     </row>
@@ -26602,15 +27824,21 @@
         <v>0</v>
       </c>
       <c r="AK204" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL204" t="n">
+        <v>0.0125</v>
+      </c>
+      <c r="AM204" t="n">
         <v>1000</v>
       </c>
-      <c r="AL204" t="n">
+      <c r="AN204" t="n">
         <v>1.980570624845274</v>
       </c>
-      <c r="AM204" t="n">
+      <c r="AO204" t="n">
         <v>1.945262675612751</v>
       </c>
-      <c r="AN204" t="n">
+      <c r="AP204" t="n">
         <v>1.204819277108434e-05</v>
       </c>
     </row>
@@ -26730,15 +27958,21 @@
         <v>0</v>
       </c>
       <c r="AK205" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL205" t="n">
+        <v>0.01238805970149254</v>
+      </c>
+      <c r="AM205" t="n">
         <v>1000</v>
       </c>
-      <c r="AL205" t="n">
+      <c r="AN205" t="n">
         <v>1.980570624845274</v>
       </c>
-      <c r="AM205" t="n">
+      <c r="AO205" t="n">
         <v>1.945693845931205</v>
       </c>
-      <c r="AN205" t="n">
+      <c r="AP205" t="n">
         <v>1.194029850746269e-05</v>
       </c>
     </row>
@@ -26858,15 +28092,21 @@
         <v>0</v>
       </c>
       <c r="AK206" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL206" t="n">
+        <v>0.01265243902439024</v>
+      </c>
+      <c r="AM206" t="n">
         <v>1000</v>
       </c>
-      <c r="AL206" t="n">
+      <c r="AN206" t="n">
         <v>1.980570624845274</v>
       </c>
-      <c r="AM206" t="n">
+      <c r="AO206" t="n">
         <v>1.944673090056523</v>
       </c>
-      <c r="AN206" t="n">
+      <c r="AP206" t="n">
         <v>0.0007591463414634148</v>
       </c>
     </row>
@@ -26986,15 +28226,21 @@
         <v>0</v>
       </c>
       <c r="AK207" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL207" t="n">
+        <v>0.01265243902439024</v>
+      </c>
+      <c r="AM207" t="n">
         <v>1000</v>
       </c>
-      <c r="AL207" t="n">
+      <c r="AN207" t="n">
         <v>1.980570624845274</v>
       </c>
-      <c r="AM207" t="n">
+      <c r="AO207" t="n">
         <v>1.944673090056523</v>
       </c>
-      <c r="AN207" t="n">
+      <c r="AP207" t="n">
         <v>1.219512195121951e-05</v>
       </c>
     </row>
@@ -27114,15 +28360,21 @@
         <v>0</v>
       </c>
       <c r="AK208" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL208" t="n">
+        <v>0.01209912536443149</v>
+      </c>
+      <c r="AM208" t="n">
         <v>1000</v>
       </c>
-      <c r="AL208" t="n">
+      <c r="AN208" t="n">
         <v>1.980570624845274</v>
       </c>
-      <c r="AM208" t="n">
+      <c r="AO208" t="n">
         <v>1.946799739592073</v>
       </c>
-      <c r="AN208" t="n">
+      <c r="AP208" t="n">
         <v>0.0007259475218658894</v>
       </c>
     </row>
@@ -27242,15 +28494,21 @@
         <v>0</v>
       </c>
       <c r="AK209" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL209" t="n">
+        <v>0.01209912536443149</v>
+      </c>
+      <c r="AM209" t="n">
         <v>1000</v>
       </c>
-      <c r="AL209" t="n">
+      <c r="AN209" t="n">
         <v>1.980570624845274</v>
       </c>
-      <c r="AM209" t="n">
+      <c r="AO209" t="n">
         <v>1.946799739592073</v>
       </c>
-      <c r="AN209" t="n">
+      <c r="AP209" t="n">
         <v>0.0007259475218658894</v>
       </c>
     </row>
@@ -27370,15 +28628,21 @@
         <v>-1.049890220956849e-05</v>
       </c>
       <c r="AK210" t="n">
+        <v>-7.073583377120142e-09</v>
+      </c>
+      <c r="AL210" t="n">
+        <v>-0.01431034482758621</v>
+      </c>
+      <c r="AM210" t="n">
         <v>1164.007111686684</v>
       </c>
-      <c r="AL210" t="n">
+      <c r="AN210" t="n">
         <v>1.980570624845274</v>
       </c>
-      <c r="AM210" t="n">
+      <c r="AO210" t="n">
         <v>1.944035514106814</v>
       </c>
-      <c r="AN210" t="n">
+      <c r="AP210" t="n">
         <v>1.379310344827586e-05</v>
       </c>
     </row>
@@ -27498,15 +28762,21 @@
         <v>-1.049890220956849e-05</v>
       </c>
       <c r="AK211" t="n">
+        <v>-7.049275530463371e-09</v>
+      </c>
+      <c r="AL211" t="n">
+        <v>-0.01426116838487972</v>
+      </c>
+      <c r="AM211" t="n">
         <v>1164.250430180415</v>
       </c>
-      <c r="AL211" t="n">
+      <c r="AN211" t="n">
         <v>1.980570624845274</v>
       </c>
-      <c r="AM211" t="n">
+      <c r="AO211" t="n">
         <v>1.944215583665192</v>
       </c>
-      <c r="AN211" t="n">
+      <c r="AP211" t="n">
         <v>0.0008556701030927837</v>
       </c>
     </row>
@@ -27626,15 +28896,21 @@
         <v>-1.049890220956849e-05</v>
       </c>
       <c r="AK212" t="n">
+        <v>-7.352470176934914e-09</v>
+      </c>
+      <c r="AL212" t="n">
+        <v>-0.01487455197132617</v>
+      </c>
+      <c r="AM212" t="n">
         <v>1163.702317805029</v>
       </c>
-      <c r="AL212" t="n">
+      <c r="AN212" t="n">
         <v>1.980570624845274</v>
       </c>
-      <c r="AM212" t="n">
+      <c r="AO212" t="n">
         <v>1.94202953129187</v>
       </c>
-      <c r="AN212" t="n">
+      <c r="AP212" t="n">
         <v>3.584229390681004e-05</v>
       </c>
     </row>
@@ -27754,15 +29030,21 @@
         <v>-1.049890220956849e-05</v>
       </c>
       <c r="AK213" t="n">
+        <v>-7.514062928076342e-09</v>
+      </c>
+      <c r="AL213" t="n">
+        <v>-0.0152014652014652</v>
+      </c>
+      <c r="AM213" t="n">
         <v>1165.230299450247</v>
       </c>
-      <c r="AL213" t="n">
+      <c r="AN213" t="n">
         <v>1.980570624845274</v>
       </c>
-      <c r="AM213" t="n">
+      <c r="AO213" t="n">
         <v>1.940910512126237</v>
       </c>
-      <c r="AN213" t="n">
+      <c r="AP213" t="n">
         <v>1.465201465201465e-05</v>
       </c>
     </row>
@@ -27882,15 +29164,21 @@
         <v>-1.049890220956849e-05</v>
       </c>
       <c r="AK214" t="n">
+        <v>-7.073583377120142e-09</v>
+      </c>
+      <c r="AL214" t="n">
+        <v>-0.01431034482758621</v>
+      </c>
+      <c r="AM214" t="n">
         <v>1163.93693295638</v>
       </c>
-      <c r="AL214" t="n">
+      <c r="AN214" t="n">
         <v>1.980570624845274</v>
       </c>
-      <c r="AM214" t="n">
+      <c r="AO214" t="n">
         <v>1.94403332178747</v>
       </c>
-      <c r="AN214" t="n">
+      <c r="AP214" t="n">
         <v>0.0008586206896551725</v>
       </c>
     </row>
@@ -28010,15 +29298,21 @@
         <v>-1.049890220956849e-05</v>
       </c>
       <c r="AK215" t="n">
+        <v>-7.223025279453665e-09</v>
+      </c>
+      <c r="AL215" t="n">
+        <v>-0.01461267605633803</v>
+      </c>
+      <c r="AM215" t="n">
         <v>1163.628924568694</v>
       </c>
-      <c r="AL215" t="n">
+      <c r="AN215" t="n">
         <v>1.980570624845274</v>
       </c>
-      <c r="AM215" t="n">
+      <c r="AO215" t="n">
         <v>1.942957647156456</v>
       </c>
-      <c r="AN215" t="n">
+      <c r="AP215" t="n">
         <v>1.408450704225352e-05</v>
       </c>
     </row>
@@ -28138,15 +29432,21 @@
         <v>1.26542967403936e-06</v>
       </c>
       <c r="AK216" t="n">
+        <v>9.418945650189837e-10</v>
+      </c>
+      <c r="AL216" t="n">
+        <v>0.01317460317460317</v>
+      </c>
+      <c r="AM216" t="n">
         <v>1181.61595799572</v>
       </c>
-      <c r="AL216" t="n">
+      <c r="AN216" t="n">
         <v>1.980570624845274</v>
       </c>
-      <c r="AM216" t="n">
+      <c r="AO216" t="n">
         <v>1.948443423403061</v>
       </c>
-      <c r="AN216" t="n">
+      <c r="AP216" t="n">
         <v>1.26984126984127e-05</v>
       </c>
     </row>
@@ -28266,15 +29566,21 @@
         <v>1.26542967403936e-06</v>
       </c>
       <c r="AK217" t="n">
+        <v>1.026632484363252e-09</v>
+      </c>
+      <c r="AL217" t="n">
+        <v>0.0143598615916955</v>
+      </c>
+      <c r="AM217" t="n">
         <v>1181.609420398149</v>
       </c>
-      <c r="AL217" t="n">
+      <c r="AN217" t="n">
         <v>1.980570624845274</v>
       </c>
-      <c r="AM217" t="n">
+      <c r="AO217" t="n">
         <v>1.944405863540963</v>
       </c>
-      <c r="AN217" t="n">
+      <c r="AP217" t="n">
         <v>0.0008615916955017302</v>
       </c>
     </row>
@@ -28394,15 +29700,21 @@
         <v>1.26542967403936e-06</v>
       </c>
       <c r="AK218" t="n">
+        <v>9.479130606421081e-10</v>
+      </c>
+      <c r="AL218" t="n">
+        <v>0.01325878594249201</v>
+      </c>
+      <c r="AM218" t="n">
         <v>1181.609448550224</v>
       </c>
-      <c r="AL218" t="n">
+      <c r="AN218" t="n">
         <v>1.980570624845274</v>
       </c>
-      <c r="AM218" t="n">
+      <c r="AO218" t="n">
         <v>1.948161078445132</v>
       </c>
-      <c r="AN218" t="n">
+      <c r="AP218" t="n">
         <v>3.194888178913738e-05</v>
       </c>
     </row>
@@ -28522,15 +29834,21 @@
         <v>1.26542967403936e-06</v>
       </c>
       <c r="AK219" t="n">
+        <v>1.033786717703763e-09</v>
+      </c>
+      <c r="AL219" t="n">
+        <v>0.01445993031358885</v>
+      </c>
+      <c r="AM219" t="n">
         <v>1181.607601888355</v>
       </c>
-      <c r="AL219" t="n">
+      <c r="AN219" t="n">
         <v>1.980570624845274</v>
       </c>
-      <c r="AM219" t="n">
+      <c r="AO219" t="n">
         <v>1.944058674785871</v>
       </c>
-      <c r="AN219" t="n">
+      <c r="AP219" t="n">
         <v>0.003794425087108014</v>
       </c>
     </row>
@@ -28650,15 +29968,21 @@
         <v>1.26542967403936e-06</v>
       </c>
       <c r="AK220" t="n">
+        <v>1.093477105581007e-09</v>
+      </c>
+      <c r="AL220" t="n">
+        <v>0.0152948402948403</v>
+      </c>
+      <c r="AM220" t="n">
         <v>1181.609730552862</v>
       </c>
-      <c r="AL220" t="n">
+      <c r="AN220" t="n">
         <v>1.980570624845274</v>
       </c>
-      <c r="AM220" t="n">
+      <c r="AO220" t="n">
         <v>1.941125457052606</v>
       </c>
-      <c r="AN220" t="n">
+      <c r="AP220" t="n">
         <v>1.474201474201475e-05</v>
       </c>
     </row>
@@ -28778,15 +30102,21 @@
         <v>1.26542967403936e-06</v>
       </c>
       <c r="AK221" t="n">
+        <v>1.020745830209793e-09</v>
+      </c>
+      <c r="AL221" t="n">
+        <v>0.01427752293577982</v>
+      </c>
+      <c r="AM221" t="n">
         <v>1181.607317816022</v>
       </c>
-      <c r="AL221" t="n">
+      <c r="AN221" t="n">
         <v>1.980570624845274</v>
       </c>
-      <c r="AM221" t="n">
+      <c r="AO221" t="n">
         <v>1.94469070679925</v>
       </c>
-      <c r="AN221" t="n">
+      <c r="AP221" t="n">
         <v>0.0008566513761467889</v>
       </c>
     </row>
@@ -28906,15 +30236,21 @@
         <v>1.26542967403936e-06</v>
       </c>
       <c r="AK222" t="n">
+        <v>1.029006201090104e-09</v>
+      </c>
+      <c r="AL222" t="n">
+        <v>0.01439306358381503</v>
+      </c>
+      <c r="AM222" t="n">
         <v>1181.610097886259</v>
       </c>
-      <c r="AL222" t="n">
+      <c r="AN222" t="n">
         <v>1.980570624845274</v>
       </c>
-      <c r="AM222" t="n">
+      <c r="AO222" t="n">
         <v>1.94429081486321</v>
       </c>
-      <c r="AN222" t="n">
+      <c r="AP222" t="n">
         <v>3.46820809248555e-05</v>
       </c>
     </row>
@@ -29034,15 +30370,21 @@
         <v>1.26542967403936e-06</v>
       </c>
       <c r="AK223" t="n">
+        <v>1.042260379324286e-09</v>
+      </c>
+      <c r="AL223" t="n">
+        <v>0.01457845433255269</v>
+      </c>
+      <c r="AM223" t="n">
         <v>1181.613672870503</v>
       </c>
-      <c r="AL223" t="n">
+      <c r="AN223" t="n">
         <v>1.980570624845274</v>
       </c>
-      <c r="AM223" t="n">
+      <c r="AO223" t="n">
         <v>1.943646469936154</v>
       </c>
-      <c r="AN223" t="n">
+      <c r="AP223" t="n">
         <v>0.00382552693208431</v>
       </c>
     </row>
@@ -29162,15 +30504,21 @@
         <v>1.26542967403936e-06</v>
       </c>
       <c r="AK224" t="n">
+        <v>1.119610520682943e-09</v>
+      </c>
+      <c r="AL224" t="n">
+        <v>0.01566037735849057</v>
+      </c>
+      <c r="AM224" t="n">
         <v>1181.609459642261</v>
       </c>
-      <c r="AL224" t="n">
+      <c r="AN224" t="n">
         <v>1.980570624845274</v>
       </c>
-      <c r="AM224" t="n">
+      <c r="AO224" t="n">
         <v>1.939820719833711</v>
       </c>
-      <c r="AN224" t="n">
+      <c r="AP224" t="n">
         <v>0.0009396226415094341</v>
       </c>
     </row>
@@ -29290,15 +30638,21 @@
         <v>0.0003679703698917816</v>
       </c>
       <c r="AK225" t="n">
+        <v>1.69645512448222e-06</v>
+      </c>
+      <c r="AL225" t="n">
+        <v>0.08160237388724036</v>
+      </c>
+      <c r="AM225" t="n">
         <v>1181.902763926532</v>
       </c>
-      <c r="AL225" t="n">
+      <c r="AN225" t="n">
         <v>1.980570624845274</v>
       </c>
-      <c r="AM225" t="n">
+      <c r="AO225" t="n">
         <v>1.951292026305375</v>
       </c>
-      <c r="AN225" t="n">
+      <c r="AP225" t="n">
         <v>1.186943620178041e-05</v>
       </c>
     </row>
@@ -29418,15 +30772,21 @@
         <v>0.0003679703698917816</v>
       </c>
       <c r="AK226" t="n">
+        <v>1.676555357626124e-06</v>
+      </c>
+      <c r="AL226" t="n">
+        <v>0.08064516129032258</v>
+      </c>
+      <c r="AM226" t="n">
         <v>1182.127644663908</v>
       </c>
-      <c r="AL226" t="n">
+      <c r="AN226" t="n">
         <v>1.980570624845274</v>
       </c>
-      <c r="AM226" t="n">
+      <c r="AO226" t="n">
         <v>1.951767151088345</v>
       </c>
-      <c r="AN226" t="n">
+      <c r="AP226" t="n">
         <v>0.0007302052785923755</v>
       </c>
     </row>
@@ -29546,15 +30906,21 @@
         <v>0.0003679703698917816</v>
       </c>
       <c r="AK227" t="n">
+        <v>1.691436026480793e-06</v>
+      </c>
+      <c r="AL227" t="n">
+        <v>0.08136094674556214</v>
+      </c>
+      <c r="AM227" t="n">
         <v>1181.991777136721</v>
       </c>
-      <c r="AL227" t="n">
+      <c r="AN227" t="n">
         <v>1.980570624845274</v>
       </c>
-      <c r="AM227" t="n">
+      <c r="AO227" t="n">
         <v>1.951412880939637</v>
       </c>
-      <c r="AN227" t="n">
+      <c r="AP227" t="n">
         <v>2.958579881656804e-05</v>
       </c>
     </row>
@@ -29674,15 +31040,21 @@
         <v>0.0003679703698917816</v>
       </c>
       <c r="AK228" t="n">
+        <v>2.157378780945314e-06</v>
+      </c>
+      <c r="AL228" t="n">
+        <v>0.1037735849056604</v>
+      </c>
+      <c r="AM228" t="n">
         <v>1182.8020942328</v>
       </c>
-      <c r="AL228" t="n">
+      <c r="AN228" t="n">
         <v>1.980570624845274</v>
       </c>
-      <c r="AM228" t="n">
+      <c r="AO228" t="n">
         <v>1.939861513343006</v>
       </c>
-      <c r="AN228" t="n">
+      <c r="AP228" t="n">
         <v>3.773584905660377e-05</v>
       </c>
     </row>
@@ -29802,15 +31174,21 @@
         <v>0.0003679703698917816</v>
       </c>
       <c r="AK229" t="n">
+        <v>1.992004797736962e-06</v>
+      </c>
+      <c r="AL229" t="n">
+        <v>0.09581881533101046</v>
+      </c>
+      <c r="AM229" t="n">
         <v>1184.711228045404</v>
       </c>
-      <c r="AL229" t="n">
+      <c r="AN229" t="n">
         <v>1.980570624845274</v>
       </c>
-      <c r="AM229" t="n">
+      <c r="AO229" t="n">
         <v>1.944153873573255</v>
       </c>
-      <c r="AN229" t="n">
+      <c r="AP229" t="n">
         <v>1.393728222996516e-05</v>
       </c>
     </row>
@@ -29930,15 +31308,21 @@
         <v>0.0003679703698917816</v>
       </c>
       <c r="AK230" t="n">
+        <v>2.107022273773372e-06</v>
+      </c>
+      <c r="AL230" t="n">
+        <v>0.1013513513513514</v>
+      </c>
+      <c r="AM230" t="n">
         <v>1182.977678862071</v>
       </c>
-      <c r="AL230" t="n">
+      <c r="AN230" t="n">
         <v>1.980570624845274</v>
       </c>
-      <c r="AM230" t="n">
+      <c r="AO230" t="n">
         <v>1.941170775332062</v>
       </c>
-      <c r="AN230" t="n">
+      <c r="AP230" t="n">
         <v>0.000917690417690418</v>
       </c>
     </row>
@@ -30058,15 +31442,21 @@
         <v>0.0003679703698917816</v>
       </c>
       <c r="AK231" t="n">
+        <v>1.966876296848078e-06</v>
+      </c>
+      <c r="AL231" t="n">
+        <v>0.09461009174311927</v>
+      </c>
+      <c r="AM231" t="n">
         <v>1182.39953130924</v>
       </c>
-      <c r="AL231" t="n">
+      <c r="AN231" t="n">
         <v>1.980570624845274</v>
       </c>
-      <c r="AM231" t="n">
+      <c r="AO231" t="n">
         <v>1.944714641329697</v>
       </c>
-      <c r="AN231" t="n">
+      <c r="AP231" t="n">
         <v>3.440366972477063e-05</v>
       </c>
     </row>
@@ -30186,15 +31576,21 @@
         <v>0.0003679703698917816</v>
       </c>
       <c r="AK232" t="n">
+        <v>1.982793214857254e-06</v>
+      </c>
+      <c r="AL232" t="n">
+        <v>0.09537572254335261</v>
+      </c>
+      <c r="AM232" t="n">
         <v>1182.116972571849</v>
       </c>
-      <c r="AL232" t="n">
+      <c r="AN232" t="n">
         <v>1.980570624845274</v>
       </c>
-      <c r="AM232" t="n">
+      <c r="AO232" t="n">
         <v>1.944306299215508</v>
       </c>
-      <c r="AN232" t="n">
+      <c r="AP232" t="n">
         <v>0.003776878612716764</v>
       </c>
     </row>
@@ -30314,15 +31710,21 @@
         <v>0</v>
       </c>
       <c r="AK233" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL233" t="n">
+        <v>0.01133879781420765</v>
+      </c>
+      <c r="AM233" t="n">
         <v>1000</v>
       </c>
-      <c r="AL233" t="n">
+      <c r="AN233" t="n">
         <v>1.980570624845274</v>
       </c>
-      <c r="AM233" t="n">
+      <c r="AO233" t="n">
         <v>1.949660672750196</v>
       </c>
-      <c r="AN233" t="n">
+      <c r="AP233" t="n">
         <v>1.092896174863388e-05</v>
       </c>
     </row>
@@ -30442,15 +31844,21 @@
         <v>0</v>
       </c>
       <c r="AK234" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL234" t="n">
+        <v>0.01566037735849057</v>
+      </c>
+      <c r="AM234" t="n">
         <v>1000</v>
       </c>
-      <c r="AL234" t="n">
+      <c r="AN234" t="n">
         <v>1.980570624845274</v>
       </c>
-      <c r="AM234" t="n">
+      <c r="AO234" t="n">
         <v>1.932493259242691</v>
       </c>
-      <c r="AN234" t="n">
+      <c r="AP234" t="n">
         <v>0.0009396226415094341</v>
       </c>
     </row>
@@ -30570,15 +31978,21 @@
         <v>0</v>
       </c>
       <c r="AK235" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL235" t="n">
+        <v>0.01265243902439024</v>
+      </c>
+      <c r="AM235" t="n">
         <v>1000</v>
       </c>
-      <c r="AL235" t="n">
+      <c r="AN235" t="n">
         <v>1.980570624845274</v>
       </c>
-      <c r="AM235" t="n">
+      <c r="AO235" t="n">
         <v>1.944673090056523</v>
       </c>
-      <c r="AN235" t="n">
+      <c r="AP235" t="n">
         <v>3.048780487804878e-05</v>
       </c>
     </row>
@@ -30698,15 +32112,21 @@
         <v>0</v>
       </c>
       <c r="AK236" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL236" t="n">
+        <v>0.01269113149847095</v>
+      </c>
+      <c r="AM236" t="n">
         <v>1000</v>
       </c>
-      <c r="AL236" t="n">
+      <c r="AN236" t="n">
         <v>1.980570624845274</v>
       </c>
-      <c r="AM236" t="n">
+      <c r="AO236" t="n">
         <v>1.944522997303554</v>
       </c>
-      <c r="AN236" t="n">
+      <c r="AP236" t="n">
         <v>3.058103975535168e-05</v>
       </c>
     </row>
@@ -30826,15 +32246,21 @@
         <v>0</v>
       </c>
       <c r="AK237" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL237" t="n">
+        <v>0.01206395348837209</v>
+      </c>
+      <c r="AM237" t="n">
         <v>1000</v>
       </c>
-      <c r="AL237" t="n">
+      <c r="AN237" t="n">
         <v>1.980570624845274</v>
       </c>
-      <c r="AM237" t="n">
+      <c r="AO237" t="n">
         <v>1.946933664205205</v>
       </c>
-      <c r="AN237" t="n">
+      <c r="AP237" t="n">
         <v>2.906976744186046e-05</v>
       </c>
     </row>
@@ -30954,15 +32380,21 @@
         <v>0</v>
       </c>
       <c r="AK238" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL238" t="n">
+        <v>0.01566037735849057</v>
+      </c>
+      <c r="AM238" t="n">
         <v>1000</v>
       </c>
-      <c r="AL238" t="n">
+      <c r="AN238" t="n">
         <v>1.980570624845274</v>
       </c>
-      <c r="AM238" t="n">
+      <c r="AO238" t="n">
         <v>1.932493259242691</v>
       </c>
-      <c r="AN238" t="n">
+      <c r="AP238" t="n">
         <v>0.004109433962264151</v>
       </c>
     </row>
@@ -31082,15 +32514,21 @@
         <v>0</v>
       </c>
       <c r="AK239" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL239" t="n">
+        <v>0.01257575757575758</v>
+      </c>
+      <c r="AM239" t="n">
         <v>1000</v>
       </c>
-      <c r="AL239" t="n">
+      <c r="AN239" t="n">
         <v>1.980570624845274</v>
       </c>
-      <c r="AM239" t="n">
+      <c r="AO239" t="n">
         <v>1.944970017712993</v>
       </c>
-      <c r="AN239" t="n">
+      <c r="AP239" t="n">
         <v>1.212121212121212e-05</v>
       </c>
     </row>
@@ -31210,15 +32648,21 @@
         <v>-1.049890220956849e-05</v>
       </c>
       <c r="AK240" t="n">
+        <v>-6.770096301534129e-09</v>
+      </c>
+      <c r="AL240" t="n">
+        <v>-0.0136963696369637</v>
+      </c>
+      <c r="AM240" t="n">
         <v>1162.689111721929</v>
       </c>
-      <c r="AL240" t="n">
+      <c r="AN240" t="n">
         <v>3.961141249690548</v>
       </c>
-      <c r="AM240" t="n">
+      <c r="AO240" t="n">
         <v>3.750198190432558</v>
       </c>
-      <c r="AN240" t="n">
+      <c r="AP240" t="n">
         <v>1.32013201320132e-05</v>
       </c>
     </row>
@@ -31338,15 +32782,21 @@
         <v>-1.049890220956849e-05</v>
       </c>
       <c r="AK241" t="n">
+        <v>-7.001157608753724e-09</v>
+      </c>
+      <c r="AL241" t="n">
+        <v>-0.01416382252559727</v>
+      </c>
+      <c r="AM241" t="n">
         <v>1163.129548094387</v>
       </c>
-      <c r="AL241" t="n">
+      <c r="AN241" t="n">
         <v>3.961141249690548</v>
       </c>
-      <c r="AM241" t="n">
+      <c r="AO241" t="n">
         <v>3.741040361440557</v>
       </c>
-      <c r="AN241" t="n">
+      <c r="AP241" t="n">
         <v>0.0008498293515358363</v>
       </c>
     </row>
@@ -31466,15 +32916,21 @@
         <v>-1.049890220956849e-05</v>
       </c>
       <c r="AK242" t="n">
+        <v>-6.930199930286626e-09</v>
+      </c>
+      <c r="AL242" t="n">
+        <v>-0.01402027027027027</v>
+      </c>
+      <c r="AM242" t="n">
         <v>1164.072306623774</v>
       </c>
-      <c r="AL242" t="n">
+      <c r="AN242" t="n">
         <v>3.961141249690548</v>
       </c>
-      <c r="AM242" t="n">
+      <c r="AO242" t="n">
         <v>3.74405588620131</v>
       </c>
-      <c r="AN242" t="n">
+      <c r="AP242" t="n">
         <v>0.0008412162162162164</v>
       </c>
     </row>
@@ -31594,15 +33050,21 @@
         <v>-1.049890220956849e-05</v>
       </c>
       <c r="AK243" t="n">
+        <v>-7.147523273048226e-09</v>
+      </c>
+      <c r="AL243" t="n">
+        <v>-0.01445993031358885</v>
+      </c>
+      <c r="AM243" t="n">
         <v>1162.76746693782</v>
       </c>
-      <c r="AL243" t="n">
+      <c r="AN243" t="n">
         <v>3.961141249690548</v>
       </c>
-      <c r="AM243" t="n">
+      <c r="AO243" t="n">
         <v>3.735075223928057</v>
       </c>
-      <c r="AN243" t="n">
+      <c r="AP243" t="n">
         <v>3.484320557491289e-05</v>
       </c>
     </row>
@@ -31722,15 +33184,21 @@
         <v>-1.049890220956849e-05</v>
       </c>
       <c r="AK244" t="n">
+        <v>-6.172535143525097e-09</v>
+      </c>
+      <c r="AL244" t="n">
+        <v>-0.01248746238716148</v>
+      </c>
+      <c r="AM244" t="n">
         <v>1162.503618349008</v>
       </c>
-      <c r="AL244" t="n">
+      <c r="AN244" t="n">
         <v>3.961141249690548</v>
       </c>
-      <c r="AM244" t="n">
+      <c r="AO244" t="n">
         <v>3.773614540366526</v>
       </c>
-      <c r="AN244" t="n">
+      <c r="AP244" t="n">
         <v>1.203610832497492e-05</v>
       </c>
     </row>
@@ -31850,15 +33318,21 @@
         <v>-1.049890220956849e-05</v>
       </c>
       <c r="AK245" t="n">
+        <v>-6.930199930286626e-09</v>
+      </c>
+      <c r="AL245" t="n">
+        <v>-0.01402027027027027</v>
+      </c>
+      <c r="AM245" t="n">
         <v>1163.781919708341</v>
       </c>
-      <c r="AL245" t="n">
+      <c r="AN245" t="n">
         <v>3.961141249690548</v>
       </c>
-      <c r="AM245" t="n">
+      <c r="AO245" t="n">
         <v>3.74400365818155</v>
       </c>
-      <c r="AN245" t="n">
+      <c r="AP245" t="n">
         <v>3.378378378378378e-05</v>
       </c>
     </row>
@@ -31978,15 +33452,21 @@
         <v>0</v>
       </c>
       <c r="AK246" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL246" t="n">
+        <v>0.01195965417867435</v>
+      </c>
+      <c r="AM246" t="n">
         <v>1000</v>
       </c>
-      <c r="AL246" t="n">
+      <c r="AN246" t="n">
         <v>3.961141249690548</v>
       </c>
-      <c r="AM246" t="n">
+      <c r="AO246" t="n">
         <v>3.755762004610685</v>
       </c>
-      <c r="AN246" t="n">
+      <c r="AP246" t="n">
         <v>1.152737752161383e-05</v>
       </c>
     </row>
@@ -32106,15 +33586,21 @@
         <v>0</v>
       </c>
       <c r="AK247" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL247" t="n">
+        <v>0.01202898550724638</v>
+      </c>
+      <c r="AM247" t="n">
         <v>1000</v>
       </c>
-      <c r="AL247" t="n">
+      <c r="AN247" t="n">
         <v>3.961141249690548</v>
       </c>
-      <c r="AM247" t="n">
+      <c r="AO247" t="n">
         <v>3.754255343667625</v>
       </c>
-      <c r="AN247" t="n">
+      <c r="AP247" t="n">
         <v>0.0007217391304347827</v>
       </c>
     </row>
@@ -32234,15 +33720,21 @@
         <v>0</v>
       </c>
       <c r="AK248" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL248" t="n">
+        <v>0.01213450292397661</v>
+      </c>
+      <c r="AM248" t="n">
         <v>1000</v>
       </c>
-      <c r="AL248" t="n">
+      <c r="AN248" t="n">
         <v>3.961141249690548</v>
       </c>
-      <c r="AM248" t="n">
+      <c r="AO248" t="n">
         <v>3.751957355084721</v>
       </c>
-      <c r="AN248" t="n">
+      <c r="AP248" t="n">
         <v>2.923976608187135e-05</v>
       </c>
     </row>
@@ -32362,15 +33854,21 @@
         <v>0</v>
       </c>
       <c r="AK249" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL249" t="n">
+        <v>0.01220588235294118</v>
+      </c>
+      <c r="AM249" t="n">
         <v>1000</v>
       </c>
-      <c r="AL249" t="n">
+      <c r="AN249" t="n">
         <v>3.961141249690548</v>
       </c>
-      <c r="AM249" t="n">
+      <c r="AO249" t="n">
         <v>3.750399463094666</v>
       </c>
-      <c r="AN249" t="n">
+      <c r="AP249" t="n">
         <v>0.0007323529411764708</v>
       </c>
     </row>
@@ -32490,15 +33988,21 @@
         <v>0</v>
       </c>
       <c r="AK250" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL250" t="n">
+        <v>0.01238805970149254</v>
+      </c>
+      <c r="AM250" t="n">
         <v>1000</v>
       </c>
-      <c r="AL250" t="n">
+      <c r="AN250" t="n">
         <v>3.961141249690548</v>
       </c>
-      <c r="AM250" t="n">
+      <c r="AO250" t="n">
         <v>3.746411136222354</v>
       </c>
-      <c r="AN250" t="n">
+      <c r="AP250" t="n">
         <v>0.0007432835820895523</v>
       </c>
     </row>
@@ -32618,15 +34122,21 @@
         <v>1.26542967403936e-06</v>
       </c>
       <c r="AK251" t="n">
+        <v>9.157308271017899e-10</v>
+      </c>
+      <c r="AL251" t="n">
+        <v>0.01280864197530864</v>
+      </c>
+      <c r="AM251" t="n">
         <v>1181.608087184106</v>
       </c>
-      <c r="AL251" t="n">
+      <c r="AN251" t="n">
         <v>3.961141249690548</v>
       </c>
-      <c r="AM251" t="n">
+      <c r="AO251" t="n">
         <v>3.770484223402482</v>
       </c>
-      <c r="AN251" t="n">
+      <c r="AP251" t="n">
         <v>1.234567901234568e-05</v>
       </c>
     </row>
@@ -32746,15 +34256,21 @@
         <v>1.26542967403936e-06</v>
       </c>
       <c r="AK252" t="n">
+        <v>8.990811756999391e-10</v>
+      </c>
+      <c r="AL252" t="n">
+        <v>0.01257575757575758</v>
+      </c>
+      <c r="AM252" t="n">
         <v>1181.607654036713</v>
       </c>
-      <c r="AL252" t="n">
+      <c r="AN252" t="n">
         <v>3.961141249690548</v>
       </c>
-      <c r="AM252" t="n">
+      <c r="AO252" t="n">
         <v>3.7748915941997</v>
       </c>
-      <c r="AN252" t="n">
+      <c r="AP252" t="n">
         <v>1.212121212121212e-05</v>
       </c>
     </row>
@@ -32874,15 +34390,21 @@
         <v>1.26542967403936e-06</v>
       </c>
       <c r="AK253" t="n">
+        <v>8.963649183715405e-10</v>
+      </c>
+      <c r="AL253" t="n">
+        <v>0.01253776435045317</v>
+      </c>
+      <c r="AM253" t="n">
         <v>1181.617192381408</v>
       </c>
-      <c r="AL253" t="n">
+      <c r="AN253" t="n">
         <v>3.961141249690548</v>
       </c>
-      <c r="AM253" t="n">
+      <c r="AO253" t="n">
         <v>3.775609714814665</v>
       </c>
-      <c r="AN253" t="n">
+      <c r="AP253" t="n">
         <v>0.0007522658610271904</v>
       </c>
     </row>
@@ -33002,15 +34524,21 @@
         <v>1.26542967403936e-06</v>
       </c>
       <c r="AK254" t="n">
+        <v>9.857036145547505e-10</v>
+      </c>
+      <c r="AL254" t="n">
+        <v>0.01378737541528239</v>
+      </c>
+      <c r="AM254" t="n">
         <v>1181.61008632305</v>
       </c>
-      <c r="AL254" t="n">
+      <c r="AN254" t="n">
         <v>3.961141249690548</v>
       </c>
-      <c r="AM254" t="n">
+      <c r="AO254" t="n">
         <v>3.751696258023839</v>
       </c>
-      <c r="AN254" t="n">
+      <c r="AP254" t="n">
         <v>3.322259136212624e-05</v>
       </c>
     </row>
@@ -33130,15 +34658,21 @@
         <v>1.26542967403936e-06</v>
       </c>
       <c r="AK255" t="n">
+        <v>9.509512435287817e-10</v>
+      </c>
+      <c r="AL255" t="n">
+        <v>0.01330128205128205</v>
+      </c>
+      <c r="AM255" t="n">
         <v>1181.605917024877</v>
       </c>
-      <c r="AL255" t="n">
+      <c r="AN255" t="n">
         <v>3.961141249690548</v>
       </c>
-      <c r="AM255" t="n">
+      <c r="AO255" t="n">
         <v>3.761079566550702</v>
       </c>
-      <c r="AN255" t="n">
+      <c r="AP255" t="n">
         <v>0.003490384615384616</v>
       </c>
     </row>
@@ -33258,15 +34792,21 @@
         <v>1.26542967403936e-06</v>
       </c>
       <c r="AK256" t="n">
+        <v>1.186787151923919e-09</v>
+      </c>
+      <c r="AL256" t="n">
+        <v>0.0166</v>
+      </c>
+      <c r="AM256" t="n">
         <v>1181.61619571635</v>
       </c>
-      <c r="AL256" t="n">
+      <c r="AN256" t="n">
         <v>3.961141249690548</v>
       </c>
-      <c r="AM256" t="n">
+      <c r="AO256" t="n">
         <v>3.695524138969889</v>
       </c>
-      <c r="AN256" t="n">
+      <c r="AP256" t="n">
         <v>0.0009960000000000001</v>
       </c>
     </row>
@@ -33386,15 +34926,21 @@
         <v>1.26542967403936e-06</v>
       </c>
       <c r="AK257" t="n">
+        <v>8.856620536745667e-10</v>
+      </c>
+      <c r="AL257" t="n">
+        <v>0.01238805970149254</v>
+      </c>
+      <c r="AM257" t="n">
         <v>1181.605072709822</v>
       </c>
-      <c r="AL257" t="n">
+      <c r="AN257" t="n">
         <v>3.961141249690548</v>
       </c>
-      <c r="AM257" t="n">
+      <c r="AO257" t="n">
         <v>3.778425222701941</v>
       </c>
-      <c r="AN257" t="n">
+      <c r="AP257" t="n">
         <v>2.985074626865671e-05</v>
       </c>
     </row>
@@ -33514,15 +35060,21 @@
         <v>1.26542967403936e-06</v>
       </c>
       <c r="AK258" t="n">
+        <v>8.927686699527978e-10</v>
+      </c>
+      <c r="AL258" t="n">
+        <v>0.01248746238716148</v>
+      </c>
+      <c r="AM258" t="n">
         <v>1181.604995965042</v>
       </c>
-      <c r="AL258" t="n">
+      <c r="AN258" t="n">
         <v>3.961141249690548</v>
       </c>
-      <c r="AM258" t="n">
+      <c r="AO258" t="n">
         <v>3.776555676274813</v>
       </c>
-      <c r="AN258" t="n">
+      <c r="AP258" t="n">
         <v>0.003276830491474423</v>
       </c>
     </row>
@@ -33642,15 +35194,21 @@
         <v>1.26542967403936e-06</v>
       </c>
       <c r="AK259" t="n">
+        <v>9.076380325726781e-10</v>
+      </c>
+      <c r="AL259" t="n">
+        <v>0.01269544527532291</v>
+      </c>
+      <c r="AM259" t="n">
         <v>1181.605774751627</v>
       </c>
-      <c r="AL259" t="n">
+      <c r="AN259" t="n">
         <v>3.961141249690548</v>
       </c>
-      <c r="AM259" t="n">
+      <c r="AO259" t="n">
         <v>3.772629270934751</v>
       </c>
-      <c r="AN259" t="n">
+      <c r="AP259" t="n">
         <v>0.0007617267165193747</v>
       </c>
     </row>
@@ -33770,15 +35328,21 @@
         <v>0.0003679703698917816</v>
       </c>
       <c r="AK260" t="n">
+        <v>1.647565927811263e-06</v>
+      </c>
+      <c r="AL260" t="n">
+        <v>0.0792507204610951</v>
+      </c>
+      <c r="AM260" t="n">
         <v>1181.97363249932</v>
       </c>
-      <c r="AL260" t="n">
+      <c r="AN260" t="n">
         <v>3.961141249690548</v>
       </c>
-      <c r="AM260" t="n">
+      <c r="AO260" t="n">
         <v>3.786482060770195</v>
       </c>
-      <c r="AN260" t="n">
+      <c r="AP260" t="n">
         <v>1.152737752161383e-05</v>
       </c>
     </row>
@@ -33898,15 +35462,21 @@
         <v>0.0003679703698917816</v>
       </c>
       <c r="AK261" t="n">
+        <v>1.657117034639154e-06</v>
+      </c>
+      <c r="AL261" t="n">
+        <v>0.07971014492753623</v>
+      </c>
+      <c r="AM261" t="n">
         <v>1182.105584510654</v>
       </c>
-      <c r="AL261" t="n">
+      <c r="AN261" t="n">
         <v>3.961141249690548</v>
       </c>
-      <c r="AM261" t="n">
+      <c r="AO261" t="n">
         <v>3.785212160728623</v>
       </c>
-      <c r="AN261" t="n">
+      <c r="AP261" t="n">
         <v>0.0007217391304347827</v>
       </c>
     </row>
@@ -34026,15 +35596,21 @@
         <v>0.0003679703698917816</v>
       </c>
       <c r="AK262" t="n">
+        <v>1.610437681550727e-06</v>
+      </c>
+      <c r="AL262" t="n">
+        <v>0.07746478873239437</v>
+      </c>
+      <c r="AM262" t="n">
         <v>1181.855408075503</v>
       </c>
-      <c r="AL262" t="n">
+      <c r="AN262" t="n">
         <v>3.961141249690548</v>
       </c>
-      <c r="AM262" t="n">
+      <c r="AO262" t="n">
         <v>3.791454076864708</v>
       </c>
-      <c r="AN262" t="n">
+      <c r="AP262" t="n">
         <v>2.816901408450704e-05</v>
       </c>
     </row>
@@ -34154,15 +35730,21 @@
         <v>0.0003679703698917816</v>
       </c>
       <c r="AK263" t="n">
+        <v>1.748334486087181e-06</v>
+      </c>
+      <c r="AL263" t="n">
+        <v>0.08409785932721714</v>
+      </c>
+      <c r="AM263" t="n">
         <v>1182.723072785544</v>
       </c>
-      <c r="AL263" t="n">
+      <c r="AN263" t="n">
         <v>3.961141249690548</v>
       </c>
-      <c r="AM263" t="n">
+      <c r="AO263" t="n">
         <v>3.772883502728543</v>
       </c>
-      <c r="AN263" t="n">
+      <c r="AP263" t="n">
         <v>1.223241590214067e-05</v>
       </c>
     </row>
@@ -34282,15 +35864,21 @@
         <v>0.0003679703698917816</v>
       </c>
       <c r="AK264" t="n">
+        <v>1.847190232473371e-06</v>
+      </c>
+      <c r="AL264" t="n">
+        <v>0.08885298869143782</v>
+      </c>
+      <c r="AM264" t="n">
         <v>1181.985423085461</v>
       </c>
-      <c r="AL264" t="n">
+      <c r="AN264" t="n">
         <v>3.961141249690548</v>
       </c>
-      <c r="AM264" t="n">
+      <c r="AO264" t="n">
         <v>3.75907699114125</v>
       </c>
-      <c r="AN264" t="n">
+      <c r="AP264" t="n">
         <v>0.0008045234248788369</v>
       </c>
     </row>
@@ -34410,15 +35998,21 @@
         <v>0.0003679703698917816</v>
       </c>
       <c r="AK265" t="n">
+        <v>1.665565555573221e-06</v>
+      </c>
+      <c r="AL265" t="n">
+        <v>0.08011653313911143</v>
+      </c>
+      <c r="AM265" t="n">
         <v>1181.98601255625</v>
       </c>
-      <c r="AL265" t="n">
+      <c r="AN265" t="n">
         <v>3.961141249690548</v>
       </c>
-      <c r="AM265" t="n">
+      <c r="AO265" t="n">
         <v>3.78405276075822</v>
       </c>
-      <c r="AN265" t="n">
+      <c r="AP265" t="n">
         <v>1.165331391114348e-05</v>
       </c>
     </row>
@@ -34538,15 +36132,21 @@
         <v>0</v>
       </c>
       <c r="AK266" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL266" t="n">
+        <v>0.01165730337078652</v>
+      </c>
+      <c r="AM266" t="n">
         <v>1000</v>
       </c>
-      <c r="AL266" t="n">
+      <c r="AN266" t="n">
         <v>3.961141249690548</v>
       </c>
-      <c r="AM266" t="n">
+      <c r="AO266" t="n">
         <v>3.762301913988289</v>
       </c>
-      <c r="AN266" t="n">
+      <c r="AP266" t="n">
         <v>1.123595505617978e-05</v>
       </c>
     </row>
@@ -34666,15 +36266,21 @@
         <v>0</v>
       </c>
       <c r="AK267" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL267" t="n">
+        <v>0.0124251497005988</v>
+      </c>
+      <c r="AM267" t="n">
         <v>1000</v>
       </c>
-      <c r="AL267" t="n">
+      <c r="AN267" t="n">
         <v>3.961141249690548</v>
       </c>
-      <c r="AM267" t="n">
+      <c r="AO267" t="n">
         <v>3.745597007267792</v>
       </c>
-      <c r="AN267" t="n">
+      <c r="AP267" t="n">
         <v>0.0007455089820359282</v>
       </c>
     </row>
@@ -34794,15 +36400,21 @@
         <v>0</v>
       </c>
       <c r="AK268" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL268" t="n">
+        <v>0.01227810650887574</v>
+      </c>
+      <c r="AM268" t="n">
         <v>1000</v>
       </c>
-      <c r="AL268" t="n">
+      <c r="AN268" t="n">
         <v>3.961141249690548</v>
       </c>
-      <c r="AM268" t="n">
+      <c r="AO268" t="n">
         <v>3.748820384115742</v>
       </c>
-      <c r="AN268" t="n">
+      <c r="AP268" t="n">
         <v>2.958579881656804e-05</v>
       </c>
     </row>
@@ -34922,15 +36534,21 @@
         <v>0</v>
       </c>
       <c r="AK269" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL269" t="n">
+        <v>0.01192528735632184</v>
+      </c>
+      <c r="AM269" t="n">
         <v>1000</v>
       </c>
-      <c r="AL269" t="n">
+      <c r="AN269" t="n">
         <v>3.961141249690548</v>
       </c>
-      <c r="AM269" t="n">
+      <c r="AO269" t="n">
         <v>3.756507878202096</v>
       </c>
-      <c r="AN269" t="n">
+      <c r="AP269" t="n">
         <v>1.149425287356322e-05</v>
       </c>
     </row>
@@ -35050,15 +36668,21 @@
         <v>0</v>
       </c>
       <c r="AK270" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL270" t="n">
+        <v>0.01340872374798062</v>
+      </c>
+      <c r="AM270" t="n">
         <v>1000</v>
       </c>
-      <c r="AL270" t="n">
+      <c r="AN270" t="n">
         <v>3.961141249690548</v>
       </c>
-      <c r="AM270" t="n">
+      <c r="AO270" t="n">
         <v>3.723752031606227</v>
       </c>
-      <c r="AN270" t="n">
+      <c r="AP270" t="n">
         <v>0.0008045234248788369</v>
       </c>
     </row>
@@ -35178,15 +36802,21 @@
         <v>0</v>
       </c>
       <c r="AK271" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL271" t="n">
+        <v>0.01209031318281136</v>
+      </c>
+      <c r="AM271" t="n">
         <v>1000</v>
       </c>
-      <c r="AL271" t="n">
+      <c r="AN271" t="n">
         <v>3.961141249690548</v>
       </c>
-      <c r="AM271" t="n">
+      <c r="AO271" t="n">
         <v>3.752920457496603</v>
       </c>
-      <c r="AN271" t="n">
+      <c r="AP271" t="n">
         <v>2.91332847778587e-05</v>
       </c>
     </row>
@@ -35306,15 +36936,21 @@
         <v>0</v>
       </c>
       <c r="AK272" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL272" t="n">
+        <v>0.01165730337078652</v>
+      </c>
+      <c r="AM272" t="n">
         <v>1000</v>
       </c>
-      <c r="AL272" t="n">
+      <c r="AN272" t="n">
         <v>3.961141249690548</v>
       </c>
-      <c r="AM272" t="n">
+      <c r="AO272" t="n">
         <v>3.762301913988289</v>
       </c>
-      <c r="AN272" t="n">
+      <c r="AP272" t="n">
         <v>0.003058988764044944</v>
       </c>
     </row>
@@ -35434,15 +37070,21 @@
         <v>0</v>
       </c>
       <c r="AK273" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL273" t="n">
+        <v>0.0124251497005988</v>
+      </c>
+      <c r="AM273" t="n">
         <v>1000</v>
       </c>
-      <c r="AL273" t="n">
+      <c r="AN273" t="n">
         <v>3.961141249690548</v>
       </c>
-      <c r="AM273" t="n">
+      <c r="AO273" t="n">
         <v>3.745597007267792</v>
       </c>
-      <c r="AN273" t="n">
+      <c r="AP273" t="n">
         <v>0.003260479041916168</v>
       </c>
     </row>
@@ -35562,15 +37204,21 @@
         <v>0</v>
       </c>
       <c r="AK274" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL274" t="n">
+        <v>0.01217008797653959</v>
+      </c>
+      <c r="AM274" t="n">
         <v>1000</v>
       </c>
-      <c r="AL274" t="n">
+      <c r="AN274" t="n">
         <v>3.961141249690548</v>
       </c>
-      <c r="AM274" t="n">
+      <c r="AO274" t="n">
         <v>3.751181032119062</v>
       </c>
-      <c r="AN274" t="n">
+      <c r="AP274" t="n">
         <v>0.0007302052785923755</v>
       </c>
     </row>
@@ -35690,15 +37338,21 @@
         <v>-1.049890220956849e-05</v>
       </c>
       <c r="AK275" t="n">
+        <v>-6.930199930286626e-09</v>
+      </c>
+      <c r="AL275" t="n">
+        <v>-0.01402027027027027</v>
+      </c>
+      <c r="AM275" t="n">
         <v>1162.963556583029</v>
       </c>
-      <c r="AL275" t="n">
+      <c r="AN275" t="n">
         <v>3.961141249690548</v>
       </c>
-      <c r="AM275" t="n">
+      <c r="AO275" t="n">
         <v>3.743856335278243</v>
       </c>
-      <c r="AN275" t="n">
+      <c r="AP275" t="n">
         <v>1.351351351351351e-05</v>
       </c>
     </row>
@@ -35818,15 +37472,21 @@
         <v>-1.049890220956849e-05</v>
       </c>
       <c r="AK276" t="n">
+        <v>-6.906865923787344e-09</v>
+      </c>
+      <c r="AL276" t="n">
+        <v>-0.01397306397306397</v>
+      </c>
+      <c r="AM276" t="n">
         <v>1162.783991579858</v>
       </c>
-      <c r="AL276" t="n">
+      <c r="AN276" t="n">
         <v>3.961141249690548</v>
       </c>
-      <c r="AM276" t="n">
+      <c r="AO276" t="n">
         <v>3.744758187703347</v>
       </c>
-      <c r="AN276" t="n">
+      <c r="AP276" t="n">
         <v>0.0008383838383838385</v>
       </c>
     </row>
@@ -35946,15 +37606,21 @@
         <v>-1.049890220956849e-05</v>
       </c>
       <c r="AK277" t="n">
+        <v>-7.025134175906991e-09</v>
+      </c>
+      <c r="AL277" t="n">
+        <v>-0.01421232876712329</v>
+      </c>
+      <c r="AM277" t="n">
         <v>1165.286085374777</v>
       </c>
-      <c r="AL277" t="n">
+      <c r="AN277" t="n">
         <v>3.961141249690548</v>
       </c>
-      <c r="AM277" t="n">
+      <c r="AO277" t="n">
         <v>3.740470990674091</v>
       </c>
-      <c r="AN277" t="n">
+      <c r="AP277" t="n">
         <v>3.424657534246575e-05</v>
       </c>
     </row>
@@ -36074,15 +37740,21 @@
         <v>-1.049890220956849e-05</v>
       </c>
       <c r="AK278" t="n">
+        <v>-7.049275530463371e-09</v>
+      </c>
+      <c r="AL278" t="n">
+        <v>-0.01426116838487972</v>
+      </c>
+      <c r="AM278" t="n">
         <v>1163.319696710737</v>
       </c>
-      <c r="AL278" t="n">
+      <c r="AN278" t="n">
         <v>3.961141249690548</v>
       </c>
-      <c r="AM278" t="n">
+      <c r="AO278" t="n">
         <v>3.739140560395881</v>
       </c>
-      <c r="AN278" t="n">
+      <c r="AP278" t="n">
         <v>3.436426116838488e-05</v>
       </c>
     </row>
@@ -36202,15 +37874,21 @@
         <v>-1.049890220956849e-05</v>
       </c>
       <c r="AK279" t="n">
+        <v>-6.141734069954614e-09</v>
+      </c>
+      <c r="AL279" t="n">
+        <v>-0.0124251497005988</v>
+      </c>
+      <c r="AM279" t="n">
         <v>1162.459367324382</v>
       </c>
-      <c r="AL279" t="n">
+      <c r="AN279" t="n">
         <v>3.961141249690548</v>
       </c>
-      <c r="AM279" t="n">
+      <c r="AO279" t="n">
         <v>3.774798167238938</v>
       </c>
-      <c r="AN279" t="n">
+      <c r="AP279" t="n">
         <v>1.197604790419162e-05</v>
       </c>
     </row>
@@ -36330,15 +38008,21 @@
         <v>-1.049890220956849e-05</v>
       </c>
       <c r="AK280" t="n">
+        <v>-6.015657417492203e-09</v>
+      </c>
+      <c r="AL280" t="n">
+        <v>-0.01217008797653959</v>
+      </c>
+      <c r="AM280" t="n">
         <v>1163.269064494395</v>
       </c>
-      <c r="AL280" t="n">
+      <c r="AN280" t="n">
         <v>3.961141249690548</v>
       </c>
-      <c r="AM280" t="n">
+      <c r="AO280" t="n">
         <v>3.779774794964973</v>
       </c>
-      <c r="AN280" t="n">
+      <c r="AP280" t="n">
         <v>0.0007302052785923755</v>
       </c>
     </row>
@@ -36458,15 +38142,21 @@
         <v>-1.049890220956849e-05</v>
       </c>
       <c r="AK281" t="n">
+        <v>-6.27320849958667e-09</v>
+      </c>
+      <c r="AL281" t="n">
+        <v>-0.01269113149847095</v>
+      </c>
+      <c r="AM281" t="n">
         <v>1162.724465915434</v>
       </c>
-      <c r="AL281" t="n">
+      <c r="AN281" t="n">
         <v>3.961141249690548</v>
       </c>
-      <c r="AM281" t="n">
+      <c r="AO281" t="n">
         <v>3.769745887796589</v>
       </c>
-      <c r="AN281" t="n">
+      <c r="AP281" t="n">
         <v>0.003330275229357799</v>
       </c>
     </row>
@@ -36586,15 +38276,21 @@
         <v>-1.049890220956849e-05</v>
       </c>
       <c r="AK282" t="n">
+        <v>-9.630700372604889e-09</v>
+      </c>
+      <c r="AL282" t="n">
+        <v>-0.01948356807511737</v>
+      </c>
+      <c r="AM282" t="n">
         <v>1168.872146600376</v>
       </c>
-      <c r="AL282" t="n">
+      <c r="AN282" t="n">
         <v>3.961141249690548</v>
       </c>
-      <c r="AM282" t="n">
+      <c r="AO282" t="n">
         <v>3.631669308379464</v>
       </c>
-      <c r="AN282" t="n">
+      <c r="AP282" t="n">
         <v>0.005112676056338029</v>
       </c>
     </row>
@@ -36714,15 +38410,21 @@
         <v>1.26542967403936e-06</v>
       </c>
       <c r="AK283" t="n">
+        <v>8.700785571289733e-10</v>
+      </c>
+      <c r="AL283" t="n">
+        <v>0.01217008797653959</v>
+      </c>
+      <c r="AM283" t="n">
         <v>1181.608046874219</v>
       </c>
-      <c r="AL283" t="n">
+      <c r="AN283" t="n">
         <v>3.961141249690548</v>
       </c>
-      <c r="AM283" t="n">
+      <c r="AO283" t="n">
         <v>3.782508936274809</v>
       </c>
-      <c r="AN283" t="n">
+      <c r="AP283" t="n">
         <v>1.173020527859238e-05</v>
       </c>
     </row>
@@ -36842,15 +38544,21 @@
         <v>1.26542967403936e-06</v>
       </c>
       <c r="AK284" t="n">
+        <v>9.045633779907923e-10</v>
+      </c>
+      <c r="AL284" t="n">
+        <v>0.01265243902439024</v>
+      </c>
+      <c r="AM284" t="n">
         <v>1181.605196603368</v>
       </c>
-      <c r="AL284" t="n">
+      <c r="AN284" t="n">
         <v>3.961141249690548</v>
       </c>
-      <c r="AM284" t="n">
+      <c r="AO284" t="n">
         <v>3.773442737478323</v>
       </c>
-      <c r="AN284" t="n">
+      <c r="AP284" t="n">
         <v>0.0007591463414634148</v>
       </c>
     </row>
@@ -36970,15 +38678,21 @@
         <v>1.26542967403936e-06</v>
       </c>
       <c r="AK285" t="n">
+        <v>8.963649183715405e-10</v>
+      </c>
+      <c r="AL285" t="n">
+        <v>0.01253776435045317</v>
+      </c>
+      <c r="AM285" t="n">
         <v>1181.604247529524</v>
       </c>
-      <c r="AL285" t="n">
+      <c r="AN285" t="n">
         <v>3.961141249690548</v>
       </c>
-      <c r="AM285" t="n">
+      <c r="AO285" t="n">
         <v>3.775607743080117</v>
       </c>
-      <c r="AN285" t="n">
+      <c r="AP285" t="n">
         <v>3.021148036253776e-05</v>
       </c>
     </row>
@@ -37098,15 +38812,21 @@
         <v>1.26542967403936e-06</v>
       </c>
       <c r="AK286" t="n">
+        <v>1.273376772450557e-09</v>
+      </c>
+      <c r="AL286" t="n">
+        <v>0.01781115879828326</v>
+      </c>
+      <c r="AM286" t="n">
         <v>1181.621745259641</v>
       </c>
-      <c r="AL286" t="n">
+      <c r="AN286" t="n">
         <v>3.961141249690548</v>
       </c>
-      <c r="AM286" t="n">
+      <c r="AO286" t="n">
         <v>3.670443713088548</v>
       </c>
-      <c r="AN286" t="n">
+      <c r="AP286" t="n">
         <v>0.001068669527896996</v>
       </c>
     </row>
@@ -37226,15 +38946,21 @@
         <v>1.26542967403936e-06</v>
       </c>
       <c r="AK287" t="n">
+        <v>1.186787151923919e-09</v>
+      </c>
+      <c r="AL287" t="n">
+        <v>0.0166</v>
+      </c>
+      <c r="AM287" t="n">
         <v>1181.611970746867</v>
       </c>
-      <c r="AL287" t="n">
+      <c r="AN287" t="n">
         <v>3.961141249690548</v>
       </c>
-      <c r="AM287" t="n">
+      <c r="AO287" t="n">
         <v>3.695523231448532</v>
       </c>
-      <c r="AN287" t="n">
+      <c r="AP287" t="n">
         <v>1.6e-05</v>
       </c>
     </row>
@@ -37354,15 +39080,21 @@
         <v>1.26542967403936e-06</v>
       </c>
       <c r="AK288" t="n">
+        <v>8.936650240390961e-10</v>
+      </c>
+      <c r="AL288" t="n">
+        <v>0.0125</v>
+      </c>
+      <c r="AM288" t="n">
         <v>1181.603908602029</v>
       </c>
-      <c r="AL288" t="n">
+      <c r="AN288" t="n">
         <v>3.961141249690548</v>
       </c>
-      <c r="AM288" t="n">
+      <c r="AO288" t="n">
         <v>3.776319380264171</v>
       </c>
-      <c r="AN288" t="n">
+      <c r="AP288" t="n">
         <v>3.012048192771084e-05</v>
       </c>
     </row>
@@ -37482,15 +39214,21 @@
         <v>1.26542967403936e-06</v>
       </c>
       <c r="AK289" t="n">
+        <v>8.936650240390961e-10</v>
+      </c>
+      <c r="AL289" t="n">
+        <v>0.0125</v>
+      </c>
+      <c r="AM289" t="n">
         <v>1181.604610145983</v>
       </c>
-      <c r="AL289" t="n">
+      <c r="AN289" t="n">
         <v>3.961141249690548</v>
       </c>
-      <c r="AM289" t="n">
+      <c r="AO289" t="n">
         <v>3.776319486727869</v>
       </c>
-      <c r="AN289" t="n">
+      <c r="AP289" t="n">
         <v>3.012048192771084e-05</v>
       </c>
     </row>
@@ -37610,15 +39348,21 @@
         <v>1.26542967403936e-06</v>
       </c>
       <c r="AK290" t="n">
+        <v>8.856620536745667e-10</v>
+      </c>
+      <c r="AL290" t="n">
+        <v>0.01238805970149254</v>
+      </c>
+      <c r="AM290" t="n">
         <v>1181.603804532366</v>
       </c>
-      <c r="AL290" t="n">
+      <c r="AN290" t="n">
         <v>3.961141249690548</v>
       </c>
-      <c r="AM290" t="n">
+      <c r="AO290" t="n">
         <v>3.778425032363067</v>
       </c>
-      <c r="AN290" t="n">
+      <c r="AP290" t="n">
         <v>0.003250746268656716</v>
       </c>
     </row>
@@ -37738,15 +39482,21 @@
         <v>1.26542967403936e-06</v>
       </c>
       <c r="AK291" t="n">
+        <v>8.963649183715405e-10</v>
+      </c>
+      <c r="AL291" t="n">
+        <v>0.01253776435045317</v>
+      </c>
+      <c r="AM291" t="n">
         <v>1181.606371294287</v>
       </c>
-      <c r="AL291" t="n">
+      <c r="AN291" t="n">
         <v>3.961141249690548</v>
       </c>
-      <c r="AM291" t="n">
+      <c r="AO291" t="n">
         <v>3.775608066570674</v>
       </c>
-      <c r="AN291" t="n">
+      <c r="AP291" t="n">
         <v>0.003290030211480363</v>
       </c>
     </row>
@@ -37866,15 +39616,21 @@
         <v>0.0003679703698917816</v>
       </c>
       <c r="AK292" t="n">
+        <v>1.583671404295037e-06</v>
+      </c>
+      <c r="AL292" t="n">
+        <v>0.07617728531855956</v>
+      </c>
+      <c r="AM292" t="n">
         <v>1181.781307428795</v>
       </c>
-      <c r="AL292" t="n">
+      <c r="AN292" t="n">
         <v>3.961141249690548</v>
       </c>
-      <c r="AM292" t="n">
+      <c r="AO292" t="n">
         <v>3.795018401085928</v>
       </c>
-      <c r="AN292" t="n">
+      <c r="AP292" t="n">
         <v>1.10803324099723e-05</v>
       </c>
     </row>
@@ -37994,15 +39750,21 @@
         <v>0.0003679703698917816</v>
       </c>
       <c r="AK293" t="n">
+        <v>1.63812428925647e-06</v>
+      </c>
+      <c r="AL293" t="n">
+        <v>0.07879656160458454</v>
+      </c>
+      <c r="AM293" t="n">
         <v>1181.774157782344</v>
       </c>
-      <c r="AL293" t="n">
+      <c r="AN293" t="n">
         <v>3.961141249690548</v>
       </c>
-      <c r="AM293" t="n">
+      <c r="AO293" t="n">
         <v>3.787725533471395</v>
       </c>
-      <c r="AN293" t="n">
+      <c r="AP293" t="n">
         <v>0.0007134670487106018</v>
       </c>
     </row>
@@ -38122,15 +39884,21 @@
         <v>0.0003679703698917816</v>
       </c>
       <c r="AK294" t="n">
+        <v>1.601415621710107e-06</v>
+      </c>
+      <c r="AL294" t="n">
+        <v>0.07703081232492998</v>
+      </c>
+      <c r="AM294" t="n">
         <v>1181.769784454709</v>
       </c>
-      <c r="AL294" t="n">
+      <c r="AN294" t="n">
         <v>3.961141249690548</v>
       </c>
-      <c r="AM294" t="n">
+      <c r="AO294" t="n">
         <v>3.792649127111939</v>
       </c>
-      <c r="AN294" t="n">
+      <c r="AP294" t="n">
         <v>2.801120448179272e-05</v>
       </c>
     </row>
@@ -38250,15 +40018,21 @@
         <v>0.0003679703698917816</v>
       </c>
       <c r="AK295" t="n">
+        <v>1.624163002700307e-06</v>
+      </c>
+      <c r="AL295" t="n">
+        <v>0.078125</v>
+      </c>
+      <c r="AM295" t="n">
         <v>1182.057567352442</v>
       </c>
-      <c r="AL295" t="n">
+      <c r="AN295" t="n">
         <v>3.961141249690548</v>
       </c>
-      <c r="AM295" t="n">
+      <c r="AO295" t="n">
         <v>3.789642447045158</v>
       </c>
-      <c r="AN295" t="n">
+      <c r="AP295" t="n">
         <v>1.136363636363636e-05</v>
       </c>
     </row>
@@ -38378,15 +40152,21 @@
         <v>0.0003679703698917816</v>
       </c>
       <c r="AK296" t="n">
+        <v>1.720276961736734e-06</v>
+      </c>
+      <c r="AL296" t="n">
+        <v>0.08274824473420261</v>
+      </c>
+      <c r="AM296" t="n">
         <v>1181.828004263473</v>
       </c>
-      <c r="AL296" t="n">
+      <c r="AN296" t="n">
         <v>3.961141249690548</v>
       </c>
-      <c r="AM296" t="n">
+      <c r="AO296" t="n">
         <v>3.776589471284598</v>
       </c>
-      <c r="AN296" t="n">
+      <c r="AP296" t="n">
         <v>0.000749247743229689</v>
       </c>
     </row>
@@ -38506,15 +40286,21 @@
         <v>0.0003679703698917816</v>
       </c>
       <c r="AK297" t="n">
+        <v>1.748928753417598e-06</v>
+      </c>
+      <c r="AL297" t="n">
+        <v>0.08412644459551324</v>
+      </c>
+      <c r="AM297" t="n">
         <v>1182.046922883927</v>
       </c>
-      <c r="AL297" t="n">
+      <c r="AN297" t="n">
         <v>3.961141249690548</v>
       </c>
-      <c r="AM297" t="n">
+      <c r="AO297" t="n">
         <v>3.772697481235205</v>
       </c>
-      <c r="AN297" t="n">
+      <c r="AP297" t="n">
         <v>3.059143439836846e-05</v>
       </c>
     </row>
@@ -38634,15 +40420,21 @@
         <v>0.0003679703698917816</v>
       </c>
       <c r="AK298" t="n">
+        <v>1.583671404295037e-06</v>
+      </c>
+      <c r="AL298" t="n">
+        <v>0.07617728531855956</v>
+      </c>
+      <c r="AM298" t="n">
         <v>1181.866829800869</v>
       </c>
-      <c r="AL298" t="n">
+      <c r="AN298" t="n">
         <v>1.980570624845274</v>
       </c>
-      <c r="AM298" t="n">
+      <c r="AO298" t="n">
         <v>1.953923770041765</v>
       </c>
-      <c r="AN298" t="n">
+      <c r="AP298" t="n">
         <v>1.10803324099723e-05</v>
       </c>
     </row>
@@ -38762,15 +40554,21 @@
         <v>0.0003679703698917816</v>
       </c>
       <c r="AK299" t="n">
+        <v>1.596942393716503e-06</v>
+      </c>
+      <c r="AL299" t="n">
+        <v>0.07681564245810056</v>
+      </c>
+      <c r="AM299" t="n">
         <v>1181.999868419889</v>
       </c>
-      <c r="AL299" t="n">
+      <c r="AN299" t="n">
         <v>1.980570624845274</v>
       </c>
-      <c r="AM299" t="n">
+      <c r="AO299" t="n">
         <v>1.953620744254109</v>
       </c>
-      <c r="AN299" t="n">
+      <c r="AP299" t="n">
         <v>0.0006955307262569833</v>
       </c>
     </row>
@@ -38890,15 +40688,21 @@
         <v>0.0003679703698917816</v>
       </c>
       <c r="AK300" t="n">
+        <v>1.583671404295037e-06</v>
+      </c>
+      <c r="AL300" t="n">
+        <v>0.07617728531855956</v>
+      </c>
+      <c r="AM300" t="n">
         <v>1181.747098479966</v>
       </c>
-      <c r="AL300" t="n">
+      <c r="AN300" t="n">
         <v>1.980570624845274</v>
       </c>
-      <c r="AM300" t="n">
+      <c r="AO300" t="n">
         <v>1.953921064300269</v>
       </c>
-      <c r="AN300" t="n">
+      <c r="AP300" t="n">
         <v>2.770083102493075e-05</v>
       </c>
     </row>
@@ -39018,15 +40822,21 @@
         <v>0.0003679703698917816</v>
       </c>
       <c r="AK301" t="n">
+        <v>1.619561974364046e-06</v>
+      </c>
+      <c r="AL301" t="n">
+        <v>0.07790368271954676</v>
+      </c>
+      <c r="AM301" t="n">
         <v>1182.112230288084</v>
       </c>
-      <c r="AL301" t="n">
+      <c r="AN301" t="n">
         <v>1.980570624845274</v>
       </c>
-      <c r="AM301" t="n">
+      <c r="AO301" t="n">
         <v>1.953099448151992</v>
       </c>
-      <c r="AN301" t="n">
+      <c r="AP301" t="n">
         <v>2.832861189801699e-05</v>
       </c>
     </row>
@@ -39146,15 +40956,21 @@
         <v>0.0003679703698917816</v>
       </c>
       <c r="AK302" t="n">
+        <v>2.008332705915135e-06</v>
+      </c>
+      <c r="AL302" t="n">
+        <v>0.0966042154566745</v>
+      </c>
+      <c r="AM302" t="n">
         <v>1181.955812878647</v>
       </c>
-      <c r="AL302" t="n">
+      <c r="AN302" t="n">
         <v>1.980570624845274</v>
       </c>
-      <c r="AM302" t="n">
+      <c r="AO302" t="n">
         <v>1.943657104785373</v>
       </c>
-      <c r="AN302" t="n">
+      <c r="AP302" t="n">
         <v>1.405152224824356e-05</v>
       </c>
     </row>
@@ -39274,15 +41090,21 @@
         <v>0.0003679703698917816</v>
       </c>
       <c r="AK303" t="n">
+        <v>2.157378780945314e-06</v>
+      </c>
+      <c r="AL303" t="n">
+        <v>0.1037735849056604</v>
+      </c>
+      <c r="AM303" t="n">
         <v>1183.260446710054</v>
       </c>
-      <c r="AL303" t="n">
+      <c r="AN303" t="n">
         <v>1.980570624845274</v>
       </c>
-      <c r="AM303" t="n">
+      <c r="AO303" t="n">
         <v>1.93987716952591</v>
       </c>
-      <c r="AN303" t="n">
+      <c r="AP303" t="n">
         <v>1.509433962264151e-05</v>
       </c>
     </row>
@@ -39402,15 +41224,21 @@
         <v>1.26542967403936e-06</v>
       </c>
       <c r="AK304" t="n">
+        <v>8.700785571289733e-10</v>
+      </c>
+      <c r="AL304" t="n">
+        <v>0.01217008797653959</v>
+      </c>
+      <c r="AM304" t="n">
         <v>1181.605734554041</v>
       </c>
-      <c r="AL304" t="n">
+      <c r="AN304" t="n">
         <v>1.980570624845274</v>
       </c>
-      <c r="AM304" t="n">
+      <c r="AO304" t="n">
         <v>1.951754422982434</v>
       </c>
-      <c r="AN304" t="n">
+      <c r="AP304" t="n">
         <v>1.173020527859238e-05</v>
       </c>
     </row>
@@ -39530,15 +41358,21 @@
         <v>1.26542967403936e-06</v>
       </c>
       <c r="AK305" t="n">
+        <v>8.804058990533527e-10</v>
+      </c>
+      <c r="AL305" t="n">
+        <v>0.01231454005934718</v>
+      </c>
+      <c r="AM305" t="n">
         <v>1181.604407976051</v>
       </c>
-      <c r="AL305" t="n">
+      <c r="AN305" t="n">
         <v>1.980570624845274</v>
       </c>
-      <c r="AM305" t="n">
+      <c r="AO305" t="n">
         <v>1.951284632783494</v>
       </c>
-      <c r="AN305" t="n">
+      <c r="AP305" t="n">
         <v>2.967359050445104e-05</v>
       </c>
     </row>
@@ -39658,15 +41492,21 @@
         <v>1.26542967403936e-06</v>
       </c>
       <c r="AK306" t="n">
+        <v>8.909813452882279e-10</v>
+      </c>
+      <c r="AL306" t="n">
+        <v>0.01246246246246246</v>
+      </c>
+      <c r="AM306" t="n">
         <v>1181.610229999711</v>
       </c>
-      <c r="AL306" t="n">
+      <c r="AN306" t="n">
         <v>1.980570624845274</v>
       </c>
-      <c r="AM306" t="n">
+      <c r="AO306" t="n">
         <v>1.950801481093384</v>
       </c>
-      <c r="AN306" t="n">
+      <c r="AP306" t="n">
         <v>3.003003003003003e-05</v>
       </c>
     </row>
@@ -39786,15 +41626,21 @@
         <v>1.26542967403936e-06</v>
       </c>
       <c r="AK307" t="n">
+        <v>8.525769769568387e-10</v>
+      </c>
+      <c r="AL307" t="n">
+        <v>0.01192528735632184</v>
+      </c>
+      <c r="AM307" t="n">
         <v>1181.613836635159</v>
       </c>
-      <c r="AL307" t="n">
+      <c r="AN307" t="n">
         <v>1.980570624845274</v>
       </c>
-      <c r="AM307" t="n">
+      <c r="AO307" t="n">
         <v>1.952545698519946</v>
       </c>
-      <c r="AN307" t="n">
+      <c r="AP307" t="n">
         <v>0.0007155172413793105</v>
       </c>
     </row>
@@ -39914,15 +41760,21 @@
         <v>1.26542967403936e-06</v>
       </c>
       <c r="AK308" t="n">
+        <v>8.650052127725361e-10</v>
+      </c>
+      <c r="AL308" t="n">
+        <v>0.01209912536443149</v>
+      </c>
+      <c r="AM308" t="n">
         <v>1181.609270195837</v>
       </c>
-      <c r="AL308" t="n">
+      <c r="AN308" t="n">
         <v>1.980570624845274</v>
       </c>
-      <c r="AM308" t="n">
+      <c r="AO308" t="n">
         <v>1.951984477361816</v>
       </c>
-      <c r="AN308" t="n">
+      <c r="AP308" t="n">
         <v>0.0007259475218658894</v>
       </c>
     </row>
@@ -40042,15 +41894,21 @@
         <v>1.26542967403936e-06</v>
       </c>
       <c r="AK309" t="n">
+        <v>1.093477105581007e-09</v>
+      </c>
+      <c r="AL309" t="n">
+        <v>0.0152948402948403</v>
+      </c>
+      <c r="AM309" t="n">
         <v>1181.620195487073</v>
       </c>
-      <c r="AL309" t="n">
+      <c r="AN309" t="n">
         <v>1.980570624845274</v>
       </c>
-      <c r="AM309" t="n">
+      <c r="AO309" t="n">
         <v>1.941125804134277</v>
       </c>
-      <c r="AN309" t="n">
+      <c r="AP309" t="n">
         <v>1.474201474201475e-05</v>
       </c>
     </row>
@@ -40170,15 +42028,21 @@
         <v>1.26542967403936e-06</v>
       </c>
       <c r="AK310" t="n">
+        <v>1.020745830209793e-09</v>
+      </c>
+      <c r="AL310" t="n">
+        <v>0.01427752293577982</v>
+      </c>
+      <c r="AM310" t="n">
         <v>1181.611200738809</v>
       </c>
-      <c r="AL310" t="n">
+      <c r="AN310" t="n">
         <v>1.980570624845274</v>
       </c>
-      <c r="AM310" t="n">
+      <c r="AO310" t="n">
         <v>1.944690824188211</v>
       </c>
-      <c r="AN310" t="n">
+      <c r="AP310" t="n">
         <v>1.376146788990825e-05</v>
       </c>
     </row>
@@ -40298,15 +42162,21 @@
         <v>-1.049890220956849e-05</v>
       </c>
       <c r="AK311" t="n">
+        <v>-7.740902563640911e-09</v>
+      </c>
+      <c r="AL311" t="n">
+        <v>-0.01566037735849057</v>
+      </c>
+      <c r="AM311" t="n">
         <v>1165.292644967904</v>
       </c>
-      <c r="AL311" t="n">
+      <c r="AN311" t="n">
         <v>1.980570624845274</v>
       </c>
-      <c r="AM311" t="n">
+      <c r="AO311" t="n">
         <v>1.939254351409342</v>
       </c>
-      <c r="AN311" t="n">
+      <c r="AP311" t="n">
         <v>1.509433962264151e-05</v>
       </c>
     </row>
@@ -40426,15 +42296,21 @@
         <v>-1.049890220956849e-05</v>
       </c>
       <c r="AK312" t="n">
+        <v>-6.770096301534129e-09</v>
+      </c>
+      <c r="AL312" t="n">
+        <v>-0.0136963696369637</v>
+      </c>
+      <c r="AM312" t="n">
         <v>1163.981196200545</v>
       </c>
-      <c r="AL312" t="n">
+      <c r="AN312" t="n">
         <v>1.980570624845274</v>
       </c>
-      <c r="AM312" t="n">
+      <c r="AO312" t="n">
         <v>1.946171449862554</v>
       </c>
-      <c r="AN312" t="n">
+      <c r="AP312" t="n">
         <v>0.0008217821782178219</v>
       </c>
     </row>
@@ -40554,15 +42430,21 @@
         <v>-1.049890220956849e-05</v>
       </c>
       <c r="AK313" t="n">
+        <v>-6.906865923787344e-09</v>
+      </c>
+      <c r="AL313" t="n">
+        <v>-0.01397306397306397</v>
+      </c>
+      <c r="AM313" t="n">
         <v>1164.312775160581</v>
       </c>
-      <c r="AL313" t="n">
+      <c r="AN313" t="n">
         <v>1.980570624845274</v>
       </c>
-      <c r="AM313" t="n">
+      <c r="AO313" t="n">
         <v>1.945223139729817</v>
       </c>
-      <c r="AN313" t="n">
+      <c r="AP313" t="n">
         <v>1.346801346801347e-05</v>
       </c>
     </row>
@@ -40682,15 +42564,21 @@
         <v>-1.049890220956849e-05</v>
       </c>
       <c r="AK314" t="n">
+        <v>-7.740902563640911e-09</v>
+      </c>
+      <c r="AL314" t="n">
+        <v>-0.01566037735849057</v>
+      </c>
+      <c r="AM314" t="n">
         <v>1164.041807773393</v>
       </c>
-      <c r="AL314" t="n">
+      <c r="AN314" t="n">
         <v>1.980570624845274</v>
       </c>
-      <c r="AM314" t="n">
+      <c r="AO314" t="n">
         <v>1.939210288598939</v>
       </c>
-      <c r="AN314" t="n">
+      <c r="AP314" t="n">
         <v>3.773584905660377e-05</v>
       </c>
     </row>
@@ -40810,15 +42698,21 @@
         <v>-1.049890220956849e-05</v>
       </c>
       <c r="AK315" t="n">
+        <v>-8.076138501436383e-09</v>
+      </c>
+      <c r="AL315" t="n">
+        <v>-0.01633858267716535</v>
+      </c>
+      <c r="AM315" t="n">
         <v>1164.54852076628</v>
       </c>
-      <c r="AL315" t="n">
+      <c r="AN315" t="n">
         <v>1.980570624845274</v>
       </c>
-      <c r="AM315" t="n">
+      <c r="AO315" t="n">
         <v>1.936740238668119</v>
       </c>
-      <c r="AN315" t="n">
+      <c r="AP315" t="n">
         <v>1.574803149606299e-05</v>
       </c>
     </row>
@@ -40938,15 +42832,21 @@
         <v>-1.049890220956849e-05</v>
       </c>
       <c r="AK316" t="n">
+        <v>-7.514062928076342e-09</v>
+      </c>
+      <c r="AL316" t="n">
+        <v>-0.0152014652014652</v>
+      </c>
+      <c r="AM316" t="n">
         <v>1162.992644101899</v>
       </c>
-      <c r="AL316" t="n">
+      <c r="AN316" t="n">
         <v>1.980570624845274</v>
       </c>
-      <c r="AM316" t="n">
+      <c r="AO316" t="n">
         <v>1.940834709691129</v>
       </c>
-      <c r="AN316" t="n">
+      <c r="AP316" t="n">
         <v>1.465201465201465e-05</v>
       </c>
     </row>
@@ -41066,15 +42966,21 @@
         <v>0</v>
       </c>
       <c r="AK317" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL317" t="n">
+        <v>0.01224188790560472</v>
+      </c>
+      <c r="AM317" t="n">
         <v>1000</v>
       </c>
-      <c r="AL317" t="n">
+      <c r="AN317" t="n">
         <v>1.980570624845274</v>
       </c>
-      <c r="AM317" t="n">
+      <c r="AO317" t="n">
         <v>1.946254586876382</v>
       </c>
-      <c r="AN317" t="n">
+      <c r="AP317" t="n">
         <v>1.179941002949853e-05</v>
       </c>
     </row>
@@ -41194,15 +43100,21 @@
         <v>0</v>
       </c>
       <c r="AK318" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL318" t="n">
+        <v>0.01231454005934718</v>
+      </c>
+      <c r="AM318" t="n">
         <v>1000</v>
       </c>
-      <c r="AL318" t="n">
+      <c r="AN318" t="n">
         <v>1.980570624845274</v>
       </c>
-      <c r="AM318" t="n">
+      <c r="AO318" t="n">
         <v>1.945976204262558</v>
       </c>
-      <c r="AN318" t="n">
+      <c r="AP318" t="n">
         <v>0.0007388724035608309</v>
       </c>
     </row>
@@ -41322,15 +43234,21 @@
         <v>0</v>
       </c>
       <c r="AK319" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL319" t="n">
+        <v>0.01257575757575758</v>
+      </c>
+      <c r="AM319" t="n">
         <v>1000</v>
       </c>
-      <c r="AL319" t="n">
+      <c r="AN319" t="n">
         <v>1.980570624845274</v>
       </c>
-      <c r="AM319" t="n">
+      <c r="AO319" t="n">
         <v>1.944970017712993</v>
       </c>
-      <c r="AN319" t="n">
+      <c r="AP319" t="n">
         <v>3.03030303030303e-05</v>
       </c>
     </row>
@@ -41450,15 +43368,21 @@
         <v>0</v>
       </c>
       <c r="AK320" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL320" t="n">
+        <v>0.01251885369532428</v>
+      </c>
+      <c r="AM320" t="n">
         <v>1000</v>
       </c>
-      <c r="AL320" t="n">
+      <c r="AN320" t="n">
         <v>1.980570624845274</v>
       </c>
-      <c r="AM320" t="n">
+      <c r="AO320" t="n">
         <v>1.945189906640978</v>
       </c>
-      <c r="AN320" t="n">
+      <c r="AP320" t="n">
         <v>3.01659125188537e-05</v>
       </c>
     </row>
@@ -41578,15 +43502,21 @@
         <v>0.0003679703698917816</v>
       </c>
       <c r="AK321" t="n">
+        <v>1.850179213432066e-06</v>
+      </c>
+      <c r="AL321" t="n">
+        <v>0.08899676375404532</v>
+      </c>
+      <c r="AM321" t="n">
         <v>1182.150943762585</v>
       </c>
-      <c r="AL321" t="n">
+      <c r="AN321" t="n">
         <v>5.941711874535822</v>
       </c>
-      <c r="AM321" t="n">
+      <c r="AO321" t="n">
         <v>5.356706801969351</v>
       </c>
-      <c r="AN321" t="n">
+      <c r="AP321" t="n">
         <v>1.294498381877023e-05</v>
       </c>
     </row>
@@ -41706,15 +43636,21 @@
         <v>0.0003679703698917816</v>
       </c>
       <c r="AK322" t="n">
+        <v>1.844210893388736e-06</v>
+      </c>
+      <c r="AL322" t="n">
+        <v>0.08870967741935484</v>
+      </c>
+      <c r="AM322" t="n">
         <v>1182.048388376584</v>
       </c>
-      <c r="AL322" t="n">
+      <c r="AN322" t="n">
         <v>5.941711874535822</v>
       </c>
-      <c r="AM322" t="n">
+      <c r="AO322" t="n">
         <v>5.358906486235</v>
       </c>
-      <c r="AN322" t="n">
+      <c r="AP322" t="n">
         <v>0.000803225806451613</v>
       </c>
     </row>
@@ -41834,15 +43770,21 @@
         <v>0.0003679703698917816</v>
       </c>
       <c r="AK323" t="n">
+        <v>1.72200414744129e-06</v>
+      </c>
+      <c r="AL323" t="n">
+        <v>0.08283132530120482</v>
+      </c>
+      <c r="AM323" t="n">
         <v>1181.929843816901</v>
       </c>
-      <c r="AL323" t="n">
+      <c r="AN323" t="n">
         <v>5.941711874535822</v>
       </c>
-      <c r="AM323" t="n">
+      <c r="AO323" t="n">
         <v>5.40452243409571</v>
       </c>
-      <c r="AN323" t="n">
+      <c r="AP323" t="n">
         <v>3.012048192771084e-05</v>
       </c>
     </row>
@@ -41962,15 +43904,21 @@
         <v>0.0003679703698917816</v>
       </c>
       <c r="AK324" t="n">
+        <v>1.69645512448222e-06</v>
+      </c>
+      <c r="AL324" t="n">
+        <v>0.08160237388724036</v>
+      </c>
+      <c r="AM324" t="n">
         <v>1181.927994253743</v>
       </c>
-      <c r="AL324" t="n">
+      <c r="AN324" t="n">
         <v>5.941711874535822</v>
       </c>
-      <c r="AM324" t="n">
+      <c r="AO324" t="n">
         <v>5.413983551035129</v>
       </c>
-      <c r="AN324" t="n">
+      <c r="AP324" t="n">
         <v>2.967359050445104e-05</v>
       </c>
     </row>
@@ -42090,15 +44038,21 @@
         <v>0.0003679703698917816</v>
       </c>
       <c r="AK325" t="n">
+        <v>1.809194230856039e-06</v>
+      </c>
+      <c r="AL325" t="n">
+        <v>0.08702531645569621</v>
+      </c>
+      <c r="AM325" t="n">
         <v>1181.972325642313</v>
       </c>
-      <c r="AL325" t="n">
+      <c r="AN325" t="n">
         <v>5.941711874535822</v>
       </c>
-      <c r="AM325" t="n">
+      <c r="AO325" t="n">
         <v>5.372024669349905</v>
       </c>
-      <c r="AN325" t="n">
+      <c r="AP325" t="n">
         <v>1.265822784810127e-05</v>
       </c>
     </row>
@@ -42218,15 +44172,21 @@
         <v>0.0003679703698917816</v>
       </c>
       <c r="AK326" t="n">
+        <v>1.72200414744129e-06</v>
+      </c>
+      <c r="AL326" t="n">
+        <v>0.08283132530120482</v>
+      </c>
+      <c r="AM326" t="n">
         <v>1182.110158436807</v>
       </c>
-      <c r="AL326" t="n">
+      <c r="AN326" t="n">
         <v>5.941711874535822</v>
       </c>
-      <c r="AM326" t="n">
+      <c r="AO326" t="n">
         <v>5.404599127289927</v>
       </c>
-      <c r="AN326" t="n">
+      <c r="AP326" t="n">
         <v>0.0007500000000000001</v>
       </c>
     </row>
@@ -42346,15 +44306,21 @@
         <v>1.26542967403936e-06</v>
       </c>
       <c r="AK327" t="n">
+        <v>9.448942292387894e-10</v>
+      </c>
+      <c r="AL327" t="n">
+        <v>0.01321656050955414</v>
+      </c>
+      <c r="AM327" t="n">
         <v>1181.613149375631</v>
       </c>
-      <c r="AL327" t="n">
+      <c r="AN327" t="n">
         <v>5.941711874535822</v>
       </c>
-      <c r="AM327" t="n">
+      <c r="AO327" t="n">
         <v>5.367539418141049</v>
       </c>
-      <c r="AN327" t="n">
+      <c r="AP327" t="n">
         <v>1.273885350318471e-05</v>
       </c>
     </row>
@@ -42474,15 +44440,21 @@
         <v>1.26542967403936e-06</v>
       </c>
       <c r="AK328" t="n">
+        <v>9.633012596785061e-10</v>
+      </c>
+      <c r="AL328" t="n">
+        <v>0.01347402597402597</v>
+      </c>
+      <c r="AM328" t="n">
         <v>1181.611296956519</v>
       </c>
-      <c r="AL328" t="n">
+      <c r="AN328" t="n">
         <v>5.941711874535822</v>
       </c>
-      <c r="AM328" t="n">
+      <c r="AO328" t="n">
         <v>5.354194585576508</v>
       </c>
-      <c r="AN328" t="n">
+      <c r="AP328" t="n">
         <v>0.0008084415584415585</v>
       </c>
     </row>
@@ -42602,15 +44574,21 @@
         <v>1.26542967403936e-06</v>
       </c>
       <c r="AK329" t="n">
+        <v>9.101128465674229e-10</v>
+      </c>
+      <c r="AL329" t="n">
+        <v>0.01273006134969325</v>
+      </c>
+      <c r="AM329" t="n">
         <v>1181.606563114583</v>
       </c>
-      <c r="AL329" t="n">
+      <c r="AN329" t="n">
         <v>5.941711874535822</v>
       </c>
-      <c r="AM329" t="n">
+      <c r="AO329" t="n">
         <v>5.392602149991152</v>
       </c>
-      <c r="AN329" t="n">
+      <c r="AP329" t="n">
         <v>3.067484662576687e-05</v>
       </c>
     </row>
@@ -42730,15 +44708,21 @@
         <v>1.26542967403936e-06</v>
       </c>
       <c r="AK330" t="n">
+        <v>9.479130606421081e-10</v>
+      </c>
+      <c r="AL330" t="n">
+        <v>0.01325878594249201</v>
+      </c>
+      <c r="AM330" t="n">
         <v>1181.618179489038</v>
       </c>
-      <c r="AL330" t="n">
+      <c r="AN330" t="n">
         <v>5.941711874535822</v>
       </c>
-      <c r="AM330" t="n">
+      <c r="AO330" t="n">
         <v>5.365356885969903</v>
       </c>
-      <c r="AN330" t="n">
+      <c r="AP330" t="n">
         <v>3.194888178913738e-05</v>
       </c>
     </row>
@@ -42858,15 +44842,21 @@
         <v>1.26542967403936e-06</v>
       </c>
       <c r="AK331" t="n">
+        <v>9.242890591307783e-10</v>
+      </c>
+      <c r="AL331" t="n">
+        <v>0.01292834890965732</v>
+      </c>
+      <c r="AM331" t="n">
         <v>1181.608870456838</v>
       </c>
-      <c r="AL331" t="n">
+      <c r="AN331" t="n">
         <v>5.941711874535822</v>
       </c>
-      <c r="AM331" t="n">
+      <c r="AO331" t="n">
         <v>5.382410919017866</v>
       </c>
-      <c r="AN331" t="n">
+      <c r="AP331" t="n">
         <v>1.246105919003115e-05</v>
       </c>
     </row>
@@ -42986,15 +44976,21 @@
         <v>1.26542967403936e-06</v>
       </c>
       <c r="AK332" t="n">
+        <v>9.38913886015759e-10</v>
+      </c>
+      <c r="AL332" t="n">
+        <v>0.01313291139240506</v>
+      </c>
+      <c r="AM332" t="n">
         <v>1181.609298220403</v>
       </c>
-      <c r="AL332" t="n">
+      <c r="AN332" t="n">
         <v>5.941711874535822</v>
       </c>
-      <c r="AM332" t="n">
+      <c r="AO332" t="n">
         <v>5.371861543830029</v>
       </c>
-      <c r="AN332" t="n">
+      <c r="AP332" t="n">
         <v>0.0007879746835443038</v>
       </c>
     </row>
@@ -43114,15 +45110,21 @@
         <v>1.26542967403936e-06</v>
       </c>
       <c r="AK333" t="n">
+        <v>1.074988362249927e-09</v>
+      </c>
+      <c r="AL333" t="n">
+        <v>0.01503623188405797</v>
+      </c>
+      <c r="AM333" t="n">
         <v>1181.614827323969</v>
       </c>
-      <c r="AL333" t="n">
+      <c r="AN333" t="n">
         <v>5.941711874535822</v>
       </c>
-      <c r="AM333" t="n">
+      <c r="AO333" t="n">
         <v>5.272172221534581</v>
       </c>
-      <c r="AN333" t="n">
+      <c r="AP333" t="n">
         <v>1.449275362318841e-05</v>
       </c>
     </row>
@@ -43242,15 +45244,21 @@
         <v>1.26542967403936e-06</v>
       </c>
       <c r="AK334" t="n">
+        <v>1.273376772450557e-09</v>
+      </c>
+      <c r="AL334" t="n">
+        <v>0.01781115879828326</v>
+      </c>
+      <c r="AM334" t="n">
         <v>1181.651608749548</v>
       </c>
-      <c r="AL334" t="n">
+      <c r="AN334" t="n">
         <v>5.941711874535822</v>
       </c>
-      <c r="AM334" t="n">
+      <c r="AO334" t="n">
         <v>5.122864400531817</v>
       </c>
-      <c r="AN334" t="n">
+      <c r="AP334" t="n">
         <v>0.001068669527896996</v>
       </c>
     </row>
@@ -43370,15 +45378,21 @@
         <v>1.26542967403936e-06</v>
       </c>
       <c r="AK335" t="n">
+        <v>1.186787151923919e-09</v>
+      </c>
+      <c r="AL335" t="n">
+        <v>0.0166</v>
+      </c>
+      <c r="AM335" t="n">
         <v>1181.619247083198</v>
       </c>
-      <c r="AL335" t="n">
+      <c r="AN335" t="n">
         <v>5.941711874535822</v>
       </c>
-      <c r="AM335" t="n">
+      <c r="AO335" t="n">
         <v>5.188508554684578</v>
       </c>
-      <c r="AN335" t="n">
+      <c r="AP335" t="n">
         <v>4e-05</v>
       </c>
     </row>
@@ -43498,15 +45512,21 @@
         <v>1.26542967403936e-06</v>
       </c>
       <c r="AK336" t="n">
+        <v>1.336472017932342e-09</v>
+      </c>
+      <c r="AL336" t="n">
+        <v>0.01869369369369369</v>
+      </c>
+      <c r="AM336" t="n">
         <v>1181.637543105735</v>
       </c>
-      <c r="AL336" t="n">
+      <c r="AN336" t="n">
         <v>5.941711874535822</v>
       </c>
-      <c r="AM336" t="n">
+      <c r="AO336" t="n">
         <v>5.074621637254396</v>
       </c>
-      <c r="AN336" t="n">
+      <c r="AP336" t="n">
         <v>1.801801801801802e-05</v>
       </c>
     </row>
@@ -43626,15 +45646,21 @@
         <v>1.26542967403936e-06</v>
       </c>
       <c r="AK337" t="n">
+        <v>1.289986034699913e-09</v>
+      </c>
+      <c r="AL337" t="n">
+        <v>0.01804347826086956</v>
+      </c>
+      <c r="AM337" t="n">
         <v>1181.635568831372</v>
       </c>
-      <c r="AL337" t="n">
+      <c r="AN337" t="n">
         <v>5.941711874535822</v>
       </c>
-      <c r="AM337" t="n">
+      <c r="AO337" t="n">
         <v>5.110186128756806</v>
       </c>
-      <c r="AN337" t="n">
+      <c r="AP337" t="n">
         <v>0.001082608695652174</v>
       </c>
     </row>
@@ -43754,15 +45780,21 @@
         <v>1.26542967403936e-06</v>
       </c>
       <c r="AK338" t="n">
+        <v>8.334179437667974e-10</v>
+      </c>
+      <c r="AL338" t="n">
+        <v>0.01165730337078652</v>
+      </c>
+      <c r="AM338" t="n">
         <v>1181.605527516097</v>
       </c>
-      <c r="AL338" t="n">
+      <c r="AN338" t="n">
         <v>5.941711874535822</v>
       </c>
-      <c r="AM338" t="n">
+      <c r="AO338" t="n">
         <v>5.447130152619271</v>
       </c>
-      <c r="AN338" t="n">
+      <c r="AP338" t="n">
         <v>2.808988764044944e-05</v>
       </c>
     </row>
@@ -43882,15 +45914,21 @@
         <v>1.26542967403936e-06</v>
       </c>
       <c r="AK339" t="n">
+        <v>1.22265159882272e-09</v>
+      </c>
+      <c r="AL339" t="n">
+        <v>0.01710164835164835</v>
+      </c>
+      <c r="AM339" t="n">
         <v>1181.619505375517</v>
       </c>
-      <c r="AL339" t="n">
+      <c r="AN339" t="n">
         <v>5.941711874535822</v>
       </c>
-      <c r="AM339" t="n">
+      <c r="AO339" t="n">
         <v>5.161392927438174</v>
       </c>
-      <c r="AN339" t="n">
+      <c r="AP339" t="n">
         <v>1.648351648351649e-05</v>
       </c>
     </row>
@@ -44010,15 +46048,21 @@
         <v>0</v>
       </c>
       <c r="AK340" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL340" t="n">
+        <v>0.01313291139240506</v>
+      </c>
+      <c r="AM340" t="n">
         <v>1000</v>
       </c>
-      <c r="AL340" t="n">
+      <c r="AN340" t="n">
         <v>5.941711874535822</v>
       </c>
-      <c r="AM340" t="n">
+      <c r="AO340" t="n">
         <v>5.276652571652459</v>
       </c>
-      <c r="AN340" t="n">
+      <c r="AP340" t="n">
         <v>1.265822784810127e-05</v>
       </c>
     </row>
@@ -44138,15 +46182,21 @@
         <v>0</v>
       </c>
       <c r="AK341" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL341" t="n">
+        <v>0.01431034482758621</v>
+      </c>
+      <c r="AM341" t="n">
         <v>1000</v>
       </c>
-      <c r="AL341" t="n">
+      <c r="AN341" t="n">
         <v>5.941711874535822</v>
       </c>
-      <c r="AM341" t="n">
+      <c r="AO341" t="n">
         <v>5.206027287596967</v>
       </c>
-      <c r="AN341" t="n">
+      <c r="AP341" t="n">
         <v>0.0008586206896551725</v>
       </c>
     </row>
@@ -44266,15 +46316,21 @@
         <v>0</v>
       </c>
       <c r="AK342" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL342" t="n">
+        <v>0.01482142857142857</v>
+      </c>
+      <c r="AM342" t="n">
         <v>1000</v>
       </c>
-      <c r="AL342" t="n">
+      <c r="AN342" t="n">
         <v>5.941711874535822</v>
       </c>
-      <c r="AM342" t="n">
+      <c r="AO342" t="n">
         <v>5.175074083705642</v>
       </c>
-      <c r="AN342" t="n">
+      <c r="AP342" t="n">
         <v>0.0008892857142857144</v>
       </c>
     </row>
@@ -44394,15 +46450,21 @@
         <v>0</v>
       </c>
       <c r="AK343" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL343" t="n">
+        <v>0.01402027027027027</v>
+      </c>
+      <c r="AM343" t="n">
         <v>1000</v>
       </c>
-      <c r="AL343" t="n">
+      <c r="AN343" t="n">
         <v>5.941711874535822</v>
       </c>
-      <c r="AM343" t="n">
+      <c r="AO343" t="n">
         <v>5.223519430718106</v>
       </c>
-      <c r="AN343" t="n">
+      <c r="AP343" t="n">
         <v>3.378378378378378e-05</v>
       </c>
     </row>
@@ -44522,15 +46584,21 @@
         <v>0</v>
       </c>
       <c r="AK344" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL344" t="n">
+        <v>0.01313291139240506</v>
+      </c>
+      <c r="AM344" t="n">
         <v>1000</v>
       </c>
-      <c r="AL344" t="n">
+      <c r="AN344" t="n">
         <v>5.941711874535822</v>
       </c>
-      <c r="AM344" t="n">
+      <c r="AO344" t="n">
         <v>5.276652571652459</v>
       </c>
-      <c r="AN344" t="n">
+      <c r="AP344" t="n">
         <v>3.164556962025316e-05</v>
       </c>
     </row>
@@ -44650,15 +46718,21 @@
         <v>0</v>
       </c>
       <c r="AK345" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL345" t="n">
+        <v>0.01392617449664429</v>
+      </c>
+      <c r="AM345" t="n">
         <v>1000</v>
       </c>
-      <c r="AL345" t="n">
+      <c r="AN345" t="n">
         <v>5.941711874535822</v>
       </c>
-      <c r="AM345" t="n">
+      <c r="AO345" t="n">
         <v>5.229181172642123</v>
       </c>
-      <c r="AN345" t="n">
+      <c r="AP345" t="n">
         <v>1.342281879194631e-05</v>
       </c>
     </row>
@@ -44778,15 +46852,21 @@
         <v>0</v>
       </c>
       <c r="AK346" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL346" t="n">
+        <v>0.0136963696369637</v>
+      </c>
+      <c r="AM346" t="n">
         <v>1000</v>
       </c>
-      <c r="AL346" t="n">
+      <c r="AN346" t="n">
         <v>5.941711874535822</v>
       </c>
-      <c r="AM346" t="n">
+      <c r="AO346" t="n">
         <v>5.242981984724767</v>
       </c>
-      <c r="AN346" t="n">
+      <c r="AP346" t="n">
         <v>1.32013201320132e-05</v>
       </c>
     </row>
@@ -44906,15 +46986,21 @@
         <v>0</v>
       </c>
       <c r="AK347" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL347" t="n">
+        <v>0.01781115879828326</v>
+      </c>
+      <c r="AM347" t="n">
         <v>1000</v>
       </c>
-      <c r="AL347" t="n">
+      <c r="AN347" t="n">
         <v>5.941711874535822</v>
       </c>
-      <c r="AM347" t="n">
+      <c r="AO347" t="n">
         <v>4.991314265709915</v>
       </c>
-      <c r="AN347" t="n">
+      <c r="AP347" t="n">
         <v>0.001068669527896996</v>
       </c>
     </row>
@@ -45034,15 +47120,21 @@
         <v>0</v>
       </c>
       <c r="AK348" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL348" t="n">
+        <v>0.0166</v>
+      </c>
+      <c r="AM348" t="n">
         <v>1000</v>
       </c>
-      <c r="AL348" t="n">
+      <c r="AN348" t="n">
         <v>5.941711874535822</v>
       </c>
-      <c r="AM348" t="n">
+      <c r="AO348" t="n">
         <v>5.066223800898937</v>
       </c>
-      <c r="AN348" t="n">
+      <c r="AP348" t="n">
         <v>0.004356</v>
       </c>
     </row>
@@ -45162,15 +47254,21 @@
         <v>0</v>
       </c>
       <c r="AK349" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL349" t="n">
+        <v>0.01238805970149254</v>
+      </c>
+      <c r="AM349" t="n">
         <v>1000</v>
       </c>
-      <c r="AL349" t="n">
+      <c r="AN349" t="n">
         <v>5.941711874535822</v>
       </c>
-      <c r="AM349" t="n">
+      <c r="AO349" t="n">
         <v>5.320765130110456</v>
       </c>
-      <c r="AN349" t="n">
+      <c r="AP349" t="n">
         <v>0.003250746268656716</v>
       </c>
     </row>
@@ -45290,15 +47388,21 @@
         <v>-1.049890220956849e-05</v>
       </c>
       <c r="AK350" t="n">
+        <v>-7.147523273048226e-09</v>
+      </c>
+      <c r="AL350" t="n">
+        <v>-0.01445993031358885</v>
+      </c>
+      <c r="AM350" t="n">
         <v>1163.636297433466</v>
       </c>
-      <c r="AL350" t="n">
+      <c r="AN350" t="n">
         <v>1.980570624845274</v>
       </c>
-      <c r="AM350" t="n">
+      <c r="AO350" t="n">
         <v>1.943497585957407</v>
       </c>
-      <c r="AN350" t="n">
+      <c r="AP350" t="n">
         <v>1.393728222996516e-05</v>
       </c>
     </row>
@@ -45418,15 +47522,21 @@
         <v>-1.049890220956849e-05</v>
       </c>
       <c r="AK351" t="n">
+        <v>-6.883688521358527e-09</v>
+      </c>
+      <c r="AL351" t="n">
+        <v>-0.01392617449664429</v>
+      </c>
+      <c r="AM351" t="n">
         <v>1163.267671654179</v>
       </c>
-      <c r="AL351" t="n">
+      <c r="AN351" t="n">
         <v>1.980570624845274</v>
       </c>
-      <c r="AM351" t="n">
+      <c r="AO351" t="n">
         <v>1.945354547054001</v>
       </c>
-      <c r="AN351" t="n">
+      <c r="AP351" t="n">
         <v>0.0008355704697986578</v>
       </c>
     </row>
@@ -45546,15 +47656,21 @@
         <v>-1.049890220956849e-05</v>
       </c>
       <c r="AK352" t="n">
+        <v>-8.076138501436383e-09</v>
+      </c>
+      <c r="AL352" t="n">
+        <v>-0.01633858267716535</v>
+      </c>
+      <c r="AM352" t="n">
         <v>1166.136123866585</v>
       </c>
-      <c r="AL352" t="n">
+      <c r="AN352" t="n">
         <v>1.980570624845274</v>
       </c>
-      <c r="AM352" t="n">
+      <c r="AO352" t="n">
         <v>1.936799383930199</v>
       </c>
-      <c r="AN352" t="n">
+      <c r="AP352" t="n">
         <v>0.0009803149606299212</v>
       </c>
     </row>
@@ -45674,15 +47790,21 @@
         <v>-1.049890220956849e-05</v>
       </c>
       <c r="AK353" t="n">
+        <v>-7.682918274774686e-09</v>
+      </c>
+      <c r="AL353" t="n">
+        <v>-0.01554307116104869</v>
+      </c>
+      <c r="AM353" t="n">
         <v>1164.391923869716</v>
       </c>
-      <c r="AL353" t="n">
+      <c r="AN353" t="n">
         <v>1.980570624845274</v>
       </c>
-      <c r="AM353" t="n">
+      <c r="AO353" t="n">
         <v>1.939648706067348</v>
       </c>
-      <c r="AN353" t="n">
+      <c r="AP353" t="n">
         <v>3.745318352059925e-05</v>
       </c>
     </row>
@@ -45802,15 +47924,21 @@
         <v>-1.049890220956849e-05</v>
       </c>
       <c r="AK354" t="n">
+        <v>-7.352470176934914e-09</v>
+      </c>
+      <c r="AL354" t="n">
+        <v>-0.01487455197132617</v>
+      </c>
+      <c r="AM354" t="n">
         <v>1163.576220189842</v>
       </c>
-      <c r="AL354" t="n">
+      <c r="AN354" t="n">
         <v>1.980570624845274</v>
       </c>
-      <c r="AM354" t="n">
+      <c r="AO354" t="n">
         <v>1.942025379477729</v>
       </c>
-      <c r="AN354" t="n">
+      <c r="AP354" t="n">
         <v>0.00089247311827957</v>
       </c>
     </row>
@@ -45930,15 +48058,21 @@
         <v>-1.049890220956849e-05</v>
       </c>
       <c r="AK355" t="n">
+        <v>-6.197399333428523e-09</v>
+      </c>
+      <c r="AL355" t="n">
+        <v>-0.01253776435045317</v>
+      </c>
+      <c r="AM355" t="n">
         <v>1162.538047193301</v>
       </c>
-      <c r="AL355" t="n">
+      <c r="AN355" t="n">
         <v>1.980570624845274</v>
       </c>
-      <c r="AM355" t="n">
+      <c r="AO355" t="n">
         <v>1.9500624651578</v>
       </c>
-      <c r="AN355" t="n">
+      <c r="AP355" t="n">
         <v>3.021148036253776e-05</v>
       </c>
     </row>
@@ -46058,15 +48192,21 @@
         <v>-1.049890220956849e-05</v>
       </c>
       <c r="AK356" t="n">
+        <v>-6.123400535417436e-09</v>
+      </c>
+      <c r="AL356" t="n">
+        <v>-0.01238805970149254</v>
+      </c>
+      <c r="AM356" t="n">
         <v>1162.628266879545</v>
       </c>
-      <c r="AL356" t="n">
+      <c r="AN356" t="n">
         <v>1.980570624845274</v>
       </c>
-      <c r="AM356" t="n">
+      <c r="AO356" t="n">
         <v>1.950562927926784</v>
       </c>
-      <c r="AN356" t="n">
+      <c r="AP356" t="n">
         <v>1.194029850746269e-05</v>
       </c>
     </row>
@@ -46186,15 +48326,21 @@
         <v>1.26542967403936e-06</v>
       </c>
       <c r="AK357" t="n">
+        <v>8.963649183715405e-10</v>
+      </c>
+      <c r="AL357" t="n">
+        <v>0.01253776435045317</v>
+      </c>
+      <c r="AM357" t="n">
         <v>1181.609101848981</v>
       </c>
-      <c r="AL357" t="n">
+      <c r="AN357" t="n">
         <v>1.980570624845274</v>
       </c>
-      <c r="AM357" t="n">
+      <c r="AO357" t="n">
         <v>1.950554552253744</v>
       </c>
-      <c r="AN357" t="n">
+      <c r="AP357" t="n">
         <v>1.208459214501511e-05</v>
       </c>
     </row>
@@ -46314,15 +48460,21 @@
         <v>1.26542967403936e-06</v>
       </c>
       <c r="AK358" t="n">
+        <v>8.883137364699995e-10</v>
+      </c>
+      <c r="AL358" t="n">
+        <v>0.0124251497005988</v>
+      </c>
+      <c r="AM358" t="n">
         <v>1181.606496443001</v>
       </c>
-      <c r="AL358" t="n">
+      <c r="AN358" t="n">
         <v>1.980570624845274</v>
       </c>
-      <c r="AM358" t="n">
+      <c r="AO358" t="n">
         <v>1.950923511090371</v>
       </c>
-      <c r="AN358" t="n">
+      <c r="AP358" t="n">
         <v>1.197604790419162e-05</v>
       </c>
     </row>
@@ -46442,15 +48594,21 @@
         <v>1.26542967403936e-06</v>
       </c>
       <c r="AK359" t="n">
+        <v>9.073296268531495e-10</v>
+      </c>
+      <c r="AL359" t="n">
+        <v>0.01269113149847095</v>
+      </c>
+      <c r="AM359" t="n">
         <v>1181.609859518197</v>
       </c>
-      <c r="AL359" t="n">
+      <c r="AN359" t="n">
         <v>1.980570624845274</v>
       </c>
-      <c r="AM359" t="n">
+      <c r="AO359" t="n">
         <v>1.950049900974653</v>
       </c>
-      <c r="AN359" t="n">
+      <c r="AP359" t="n">
         <v>0.000761467889908257</v>
       </c>
     </row>
@@ -46570,15 +48728,21 @@
         <v>1.26542967403936e-06</v>
       </c>
       <c r="AK360" t="n">
+        <v>8.778011478727215e-10</v>
+      </c>
+      <c r="AL360" t="n">
+        <v>0.01227810650887574</v>
+      </c>
+      <c r="AM360" t="n">
         <v>1181.604084034969</v>
       </c>
-      <c r="AL360" t="n">
+      <c r="AN360" t="n">
         <v>1.980570624845274</v>
       </c>
-      <c r="AM360" t="n">
+      <c r="AO360" t="n">
         <v>1.951403312346719</v>
       </c>
-      <c r="AN360" t="n">
+      <c r="AP360" t="n">
         <v>2.958579881656804e-05</v>
       </c>
     </row>
@@ -46698,15 +48862,21 @@
         <v>1.26542967403936e-06</v>
       </c>
       <c r="AK361" t="n">
+        <v>9.129131937876305e-10</v>
+      </c>
+      <c r="AL361" t="n">
+        <v>0.01276923076923077</v>
+      </c>
+      <c r="AM361" t="n">
         <v>1181.611858888701</v>
       </c>
-      <c r="AL361" t="n">
+      <c r="AN361" t="n">
         <v>1.980570624845274</v>
       </c>
-      <c r="AM361" t="n">
+      <c r="AO361" t="n">
         <v>1.949792030555855</v>
       </c>
-      <c r="AN361" t="n">
+      <c r="AP361" t="n">
         <v>3.076923076923077e-05</v>
       </c>
     </row>
@@ -46826,15 +48996,21 @@
         <v>1.26542967403936e-06</v>
       </c>
       <c r="AK362" t="n">
+        <v>8.830261547052972e-10</v>
+      </c>
+      <c r="AL362" t="n">
+        <v>0.01235119047619048</v>
+      </c>
+      <c r="AM362" t="n">
         <v>1181.616919647615</v>
       </c>
-      <c r="AL362" t="n">
+      <c r="AN362" t="n">
         <v>1.980570624845274</v>
       </c>
-      <c r="AM362" t="n">
+      <c r="AO362" t="n">
         <v>1.951165410443539</v>
       </c>
-      <c r="AN362" t="n">
+      <c r="AP362" t="n">
         <v>1.190476190476191e-05</v>
       </c>
     </row>
@@ -46954,15 +49130,21 @@
         <v>1.26542967403936e-06</v>
       </c>
       <c r="AK363" t="n">
+        <v>8.856620536745667e-10</v>
+      </c>
+      <c r="AL363" t="n">
+        <v>0.01238805970149254</v>
+      </c>
+      <c r="AM363" t="n">
         <v>1181.610340523868</v>
       </c>
-      <c r="AL363" t="n">
+      <c r="AN363" t="n">
         <v>1.980570624845274</v>
       </c>
-      <c r="AM363" t="n">
+      <c r="AO363" t="n">
         <v>1.95104485885576</v>
       </c>
-      <c r="AN363" t="n">
+      <c r="AP363" t="n">
         <v>0.0007432835820895523</v>
       </c>
     </row>
@@ -47082,15 +49264,21 @@
         <v>1.26542967403936e-06</v>
       </c>
       <c r="AK364" t="n">
+        <v>8.856620536745667e-10</v>
+      </c>
+      <c r="AL364" t="n">
+        <v>0.01238805970149254</v>
+      </c>
+      <c r="AM364" t="n">
         <v>1181.612974430891</v>
       </c>
-      <c r="AL364" t="n">
+      <c r="AN364" t="n">
         <v>1.980570624845274</v>
       </c>
-      <c r="AM364" t="n">
+      <c r="AO364" t="n">
         <v>1.951044924664712</v>
       </c>
-      <c r="AN364" t="n">
+      <c r="AP364" t="n">
         <v>1.194029850746269e-05</v>
       </c>
     </row>
@@ -47210,15 +49398,21 @@
         <v>1.26542967403936e-06</v>
       </c>
       <c r="AK365" t="n">
+        <v>1.027817972220484e-09</v>
+      </c>
+      <c r="AL365" t="n">
+        <v>0.01437644341801386</v>
+      </c>
+      <c r="AM365" t="n">
         <v>1181.615399356003</v>
       </c>
-      <c r="AL365" t="n">
+      <c r="AN365" t="n">
         <v>1.980570624845274</v>
       </c>
-      <c r="AM365" t="n">
+      <c r="AO365" t="n">
         <v>1.9443485909607</v>
       </c>
-      <c r="AN365" t="n">
+      <c r="AP365" t="n">
         <v>3.46420323325635e-05</v>
       </c>
     </row>
@@ -47338,15 +49532,21 @@
         <v>1.26542967403936e-06</v>
       </c>
       <c r="AK366" t="n">
+        <v>9.38913886015759e-10</v>
+      </c>
+      <c r="AL366" t="n">
+        <v>0.01313291139240506</v>
+      </c>
+      <c r="AM366" t="n">
         <v>1181.606741209792</v>
       </c>
-      <c r="AL366" t="n">
+      <c r="AN366" t="n">
         <v>1.980570624845274</v>
       </c>
-      <c r="AM366" t="n">
+      <c r="AO366" t="n">
         <v>1.948582654483628</v>
       </c>
-      <c r="AN366" t="n">
+      <c r="AP366" t="n">
         <v>3.164556962025316e-05</v>
       </c>
     </row>
@@ -47466,15 +49666,21 @@
         <v>0.0003679703698917816</v>
       </c>
       <c r="AK367" t="n">
+        <v>1.732440536213661e-06</v>
+      </c>
+      <c r="AL367" t="n">
+        <v>0.08333333333333334</v>
+      </c>
+      <c r="AM367" t="n">
         <v>1182.025444702944</v>
       </c>
-      <c r="AL367" t="n">
+      <c r="AN367" t="n">
         <v>1.980570624845274</v>
       </c>
-      <c r="AM367" t="n">
+      <c r="AO367" t="n">
         <v>1.950440367967274</v>
       </c>
-      <c r="AN367" t="n">
+      <c r="AP367" t="n">
         <v>1.212121212121212e-05</v>
       </c>
     </row>
@@ -47594,15 +49800,21 @@
         <v>0.0003679703698917816</v>
       </c>
       <c r="AK368" t="n">
+        <v>1.681486402795612e-06</v>
+      </c>
+      <c r="AL368" t="n">
+        <v>0.08088235294117647</v>
+      </c>
+      <c r="AM368" t="n">
         <v>1182.472176111635</v>
       </c>
-      <c r="AL368" t="n">
+      <c r="AN368" t="n">
         <v>1.980570624845274</v>
       </c>
-      <c r="AM368" t="n">
+      <c r="AO368" t="n">
         <v>1.951659430992412</v>
       </c>
-      <c r="AN368" t="n">
+      <c r="AP368" t="n">
         <v>0.0007323529411764708</v>
       </c>
     </row>
@@ -47722,15 +49934,21 @@
         <v>0.0003679703698917816</v>
       </c>
       <c r="AK369" t="n">
+        <v>1.711692745360803e-06</v>
+      </c>
+      <c r="AL369" t="n">
+        <v>0.08233532934131738</v>
+      </c>
+      <c r="AM369" t="n">
         <v>1182.252227163425</v>
       </c>
-      <c r="AL369" t="n">
+      <c r="AN369" t="n">
         <v>1.980570624845274</v>
       </c>
-      <c r="AM369" t="n">
+      <c r="AO369" t="n">
         <v>1.950939701035088</v>
       </c>
-      <c r="AN369" t="n">
+      <c r="AP369" t="n">
         <v>0.0007455089820359282</v>
       </c>
     </row>
@@ -47850,15 +50068,21 @@
         <v>0.0003679703698917816</v>
       </c>
       <c r="AK370" t="n">
+        <v>1.732440536213661e-06</v>
+      </c>
+      <c r="AL370" t="n">
+        <v>0.08333333333333334</v>
+      </c>
+      <c r="AM370" t="n">
         <v>1182.325495177653</v>
       </c>
-      <c r="AL370" t="n">
+      <c r="AN370" t="n">
         <v>1.980570624845274</v>
       </c>
-      <c r="AM370" t="n">
+      <c r="AO370" t="n">
         <v>1.950448010277268</v>
       </c>
-      <c r="AN370" t="n">
+      <c r="AP370" t="n">
         <v>3.03030303030303e-05</v>
       </c>
     </row>
@@ -47978,15 +50202,21 @@
         <v>0.0003679703698917816</v>
       </c>
       <c r="AK371" t="n">
+        <v>1.748334486087181e-06</v>
+      </c>
+      <c r="AL371" t="n">
+        <v>0.08409785932721714</v>
+      </c>
+      <c r="AM371" t="n">
         <v>1182.980827195341</v>
       </c>
-      <c r="AL371" t="n">
+      <c r="AN371" t="n">
         <v>1.980570624845274</v>
       </c>
-      <c r="AM371" t="n">
+      <c r="AO371" t="n">
         <v>1.950085242854228</v>
       </c>
-      <c r="AN371" t="n">
+      <c r="AP371" t="n">
         <v>3.058103975535168e-05</v>
       </c>
     </row>
@@ -48106,15 +50336,21 @@
         <v>0.0003679703698917816</v>
       </c>
       <c r="AK372" t="n">
+        <v>1.706583214777636e-06</v>
+      </c>
+      <c r="AL372" t="n">
+        <v>0.08208955223880597</v>
+      </c>
+      <c r="AM372" t="n">
         <v>1182.143664073683</v>
       </c>
-      <c r="AL372" t="n">
+      <c r="AN372" t="n">
         <v>1.980570624845274</v>
       </c>
-      <c r="AM372" t="n">
+      <c r="AO372" t="n">
         <v>1.951058178186397</v>
       </c>
-      <c r="AN372" t="n">
+      <c r="AP372" t="n">
         <v>1.194029850746269e-05</v>
       </c>
     </row>
@@ -48234,15 +50470,21 @@
         <v>0.0003679703698917816</v>
       </c>
       <c r="AK373" t="n">
+        <v>1.676555357626124e-06</v>
+      </c>
+      <c r="AL373" t="n">
+        <v>0.08064516129032258</v>
+      </c>
+      <c r="AM373" t="n">
         <v>1182.082997807731</v>
       </c>
-      <c r="AL373" t="n">
+      <c r="AN373" t="n">
         <v>1.980570624845274</v>
       </c>
-      <c r="AM373" t="n">
+      <c r="AO373" t="n">
         <v>1.951766062696067</v>
       </c>
-      <c r="AN373" t="n">
+      <c r="AP373" t="n">
         <v>0.0007302052785923755</v>
       </c>
     </row>
